--- a/Studymaterials/中学生英作文現在完了形_経験用法編.xlsx
+++ b/Studymaterials/中学生英作文現在完了形_経験用法編.xlsx
@@ -10,8 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="解答回答現在完了_経験" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'問題現在完了_経験'!$A$1:$J$155</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'解答回答現在完了_経験'!$A$1:$J$155</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'問題現在完了_経験'!$A$1:$J$263</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'解答回答現在完了_経験'!$A$1:$J$263</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -1077,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J155"/>
+  <dimension ref="A1:J263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <sheetData>
     <row r="1" ht="20" customHeight="1" s="6">
@@ -1128,8 +1128,8 @@
       <c r="A4" s="55" t="inlineStr">
         <is>
           <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
+※疑問文では ever、否定では never または not ... before を使います。
 ※回数は four times / five times のように表します。
-※否定では never または not ... before を使います。
 ※相手が答える形なので、返答では I / we ではなく you を使います。</t>
         </is>
       </c>
@@ -1143,26 +1143,26 @@
       <c r="I4" s="27" t="n"/>
       <c r="J4" s="57" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1" s="6">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>私は京都を4回訪れたことがあります。</t>
-        </is>
-      </c>
-      <c r="B5" s="27" t="n"/>
-      <c r="C5" s="27" t="n"/>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="27" t="n"/>
-      <c r="F5" s="27" t="n"/>
-      <c r="G5" s="27" t="n"/>
-      <c r="H5" s="27" t="n"/>
-      <c r="I5" s="27" t="n"/>
-      <c r="J5" s="57" t="n"/>
-    </row>
-    <row r="6" ht="26" customHeight="1" s="6">
+    <row r="5" ht="18" customHeight="1" s="6">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>【基本】訪れたことがある・ない</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="25" t="n"/>
+      <c r="I5" s="25" t="n"/>
+      <c r="J5" s="56" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>私は京都を訪れたことがあります。</t>
         </is>
       </c>
       <c r="B6" s="27" t="n"/>
@@ -1175,10 +1175,10 @@
       <c r="I6" s="27" t="n"/>
       <c r="J6" s="57" t="n"/>
     </row>
-    <row r="7" ht="20" customHeight="1" s="6">
+    <row r="7" ht="22" customHeight="1" s="6">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>私はまだ一度も京都を訪れたことがありません。</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B7" s="27" t="n"/>
@@ -1191,10 +1191,10 @@
       <c r="I7" s="27" t="n"/>
       <c r="J7" s="57" t="n"/>
     </row>
-    <row r="8" ht="26" customHeight="1" s="6">
+    <row r="8" ht="18" customHeight="1" s="6">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>私はまだ一度も京都を訪れたことがありません。</t>
         </is>
       </c>
       <c r="B8" s="27" t="n"/>
@@ -1207,10 +1207,10 @@
       <c r="I8" s="27" t="n"/>
       <c r="J8" s="57" t="n"/>
     </row>
-    <row r="9" ht="26" customHeight="1" s="6">
+    <row r="9" ht="22" customHeight="1" s="6">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B9" s="27" t="n"/>
@@ -1223,10 +1223,10 @@
       <c r="I9" s="27" t="n"/>
       <c r="J9" s="57" t="n"/>
     </row>
-    <row r="10" ht="26" customHeight="1" s="6">
+    <row r="10" ht="22" customHeight="1" s="6">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B10" s="27" t="n"/>
@@ -1239,10 +1239,10 @@
       <c r="I10" s="27" t="n"/>
       <c r="J10" s="57" t="n"/>
     </row>
-    <row r="11" ht="20" customHeight="1" s="6">
+    <row r="11" ht="22" customHeight="1" s="6">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>私は京都を何回訪れたことがありますか。</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B11" s="27" t="n"/>
@@ -1255,10 +1255,10 @@
       <c r="I11" s="27" t="n"/>
       <c r="J11" s="57" t="n"/>
     </row>
-    <row r="12" ht="26" customHeight="1" s="6">
+    <row r="12" ht="18" customHeight="1" s="6">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>回答（疑問文）：</t>
+          <t>私は京都を訪れたことがありますか。</t>
         </is>
       </c>
       <c r="B12" s="27" t="n"/>
@@ -1271,10 +1271,10 @@
       <c r="I12" s="27" t="n"/>
       <c r="J12" s="57" t="n"/>
     </row>
-    <row r="13" ht="20" customHeight="1" s="6">
+    <row r="13" ht="22" customHeight="1" s="6">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>5回訪れたことがあります。</t>
+          <t>回答（疑問文）：</t>
         </is>
       </c>
       <c r="B13" s="27" t="n"/>
@@ -1287,10 +1287,10 @@
       <c r="I13" s="27" t="n"/>
       <c r="J13" s="57" t="n"/>
     </row>
-    <row r="14" ht="26" customHeight="1" s="6">
+    <row r="14" ht="18" customHeight="1" s="6">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>回答（返答）：</t>
+          <t>はい、あります。</t>
         </is>
       </c>
       <c r="B14" s="27" t="n"/>
@@ -1303,10 +1303,10 @@
       <c r="I14" s="27" t="n"/>
       <c r="J14" s="57" t="n"/>
     </row>
-    <row r="15" ht="20" customHeight="1" s="6">
+    <row r="15" ht="22" customHeight="1" s="6">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>一度も訪れたことがありません。</t>
+          <t>回答（返答）：</t>
         </is>
       </c>
       <c r="B15" s="27" t="n"/>
@@ -1319,10 +1319,10 @@
       <c r="I15" s="27" t="n"/>
       <c r="J15" s="57" t="n"/>
     </row>
-    <row r="16" ht="26" customHeight="1" s="6">
+    <row r="16" ht="18" customHeight="1" s="6">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>いいえ、ありません。</t>
         </is>
       </c>
       <c r="B16" s="27" t="n"/>
@@ -1335,10 +1335,10 @@
       <c r="I16" s="27" t="n"/>
       <c r="J16" s="57" t="n"/>
     </row>
-    <row r="17" ht="26" customHeight="1" s="6">
+    <row r="17" ht="22" customHeight="1" s="6">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B17" s="27" t="n"/>
@@ -1351,10 +1351,10 @@
       <c r="I17" s="27" t="n"/>
       <c r="J17" s="57" t="n"/>
     </row>
-    <row r="18" ht="26" customHeight="1" s="6">
+    <row r="18" ht="22" customHeight="1" s="6">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B18" s="27" t="n"/>
@@ -1367,8 +1367,12 @@
       <c r="I18" s="27" t="n"/>
       <c r="J18" s="57" t="n"/>
     </row>
-    <row r="19" ht="6" customHeight="1" s="6">
-      <c r="A19" s="11" t="n"/>
+    <row r="19" ht="22" customHeight="1" s="6">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
+        </is>
+      </c>
       <c r="B19" s="27" t="n"/>
       <c r="C19" s="27" t="n"/>
       <c r="D19" s="27" t="n"/>
@@ -1382,7 +1386,7 @@
     <row r="20" ht="18" customHeight="1" s="6">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>2．主語は「あなた」で書いてください。</t>
+          <t>【回数】何回訪れたことがあるか</t>
         </is>
       </c>
       <c r="B20" s="25" t="n"/>
@@ -1395,12 +1399,10 @@
       <c r="I20" s="25" t="n"/>
       <c r="J20" s="56" t="n"/>
     </row>
-    <row r="21" ht="60" customHeight="1" s="6">
-      <c r="A21" s="55" t="inlineStr">
-        <is>
-          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
-※回数は four times / five times のように表します。
-※否定では never または not ... before を使います。</t>
+    <row r="21" ht="18" customHeight="1" s="6">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>私は京都を4回訪れたことがあります。</t>
         </is>
       </c>
       <c r="B21" s="27" t="n"/>
@@ -1413,10 +1415,10 @@
       <c r="I21" s="27" t="n"/>
       <c r="J21" s="57" t="n"/>
     </row>
-    <row r="22" ht="20" customHeight="1" s="6">
+    <row r="22" ht="22" customHeight="1" s="6">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>あなたは京都を4回訪れたことがあります。</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B22" s="27" t="n"/>
@@ -1429,10 +1431,10 @@
       <c r="I22" s="27" t="n"/>
       <c r="J22" s="57" t="n"/>
     </row>
-    <row r="23" ht="26" customHeight="1" s="6">
+    <row r="23" ht="18" customHeight="1" s="6">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>私は京都を何回訪れたことがありますか。</t>
         </is>
       </c>
       <c r="B23" s="27" t="n"/>
@@ -1445,10 +1447,10 @@
       <c r="I23" s="27" t="n"/>
       <c r="J23" s="57" t="n"/>
     </row>
-    <row r="24" ht="20" customHeight="1" s="6">
+    <row r="24" ht="22" customHeight="1" s="6">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>あなたはまだ一度も京都を訪れたことがありません。</t>
+          <t>回答（疑問文）：</t>
         </is>
       </c>
       <c r="B24" s="27" t="n"/>
@@ -1461,10 +1463,10 @@
       <c r="I24" s="27" t="n"/>
       <c r="J24" s="57" t="n"/>
     </row>
-    <row r="25" ht="26" customHeight="1" s="6">
+    <row r="25" ht="18" customHeight="1" s="6">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>5回訪れたことがあります。</t>
         </is>
       </c>
       <c r="B25" s="27" t="n"/>
@@ -1477,10 +1479,10 @@
       <c r="I25" s="27" t="n"/>
       <c r="J25" s="57" t="n"/>
     </row>
-    <row r="26" ht="26" customHeight="1" s="6">
+    <row r="26" ht="22" customHeight="1" s="6">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（返答）：</t>
         </is>
       </c>
       <c r="B26" s="27" t="n"/>
@@ -1493,10 +1495,10 @@
       <c r="I26" s="27" t="n"/>
       <c r="J26" s="57" t="n"/>
     </row>
-    <row r="27" ht="26" customHeight="1" s="6">
+    <row r="27" ht="18" customHeight="1" s="6">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>一度も訪れたことがありません。</t>
         </is>
       </c>
       <c r="B27" s="27" t="n"/>
@@ -1509,10 +1511,10 @@
       <c r="I27" s="27" t="n"/>
       <c r="J27" s="57" t="n"/>
     </row>
-    <row r="28" ht="20" customHeight="1" s="6">
+    <row r="28" ht="22" customHeight="1" s="6">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>あなたは京都を何回訪れたことがありますか。</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B28" s="27" t="n"/>
@@ -1525,10 +1527,10 @@
       <c r="I28" s="27" t="n"/>
       <c r="J28" s="57" t="n"/>
     </row>
-    <row r="29" ht="26" customHeight="1" s="6">
+    <row r="29" ht="22" customHeight="1" s="6">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>回答（疑問文）：</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B29" s="27" t="n"/>
@@ -1541,10 +1543,10 @@
       <c r="I29" s="27" t="n"/>
       <c r="J29" s="57" t="n"/>
     </row>
-    <row r="30" ht="20" customHeight="1" s="6">
+    <row r="30" ht="22" customHeight="1" s="6">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>5回訪れたことがあります。</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B30" s="27" t="n"/>
@@ -1557,12 +1559,8 @@
       <c r="I30" s="27" t="n"/>
       <c r="J30" s="57" t="n"/>
     </row>
-    <row r="31" ht="26" customHeight="1" s="6">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>回答（返答）：</t>
-        </is>
-      </c>
+    <row r="31" ht="6" customHeight="1" s="6">
+      <c r="A31" s="11" t="n"/>
       <c r="B31" s="27" t="n"/>
       <c r="C31" s="27" t="n"/>
       <c r="D31" s="27" t="n"/>
@@ -1573,26 +1571,28 @@
       <c r="I31" s="27" t="n"/>
       <c r="J31" s="57" t="n"/>
     </row>
-    <row r="32" ht="20" customHeight="1" s="6">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>一度も訪れたことがありません。</t>
-        </is>
-      </c>
-      <c r="B32" s="27" t="n"/>
-      <c r="C32" s="27" t="n"/>
-      <c r="D32" s="27" t="n"/>
-      <c r="E32" s="27" t="n"/>
-      <c r="F32" s="27" t="n"/>
-      <c r="G32" s="27" t="n"/>
-      <c r="H32" s="27" t="n"/>
-      <c r="I32" s="27" t="n"/>
-      <c r="J32" s="57" t="n"/>
-    </row>
-    <row r="33" ht="26" customHeight="1" s="6">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>回答（基本形）：</t>
+    <row r="32" ht="18" customHeight="1" s="6">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>2．主語は「あなた」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="n"/>
+      <c r="C32" s="25" t="n"/>
+      <c r="D32" s="25" t="n"/>
+      <c r="E32" s="25" t="n"/>
+      <c r="F32" s="25" t="n"/>
+      <c r="G32" s="25" t="n"/>
+      <c r="H32" s="25" t="n"/>
+      <c r="I32" s="25" t="n"/>
+      <c r="J32" s="56" t="n"/>
+    </row>
+    <row r="33" ht="60" customHeight="1" s="6">
+      <c r="A33" s="55" t="inlineStr">
+        <is>
+          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
+※疑問文では ever、否定では never または not ... before を使います。
+※回数は four times / five times のように表します。</t>
         </is>
       </c>
       <c r="B33" s="27" t="n"/>
@@ -1605,26 +1605,26 @@
       <c r="I33" s="27" t="n"/>
       <c r="J33" s="57" t="n"/>
     </row>
-    <row r="34" ht="26" customHeight="1" s="6">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>回答（言いかえ）：</t>
-        </is>
-      </c>
-      <c r="B34" s="27" t="n"/>
-      <c r="C34" s="27" t="n"/>
-      <c r="D34" s="27" t="n"/>
-      <c r="E34" s="27" t="n"/>
-      <c r="F34" s="27" t="n"/>
-      <c r="G34" s="27" t="n"/>
-      <c r="H34" s="27" t="n"/>
-      <c r="I34" s="27" t="n"/>
-      <c r="J34" s="57" t="n"/>
-    </row>
-    <row r="35" ht="26" customHeight="1" s="6">
+    <row r="34" ht="18" customHeight="1" s="6">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>【基本】訪れたことがある・ない</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="n"/>
+      <c r="C34" s="25" t="n"/>
+      <c r="D34" s="25" t="n"/>
+      <c r="E34" s="25" t="n"/>
+      <c r="F34" s="25" t="n"/>
+      <c r="G34" s="25" t="n"/>
+      <c r="H34" s="25" t="n"/>
+      <c r="I34" s="25" t="n"/>
+      <c r="J34" s="56" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1" s="6">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>あなたは京都を訪れたことがあります。</t>
         </is>
       </c>
       <c r="B35" s="27" t="n"/>
@@ -1637,8 +1637,12 @@
       <c r="I35" s="27" t="n"/>
       <c r="J35" s="57" t="n"/>
     </row>
-    <row r="36" ht="6" customHeight="1" s="6">
-      <c r="A36" s="11" t="n"/>
+    <row r="36" ht="22" customHeight="1" s="6">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
       <c r="B36" s="27" t="n"/>
       <c r="C36" s="27" t="n"/>
       <c r="D36" s="27" t="n"/>
@@ -1650,27 +1654,25 @@
       <c r="J36" s="57" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="6">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>3．主語は「彼」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B37" s="25" t="n"/>
-      <c r="C37" s="25" t="n"/>
-      <c r="D37" s="25" t="n"/>
-      <c r="E37" s="25" t="n"/>
-      <c r="F37" s="25" t="n"/>
-      <c r="G37" s="25" t="n"/>
-      <c r="H37" s="25" t="n"/>
-      <c r="I37" s="25" t="n"/>
-      <c r="J37" s="56" t="n"/>
-    </row>
-    <row r="38" ht="60" customHeight="1" s="6">
-      <c r="A38" s="55" t="inlineStr">
-        <is>
-          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
-※回数は four times / five times のように表します。
-※否定では never または not ... before を使います。</t>
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>あなたはまだ一度も京都を訪れたことがありません。</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="n"/>
+      <c r="C37" s="27" t="n"/>
+      <c r="D37" s="27" t="n"/>
+      <c r="E37" s="27" t="n"/>
+      <c r="F37" s="27" t="n"/>
+      <c r="G37" s="27" t="n"/>
+      <c r="H37" s="27" t="n"/>
+      <c r="I37" s="27" t="n"/>
+      <c r="J37" s="57" t="n"/>
+    </row>
+    <row r="38" ht="22" customHeight="1" s="6">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B38" s="27" t="n"/>
@@ -1683,10 +1685,10 @@
       <c r="I38" s="27" t="n"/>
       <c r="J38" s="57" t="n"/>
     </row>
-    <row r="39" ht="20" customHeight="1" s="6">
+    <row r="39" ht="22" customHeight="1" s="6">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>彼は京都を4回訪れたことがあります。</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B39" s="27" t="n"/>
@@ -1699,10 +1701,10 @@
       <c r="I39" s="27" t="n"/>
       <c r="J39" s="57" t="n"/>
     </row>
-    <row r="40" ht="26" customHeight="1" s="6">
+    <row r="40" ht="22" customHeight="1" s="6">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B40" s="27" t="n"/>
@@ -1715,10 +1717,10 @@
       <c r="I40" s="27" t="n"/>
       <c r="J40" s="57" t="n"/>
     </row>
-    <row r="41" ht="20" customHeight="1" s="6">
+    <row r="41" ht="18" customHeight="1" s="6">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>彼はまだ一度も京都を訪れたことがありません。</t>
+          <t>あなたは京都を訪れたことがありますか。</t>
         </is>
       </c>
       <c r="B41" s="27" t="n"/>
@@ -1731,10 +1733,10 @@
       <c r="I41" s="27" t="n"/>
       <c r="J41" s="57" t="n"/>
     </row>
-    <row r="42" ht="26" customHeight="1" s="6">
+    <row r="42" ht="22" customHeight="1" s="6">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（疑問文）：</t>
         </is>
       </c>
       <c r="B42" s="27" t="n"/>
@@ -1747,10 +1749,10 @@
       <c r="I42" s="27" t="n"/>
       <c r="J42" s="57" t="n"/>
     </row>
-    <row r="43" ht="26" customHeight="1" s="6">
+    <row r="43" ht="18" customHeight="1" s="6">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>はい、あります。</t>
         </is>
       </c>
       <c r="B43" s="27" t="n"/>
@@ -1763,10 +1765,10 @@
       <c r="I43" s="27" t="n"/>
       <c r="J43" s="57" t="n"/>
     </row>
-    <row r="44" ht="26" customHeight="1" s="6">
+    <row r="44" ht="22" customHeight="1" s="6">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（返答）：</t>
         </is>
       </c>
       <c r="B44" s="27" t="n"/>
@@ -1779,10 +1781,10 @@
       <c r="I44" s="27" t="n"/>
       <c r="J44" s="57" t="n"/>
     </row>
-    <row r="45" ht="20" customHeight="1" s="6">
+    <row r="45" ht="18" customHeight="1" s="6">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>彼は京都を何回訪れたことがありますか。</t>
+          <t>いいえ、ありません。</t>
         </is>
       </c>
       <c r="B45" s="27" t="n"/>
@@ -1795,10 +1797,10 @@
       <c r="I45" s="27" t="n"/>
       <c r="J45" s="57" t="n"/>
     </row>
-    <row r="46" ht="26" customHeight="1" s="6">
+    <row r="46" ht="22" customHeight="1" s="6">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>回答（疑問文）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B46" s="27" t="n"/>
@@ -1811,10 +1813,10 @@
       <c r="I46" s="27" t="n"/>
       <c r="J46" s="57" t="n"/>
     </row>
-    <row r="47" ht="20" customHeight="1" s="6">
+    <row r="47" ht="22" customHeight="1" s="6">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>5回訪れたことがあります。</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B47" s="27" t="n"/>
@@ -1827,10 +1829,10 @@
       <c r="I47" s="27" t="n"/>
       <c r="J47" s="57" t="n"/>
     </row>
-    <row r="48" ht="26" customHeight="1" s="6">
+    <row r="48" ht="22" customHeight="1" s="6">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>回答（返答）：</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B48" s="27" t="n"/>
@@ -1843,26 +1845,26 @@
       <c r="I48" s="27" t="n"/>
       <c r="J48" s="57" t="n"/>
     </row>
-    <row r="49" ht="20" customHeight="1" s="6">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>一度も訪れたことがありません。</t>
-        </is>
-      </c>
-      <c r="B49" s="27" t="n"/>
-      <c r="C49" s="27" t="n"/>
-      <c r="D49" s="27" t="n"/>
-      <c r="E49" s="27" t="n"/>
-      <c r="F49" s="27" t="n"/>
-      <c r="G49" s="27" t="n"/>
-      <c r="H49" s="27" t="n"/>
-      <c r="I49" s="27" t="n"/>
-      <c r="J49" s="57" t="n"/>
-    </row>
-    <row r="50" ht="26" customHeight="1" s="6">
+    <row r="49" ht="18" customHeight="1" s="6">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>【回数】何回訪れたことがあるか</t>
+        </is>
+      </c>
+      <c r="B49" s="25" t="n"/>
+      <c r="C49" s="25" t="n"/>
+      <c r="D49" s="25" t="n"/>
+      <c r="E49" s="25" t="n"/>
+      <c r="F49" s="25" t="n"/>
+      <c r="G49" s="25" t="n"/>
+      <c r="H49" s="25" t="n"/>
+      <c r="I49" s="25" t="n"/>
+      <c r="J49" s="56" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1" s="6">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>あなたは京都を4回訪れたことがあります。</t>
         </is>
       </c>
       <c r="B50" s="27" t="n"/>
@@ -1875,10 +1877,10 @@
       <c r="I50" s="27" t="n"/>
       <c r="J50" s="57" t="n"/>
     </row>
-    <row r="51" ht="26" customHeight="1" s="6">
+    <row r="51" ht="22" customHeight="1" s="6">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B51" s="27" t="n"/>
@@ -1891,10 +1893,10 @@
       <c r="I51" s="27" t="n"/>
       <c r="J51" s="57" t="n"/>
     </row>
-    <row r="52" ht="26" customHeight="1" s="6">
+    <row r="52" ht="18" customHeight="1" s="6">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>あなたは京都を何回訪れたことがありますか。</t>
         </is>
       </c>
       <c r="B52" s="27" t="n"/>
@@ -1907,8 +1909,12 @@
       <c r="I52" s="27" t="n"/>
       <c r="J52" s="57" t="n"/>
     </row>
-    <row r="53" ht="6" customHeight="1" s="6">
-      <c r="A53" s="11" t="n"/>
+    <row r="53" ht="22" customHeight="1" s="6">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>回答（疑問文）：</t>
+        </is>
+      </c>
       <c r="B53" s="27" t="n"/>
       <c r="C53" s="27" t="n"/>
       <c r="D53" s="27" t="n"/>
@@ -1920,27 +1926,25 @@
       <c r="J53" s="57" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1" s="6">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>4．主語は「彼女」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B54" s="25" t="n"/>
-      <c r="C54" s="25" t="n"/>
-      <c r="D54" s="25" t="n"/>
-      <c r="E54" s="25" t="n"/>
-      <c r="F54" s="25" t="n"/>
-      <c r="G54" s="25" t="n"/>
-      <c r="H54" s="25" t="n"/>
-      <c r="I54" s="25" t="n"/>
-      <c r="J54" s="56" t="n"/>
-    </row>
-    <row r="55" ht="60" customHeight="1" s="6">
-      <c r="A55" s="55" t="inlineStr">
-        <is>
-          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
-※回数は four times / five times のように表します。
-※否定では never または not ... before を使います。</t>
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>5回訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B54" s="27" t="n"/>
+      <c r="C54" s="27" t="n"/>
+      <c r="D54" s="27" t="n"/>
+      <c r="E54" s="27" t="n"/>
+      <c r="F54" s="27" t="n"/>
+      <c r="G54" s="27" t="n"/>
+      <c r="H54" s="27" t="n"/>
+      <c r="I54" s="27" t="n"/>
+      <c r="J54" s="57" t="n"/>
+    </row>
+    <row r="55" ht="22" customHeight="1" s="6">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>回答（返答）：</t>
         </is>
       </c>
       <c r="B55" s="27" t="n"/>
@@ -1953,10 +1957,10 @@
       <c r="I55" s="27" t="n"/>
       <c r="J55" s="57" t="n"/>
     </row>
-    <row r="56" ht="20" customHeight="1" s="6">
+    <row r="56" ht="18" customHeight="1" s="6">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>彼女は京都を4回訪れたことがあります。</t>
+          <t>一度も訪れたことがありません。</t>
         </is>
       </c>
       <c r="B56" s="27" t="n"/>
@@ -1969,7 +1973,7 @@
       <c r="I56" s="27" t="n"/>
       <c r="J56" s="57" t="n"/>
     </row>
-    <row r="57" ht="26" customHeight="1" s="6">
+    <row r="57" ht="22" customHeight="1" s="6">
       <c r="A57" s="11" t="inlineStr">
         <is>
           <t>回答（基本形）：</t>
@@ -1985,10 +1989,10 @@
       <c r="I57" s="27" t="n"/>
       <c r="J57" s="57" t="n"/>
     </row>
-    <row r="58" ht="20" customHeight="1" s="6">
+    <row r="58" ht="22" customHeight="1" s="6">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>彼女はまだ一度も京都を訪れたことがありません。</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B58" s="27" t="n"/>
@@ -2001,10 +2005,10 @@
       <c r="I58" s="27" t="n"/>
       <c r="J58" s="57" t="n"/>
     </row>
-    <row r="59" ht="26" customHeight="1" s="6">
+    <row r="59" ht="22" customHeight="1" s="6">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B59" s="27" t="n"/>
@@ -2017,12 +2021,8 @@
       <c r="I59" s="27" t="n"/>
       <c r="J59" s="57" t="n"/>
     </row>
-    <row r="60" ht="26" customHeight="1" s="6">
-      <c r="A60" s="11" t="inlineStr">
-        <is>
-          <t>回答（言いかえ）：</t>
-        </is>
-      </c>
+    <row r="60" ht="6" customHeight="1" s="6">
+      <c r="A60" s="11" t="n"/>
       <c r="B60" s="27" t="n"/>
       <c r="C60" s="27" t="n"/>
       <c r="D60" s="27" t="n"/>
@@ -2033,26 +2033,28 @@
       <c r="I60" s="27" t="n"/>
       <c r="J60" s="57" t="n"/>
     </row>
-    <row r="61" ht="26" customHeight="1" s="6">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t>回答（短縮形）：</t>
-        </is>
-      </c>
-      <c r="B61" s="27" t="n"/>
-      <c r="C61" s="27" t="n"/>
-      <c r="D61" s="27" t="n"/>
-      <c r="E61" s="27" t="n"/>
-      <c r="F61" s="27" t="n"/>
-      <c r="G61" s="27" t="n"/>
-      <c r="H61" s="27" t="n"/>
-      <c r="I61" s="27" t="n"/>
-      <c r="J61" s="57" t="n"/>
-    </row>
-    <row r="62" ht="20" customHeight="1" s="6">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t>彼女は京都を何回訪れたことがありますか。</t>
+    <row r="61" ht="18" customHeight="1" s="6">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>3．主語は「彼」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B61" s="25" t="n"/>
+      <c r="C61" s="25" t="n"/>
+      <c r="D61" s="25" t="n"/>
+      <c r="E61" s="25" t="n"/>
+      <c r="F61" s="25" t="n"/>
+      <c r="G61" s="25" t="n"/>
+      <c r="H61" s="25" t="n"/>
+      <c r="I61" s="25" t="n"/>
+      <c r="J61" s="56" t="n"/>
+    </row>
+    <row r="62" ht="60" customHeight="1" s="6">
+      <c r="A62" s="55" t="inlineStr">
+        <is>
+          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
+※疑問文では ever、否定では never または not ... before を使います。
+※回数は four times / five times のように表します。</t>
         </is>
       </c>
       <c r="B62" s="27" t="n"/>
@@ -2065,26 +2067,26 @@
       <c r="I62" s="27" t="n"/>
       <c r="J62" s="57" t="n"/>
     </row>
-    <row r="63" ht="26" customHeight="1" s="6">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t>回答（疑問文）：</t>
-        </is>
-      </c>
-      <c r="B63" s="27" t="n"/>
-      <c r="C63" s="27" t="n"/>
-      <c r="D63" s="27" t="n"/>
-      <c r="E63" s="27" t="n"/>
-      <c r="F63" s="27" t="n"/>
-      <c r="G63" s="27" t="n"/>
-      <c r="H63" s="27" t="n"/>
-      <c r="I63" s="27" t="n"/>
-      <c r="J63" s="57" t="n"/>
-    </row>
-    <row r="64" ht="20" customHeight="1" s="6">
+    <row r="63" ht="18" customHeight="1" s="6">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>【基本】訪れたことがある・ない</t>
+        </is>
+      </c>
+      <c r="B63" s="25" t="n"/>
+      <c r="C63" s="25" t="n"/>
+      <c r="D63" s="25" t="n"/>
+      <c r="E63" s="25" t="n"/>
+      <c r="F63" s="25" t="n"/>
+      <c r="G63" s="25" t="n"/>
+      <c r="H63" s="25" t="n"/>
+      <c r="I63" s="25" t="n"/>
+      <c r="J63" s="56" t="n"/>
+    </row>
+    <row r="64" ht="18" customHeight="1" s="6">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>5回訪れたことがあります。</t>
+          <t>彼は京都を訪れたことがあります。</t>
         </is>
       </c>
       <c r="B64" s="27" t="n"/>
@@ -2097,10 +2099,10 @@
       <c r="I64" s="27" t="n"/>
       <c r="J64" s="57" t="n"/>
     </row>
-    <row r="65" ht="26" customHeight="1" s="6">
+    <row r="65" ht="22" customHeight="1" s="6">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>回答（返答）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B65" s="27" t="n"/>
@@ -2113,10 +2115,10 @@
       <c r="I65" s="27" t="n"/>
       <c r="J65" s="57" t="n"/>
     </row>
-    <row r="66" ht="20" customHeight="1" s="6">
+    <row r="66" ht="18" customHeight="1" s="6">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>一度も訪れたことがありません。</t>
+          <t>彼はまだ一度も京都を訪れたことがありません。</t>
         </is>
       </c>
       <c r="B66" s="27" t="n"/>
@@ -2129,7 +2131,7 @@
       <c r="I66" s="27" t="n"/>
       <c r="J66" s="57" t="n"/>
     </row>
-    <row r="67" ht="26" customHeight="1" s="6">
+    <row r="67" ht="22" customHeight="1" s="6">
       <c r="A67" s="11" t="inlineStr">
         <is>
           <t>回答（基本形）：</t>
@@ -2145,7 +2147,7 @@
       <c r="I67" s="27" t="n"/>
       <c r="J67" s="57" t="n"/>
     </row>
-    <row r="68" ht="26" customHeight="1" s="6">
+    <row r="68" ht="22" customHeight="1" s="6">
       <c r="A68" s="11" t="inlineStr">
         <is>
           <t>回答（言いかえ）：</t>
@@ -2161,7 +2163,7 @@
       <c r="I68" s="27" t="n"/>
       <c r="J68" s="57" t="n"/>
     </row>
-    <row r="69" ht="26" customHeight="1" s="6">
+    <row r="69" ht="22" customHeight="1" s="6">
       <c r="A69" s="11" t="inlineStr">
         <is>
           <t>回答（短縮形）：</t>
@@ -2177,8 +2179,12 @@
       <c r="I69" s="27" t="n"/>
       <c r="J69" s="57" t="n"/>
     </row>
-    <row r="70" ht="6" customHeight="1" s="6">
-      <c r="A70" s="11" t="n"/>
+    <row r="70" ht="18" customHeight="1" s="6">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>彼は京都を訪れたことがありますか。</t>
+        </is>
+      </c>
       <c r="B70" s="27" t="n"/>
       <c r="C70" s="27" t="n"/>
       <c r="D70" s="27" t="n"/>
@@ -2189,29 +2195,26 @@
       <c r="I70" s="27" t="n"/>
       <c r="J70" s="57" t="n"/>
     </row>
-    <row r="71" ht="18" customHeight="1" s="6">
-      <c r="A71" s="9" t="inlineStr">
-        <is>
-          <t>5．主語は「私たち」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B71" s="25" t="n"/>
-      <c r="C71" s="25" t="n"/>
-      <c r="D71" s="25" t="n"/>
-      <c r="E71" s="25" t="n"/>
-      <c r="F71" s="25" t="n"/>
-      <c r="G71" s="25" t="n"/>
-      <c r="H71" s="25" t="n"/>
-      <c r="I71" s="25" t="n"/>
-      <c r="J71" s="56" t="n"/>
-    </row>
-    <row r="72" ht="60" customHeight="1" s="6">
-      <c r="A72" s="55" t="inlineStr">
-        <is>
-          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
-※回数は four times / five times のように表します。
-※否定では never または not ... before を使います。
-※相手が答える形なので、返答では I / we ではなく you を使います。</t>
+    <row r="71" ht="22" customHeight="1" s="6">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>回答（疑問文）：</t>
+        </is>
+      </c>
+      <c r="B71" s="27" t="n"/>
+      <c r="C71" s="27" t="n"/>
+      <c r="D71" s="27" t="n"/>
+      <c r="E71" s="27" t="n"/>
+      <c r="F71" s="27" t="n"/>
+      <c r="G71" s="27" t="n"/>
+      <c r="H71" s="27" t="n"/>
+      <c r="I71" s="27" t="n"/>
+      <c r="J71" s="57" t="n"/>
+    </row>
+    <row r="72" ht="18" customHeight="1" s="6">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>はい、あります。</t>
         </is>
       </c>
       <c r="B72" s="27" t="n"/>
@@ -2224,10 +2227,10 @@
       <c r="I72" s="27" t="n"/>
       <c r="J72" s="57" t="n"/>
     </row>
-    <row r="73" ht="20" customHeight="1" s="6">
+    <row r="73" ht="22" customHeight="1" s="6">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>私たちは京都を4回訪れたことがあります。</t>
+          <t>回答（返答）：</t>
         </is>
       </c>
       <c r="B73" s="27" t="n"/>
@@ -2240,10 +2243,10 @@
       <c r="I73" s="27" t="n"/>
       <c r="J73" s="57" t="n"/>
     </row>
-    <row r="74" ht="26" customHeight="1" s="6">
+    <row r="74" ht="18" customHeight="1" s="6">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>いいえ、ありません。</t>
         </is>
       </c>
       <c r="B74" s="27" t="n"/>
@@ -2256,10 +2259,10 @@
       <c r="I74" s="27" t="n"/>
       <c r="J74" s="57" t="n"/>
     </row>
-    <row r="75" ht="20" customHeight="1" s="6">
+    <row r="75" ht="22" customHeight="1" s="6">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>私たちはまだ一度も京都を訪れたことがありません。</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B75" s="27" t="n"/>
@@ -2272,10 +2275,10 @@
       <c r="I75" s="27" t="n"/>
       <c r="J75" s="57" t="n"/>
     </row>
-    <row r="76" ht="26" customHeight="1" s="6">
+    <row r="76" ht="22" customHeight="1" s="6">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B76" s="27" t="n"/>
@@ -2288,10 +2291,10 @@
       <c r="I76" s="27" t="n"/>
       <c r="J76" s="57" t="n"/>
     </row>
-    <row r="77" ht="26" customHeight="1" s="6">
+    <row r="77" ht="22" customHeight="1" s="6">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B77" s="27" t="n"/>
@@ -2304,26 +2307,26 @@
       <c r="I77" s="27" t="n"/>
       <c r="J77" s="57" t="n"/>
     </row>
-    <row r="78" ht="26" customHeight="1" s="6">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t>回答（短縮形）：</t>
-        </is>
-      </c>
-      <c r="B78" s="27" t="n"/>
-      <c r="C78" s="27" t="n"/>
-      <c r="D78" s="27" t="n"/>
-      <c r="E78" s="27" t="n"/>
-      <c r="F78" s="27" t="n"/>
-      <c r="G78" s="27" t="n"/>
-      <c r="H78" s="27" t="n"/>
-      <c r="I78" s="27" t="n"/>
-      <c r="J78" s="57" t="n"/>
-    </row>
-    <row r="79" ht="20" customHeight="1" s="6">
+    <row r="78" ht="18" customHeight="1" s="6">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>【回数】何回訪れたことがあるか</t>
+        </is>
+      </c>
+      <c r="B78" s="25" t="n"/>
+      <c r="C78" s="25" t="n"/>
+      <c r="D78" s="25" t="n"/>
+      <c r="E78" s="25" t="n"/>
+      <c r="F78" s="25" t="n"/>
+      <c r="G78" s="25" t="n"/>
+      <c r="H78" s="25" t="n"/>
+      <c r="I78" s="25" t="n"/>
+      <c r="J78" s="56" t="n"/>
+    </row>
+    <row r="79" ht="18" customHeight="1" s="6">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>私たちは京都を何回訪れたことがありますか。</t>
+          <t>彼は京都を4回訪れたことがあります。</t>
         </is>
       </c>
       <c r="B79" s="27" t="n"/>
@@ -2336,10 +2339,10 @@
       <c r="I79" s="27" t="n"/>
       <c r="J79" s="57" t="n"/>
     </row>
-    <row r="80" ht="26" customHeight="1" s="6">
+    <row r="80" ht="22" customHeight="1" s="6">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>回答（疑問文）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B80" s="27" t="n"/>
@@ -2352,10 +2355,10 @@
       <c r="I80" s="27" t="n"/>
       <c r="J80" s="57" t="n"/>
     </row>
-    <row r="81" ht="20" customHeight="1" s="6">
+    <row r="81" ht="18" customHeight="1" s="6">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>5回訪れたことがあります。</t>
+          <t>彼は京都を何回訪れたことがありますか。</t>
         </is>
       </c>
       <c r="B81" s="27" t="n"/>
@@ -2368,10 +2371,10 @@
       <c r="I81" s="27" t="n"/>
       <c r="J81" s="57" t="n"/>
     </row>
-    <row r="82" ht="26" customHeight="1" s="6">
+    <row r="82" ht="22" customHeight="1" s="6">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>回答（返答）：</t>
+          <t>回答（疑問文）：</t>
         </is>
       </c>
       <c r="B82" s="27" t="n"/>
@@ -2384,10 +2387,10 @@
       <c r="I82" s="27" t="n"/>
       <c r="J82" s="57" t="n"/>
     </row>
-    <row r="83" ht="20" customHeight="1" s="6">
+    <row r="83" ht="18" customHeight="1" s="6">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>一度も訪れたことがありません。</t>
+          <t>5回訪れたことがあります。</t>
         </is>
       </c>
       <c r="B83" s="27" t="n"/>
@@ -2400,10 +2403,10 @@
       <c r="I83" s="27" t="n"/>
       <c r="J83" s="57" t="n"/>
     </row>
-    <row r="84" ht="26" customHeight="1" s="6">
+    <row r="84" ht="22" customHeight="1" s="6">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（返答）：</t>
         </is>
       </c>
       <c r="B84" s="27" t="n"/>
@@ -2416,10 +2419,10 @@
       <c r="I84" s="27" t="n"/>
       <c r="J84" s="57" t="n"/>
     </row>
-    <row r="85" ht="26" customHeight="1" s="6">
+    <row r="85" ht="18" customHeight="1" s="6">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>一度も訪れたことがありません。</t>
         </is>
       </c>
       <c r="B85" s="27" t="n"/>
@@ -2432,10 +2435,10 @@
       <c r="I85" s="27" t="n"/>
       <c r="J85" s="57" t="n"/>
     </row>
-    <row r="86" ht="26" customHeight="1" s="6">
+    <row r="86" ht="22" customHeight="1" s="6">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B86" s="27" t="n"/>
@@ -2448,8 +2451,12 @@
       <c r="I86" s="27" t="n"/>
       <c r="J86" s="57" t="n"/>
     </row>
-    <row r="87" ht="6" customHeight="1" s="6">
-      <c r="A87" s="11" t="n"/>
+    <row r="87" ht="22" customHeight="1" s="6">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ）：</t>
+        </is>
+      </c>
       <c r="B87" s="27" t="n"/>
       <c r="C87" s="27" t="n"/>
       <c r="D87" s="27" t="n"/>
@@ -2460,30 +2467,24 @@
       <c r="I87" s="27" t="n"/>
       <c r="J87" s="57" t="n"/>
     </row>
-    <row r="88" ht="18" customHeight="1" s="6">
-      <c r="A88" s="9" t="inlineStr">
-        <is>
-          <t>6．主語は「あなたたち」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B88" s="25" t="n"/>
-      <c r="C88" s="25" t="n"/>
-      <c r="D88" s="25" t="n"/>
-      <c r="E88" s="25" t="n"/>
-      <c r="F88" s="25" t="n"/>
-      <c r="G88" s="25" t="n"/>
-      <c r="H88" s="25" t="n"/>
-      <c r="I88" s="25" t="n"/>
-      <c r="J88" s="56" t="n"/>
-    </row>
-    <row r="89" ht="60" customHeight="1" s="6">
-      <c r="A89" s="55" t="inlineStr">
-        <is>
-          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
-※回数は four times / five times のように表します。
-※否定では never または not ... before を使います。</t>
-        </is>
-      </c>
+    <row r="88" ht="22" customHeight="1" s="6">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
+        </is>
+      </c>
+      <c r="B88" s="27" t="n"/>
+      <c r="C88" s="27" t="n"/>
+      <c r="D88" s="27" t="n"/>
+      <c r="E88" s="27" t="n"/>
+      <c r="F88" s="27" t="n"/>
+      <c r="G88" s="27" t="n"/>
+      <c r="H88" s="27" t="n"/>
+      <c r="I88" s="27" t="n"/>
+      <c r="J88" s="57" t="n"/>
+    </row>
+    <row r="89" ht="6" customHeight="1" s="6">
+      <c r="A89" s="11" t="n"/>
       <c r="B89" s="27" t="n"/>
       <c r="C89" s="27" t="n"/>
       <c r="D89" s="27" t="n"/>
@@ -2494,26 +2495,28 @@
       <c r="I89" s="27" t="n"/>
       <c r="J89" s="57" t="n"/>
     </row>
-    <row r="90" ht="20" customHeight="1" s="6">
-      <c r="A90" s="11" t="inlineStr">
-        <is>
-          <t>あなたたちは京都を4回訪れたことがあります。</t>
-        </is>
-      </c>
-      <c r="B90" s="27" t="n"/>
-      <c r="C90" s="27" t="n"/>
-      <c r="D90" s="27" t="n"/>
-      <c r="E90" s="27" t="n"/>
-      <c r="F90" s="27" t="n"/>
-      <c r="G90" s="27" t="n"/>
-      <c r="H90" s="27" t="n"/>
-      <c r="I90" s="27" t="n"/>
-      <c r="J90" s="57" t="n"/>
-    </row>
-    <row r="91" ht="26" customHeight="1" s="6">
-      <c r="A91" s="11" t="inlineStr">
-        <is>
-          <t>回答（基本形）：</t>
+    <row r="90" ht="18" customHeight="1" s="6">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>4．主語は「彼女」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B90" s="25" t="n"/>
+      <c r="C90" s="25" t="n"/>
+      <c r="D90" s="25" t="n"/>
+      <c r="E90" s="25" t="n"/>
+      <c r="F90" s="25" t="n"/>
+      <c r="G90" s="25" t="n"/>
+      <c r="H90" s="25" t="n"/>
+      <c r="I90" s="25" t="n"/>
+      <c r="J90" s="56" t="n"/>
+    </row>
+    <row r="91" ht="60" customHeight="1" s="6">
+      <c r="A91" s="55" t="inlineStr">
+        <is>
+          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
+※疑問文では ever、否定では never または not ... before を使います。
+※回数は four times / five times のように表します。</t>
         </is>
       </c>
       <c r="B91" s="27" t="n"/>
@@ -2526,26 +2529,26 @@
       <c r="I91" s="27" t="n"/>
       <c r="J91" s="57" t="n"/>
     </row>
-    <row r="92" ht="20" customHeight="1" s="6">
-      <c r="A92" s="11" t="inlineStr">
-        <is>
-          <t>あなたたちはまだ一度も京都を訪れたことがありません。</t>
-        </is>
-      </c>
-      <c r="B92" s="27" t="n"/>
-      <c r="C92" s="27" t="n"/>
-      <c r="D92" s="27" t="n"/>
-      <c r="E92" s="27" t="n"/>
-      <c r="F92" s="27" t="n"/>
-      <c r="G92" s="27" t="n"/>
-      <c r="H92" s="27" t="n"/>
-      <c r="I92" s="27" t="n"/>
-      <c r="J92" s="57" t="n"/>
-    </row>
-    <row r="93" ht="26" customHeight="1" s="6">
+    <row r="92" ht="18" customHeight="1" s="6">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>【基本】訪れたことがある・ない</t>
+        </is>
+      </c>
+      <c r="B92" s="25" t="n"/>
+      <c r="C92" s="25" t="n"/>
+      <c r="D92" s="25" t="n"/>
+      <c r="E92" s="25" t="n"/>
+      <c r="F92" s="25" t="n"/>
+      <c r="G92" s="25" t="n"/>
+      <c r="H92" s="25" t="n"/>
+      <c r="I92" s="25" t="n"/>
+      <c r="J92" s="56" t="n"/>
+    </row>
+    <row r="93" ht="18" customHeight="1" s="6">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>彼女は京都を訪れたことがあります。</t>
         </is>
       </c>
       <c r="B93" s="27" t="n"/>
@@ -2558,10 +2561,10 @@
       <c r="I93" s="27" t="n"/>
       <c r="J93" s="57" t="n"/>
     </row>
-    <row r="94" ht="26" customHeight="1" s="6">
+    <row r="94" ht="22" customHeight="1" s="6">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B94" s="27" t="n"/>
@@ -2574,10 +2577,10 @@
       <c r="I94" s="27" t="n"/>
       <c r="J94" s="57" t="n"/>
     </row>
-    <row r="95" ht="26" customHeight="1" s="6">
+    <row r="95" ht="18" customHeight="1" s="6">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>彼女はまだ一度も京都を訪れたことがありません。</t>
         </is>
       </c>
       <c r="B95" s="27" t="n"/>
@@ -2590,10 +2593,10 @@
       <c r="I95" s="27" t="n"/>
       <c r="J95" s="57" t="n"/>
     </row>
-    <row r="96" ht="20" customHeight="1" s="6">
+    <row r="96" ht="22" customHeight="1" s="6">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>あなたたちは京都を何回訪れたことがありますか。</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B96" s="27" t="n"/>
@@ -2606,10 +2609,10 @@
       <c r="I96" s="27" t="n"/>
       <c r="J96" s="57" t="n"/>
     </row>
-    <row r="97" ht="26" customHeight="1" s="6">
+    <row r="97" ht="22" customHeight="1" s="6">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>回答（疑問文）：</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B97" s="27" t="n"/>
@@ -2622,10 +2625,10 @@
       <c r="I97" s="27" t="n"/>
       <c r="J97" s="57" t="n"/>
     </row>
-    <row r="98" ht="20" customHeight="1" s="6">
+    <row r="98" ht="22" customHeight="1" s="6">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>5回訪れたことがあります。</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B98" s="27" t="n"/>
@@ -2638,10 +2641,10 @@
       <c r="I98" s="27" t="n"/>
       <c r="J98" s="57" t="n"/>
     </row>
-    <row r="99" ht="26" customHeight="1" s="6">
+    <row r="99" ht="18" customHeight="1" s="6">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>回答（返答）：</t>
+          <t>彼女は京都を訪れたことがありますか。</t>
         </is>
       </c>
       <c r="B99" s="27" t="n"/>
@@ -2654,10 +2657,10 @@
       <c r="I99" s="27" t="n"/>
       <c r="J99" s="57" t="n"/>
     </row>
-    <row r="100" ht="20" customHeight="1" s="6">
+    <row r="100" ht="22" customHeight="1" s="6">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>一度も訪れたことがありません。</t>
+          <t>回答（疑問文）：</t>
         </is>
       </c>
       <c r="B100" s="27" t="n"/>
@@ -2670,10 +2673,10 @@
       <c r="I100" s="27" t="n"/>
       <c r="J100" s="57" t="n"/>
     </row>
-    <row r="101" ht="26" customHeight="1" s="6">
+    <row r="101" ht="18" customHeight="1" s="6">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>はい、あります。</t>
         </is>
       </c>
       <c r="B101" s="27" t="n"/>
@@ -2686,10 +2689,10 @@
       <c r="I101" s="27" t="n"/>
       <c r="J101" s="57" t="n"/>
     </row>
-    <row r="102" ht="26" customHeight="1" s="6">
+    <row r="102" ht="22" customHeight="1" s="6">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（返答）：</t>
         </is>
       </c>
       <c r="B102" s="27" t="n"/>
@@ -2702,10 +2705,10 @@
       <c r="I102" s="27" t="n"/>
       <c r="J102" s="57" t="n"/>
     </row>
-    <row r="103" ht="26" customHeight="1" s="6">
+    <row r="103" ht="18" customHeight="1" s="6">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>いいえ、ありません。</t>
         </is>
       </c>
       <c r="B103" s="27" t="n"/>
@@ -2718,8 +2721,12 @@
       <c r="I103" s="27" t="n"/>
       <c r="J103" s="57" t="n"/>
     </row>
-    <row r="104" ht="6" customHeight="1" s="6">
-      <c r="A104" s="11" t="n"/>
+    <row r="104" ht="22" customHeight="1" s="6">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
       <c r="B104" s="27" t="n"/>
       <c r="C104" s="27" t="n"/>
       <c r="D104" s="27" t="n"/>
@@ -2730,28 +2737,26 @@
       <c r="I104" s="27" t="n"/>
       <c r="J104" s="57" t="n"/>
     </row>
-    <row r="105" ht="18" customHeight="1" s="6">
-      <c r="A105" s="9" t="inlineStr">
-        <is>
-          <t>7．主語は「彼ら」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B105" s="25" t="n"/>
-      <c r="C105" s="25" t="n"/>
-      <c r="D105" s="25" t="n"/>
-      <c r="E105" s="25" t="n"/>
-      <c r="F105" s="25" t="n"/>
-      <c r="G105" s="25" t="n"/>
-      <c r="H105" s="25" t="n"/>
-      <c r="I105" s="25" t="n"/>
-      <c r="J105" s="56" t="n"/>
-    </row>
-    <row r="106" ht="60" customHeight="1" s="6">
-      <c r="A106" s="55" t="inlineStr">
-        <is>
-          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
-※回数は four times / five times のように表します。
-※否定では never または not ... before を使います。</t>
+    <row r="105" ht="22" customHeight="1" s="6">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ）：</t>
+        </is>
+      </c>
+      <c r="B105" s="27" t="n"/>
+      <c r="C105" s="27" t="n"/>
+      <c r="D105" s="27" t="n"/>
+      <c r="E105" s="27" t="n"/>
+      <c r="F105" s="27" t="n"/>
+      <c r="G105" s="27" t="n"/>
+      <c r="H105" s="27" t="n"/>
+      <c r="I105" s="27" t="n"/>
+      <c r="J105" s="57" t="n"/>
+    </row>
+    <row r="106" ht="22" customHeight="1" s="6">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B106" s="27" t="n"/>
@@ -2764,26 +2769,26 @@
       <c r="I106" s="27" t="n"/>
       <c r="J106" s="57" t="n"/>
     </row>
-    <row r="107" ht="20" customHeight="1" s="6">
-      <c r="A107" s="11" t="inlineStr">
-        <is>
-          <t>彼らは京都を4回訪れたことがあります。</t>
-        </is>
-      </c>
-      <c r="B107" s="27" t="n"/>
-      <c r="C107" s="27" t="n"/>
-      <c r="D107" s="27" t="n"/>
-      <c r="E107" s="27" t="n"/>
-      <c r="F107" s="27" t="n"/>
-      <c r="G107" s="27" t="n"/>
-      <c r="H107" s="27" t="n"/>
-      <c r="I107" s="27" t="n"/>
-      <c r="J107" s="57" t="n"/>
-    </row>
-    <row r="108" ht="26" customHeight="1" s="6">
+    <row r="107" ht="18" customHeight="1" s="6">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>【回数】何回訪れたことがあるか</t>
+        </is>
+      </c>
+      <c r="B107" s="25" t="n"/>
+      <c r="C107" s="25" t="n"/>
+      <c r="D107" s="25" t="n"/>
+      <c r="E107" s="25" t="n"/>
+      <c r="F107" s="25" t="n"/>
+      <c r="G107" s="25" t="n"/>
+      <c r="H107" s="25" t="n"/>
+      <c r="I107" s="25" t="n"/>
+      <c r="J107" s="56" t="n"/>
+    </row>
+    <row r="108" ht="18" customHeight="1" s="6">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>彼女は京都を4回訪れたことがあります。</t>
         </is>
       </c>
       <c r="B108" s="27" t="n"/>
@@ -2796,10 +2801,10 @@
       <c r="I108" s="27" t="n"/>
       <c r="J108" s="57" t="n"/>
     </row>
-    <row r="109" ht="20" customHeight="1" s="6">
+    <row r="109" ht="22" customHeight="1" s="6">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>彼らはまだ一度も京都を訪れたことがありません。</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B109" s="27" t="n"/>
@@ -2812,10 +2817,10 @@
       <c r="I109" s="27" t="n"/>
       <c r="J109" s="57" t="n"/>
     </row>
-    <row r="110" ht="26" customHeight="1" s="6">
+    <row r="110" ht="18" customHeight="1" s="6">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>彼女は京都を何回訪れたことがありますか。</t>
         </is>
       </c>
       <c r="B110" s="27" t="n"/>
@@ -2828,10 +2833,10 @@
       <c r="I110" s="27" t="n"/>
       <c r="J110" s="57" t="n"/>
     </row>
-    <row r="111" ht="26" customHeight="1" s="6">
+    <row r="111" ht="22" customHeight="1" s="6">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（疑問文）：</t>
         </is>
       </c>
       <c r="B111" s="27" t="n"/>
@@ -2844,10 +2849,10 @@
       <c r="I111" s="27" t="n"/>
       <c r="J111" s="57" t="n"/>
     </row>
-    <row r="112" ht="26" customHeight="1" s="6">
+    <row r="112" ht="18" customHeight="1" s="6">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>5回訪れたことがあります。</t>
         </is>
       </c>
       <c r="B112" s="27" t="n"/>
@@ -2860,10 +2865,10 @@
       <c r="I112" s="27" t="n"/>
       <c r="J112" s="57" t="n"/>
     </row>
-    <row r="113" ht="20" customHeight="1" s="6">
+    <row r="113" ht="22" customHeight="1" s="6">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>彼らは京都を何回訪れたことがありますか。</t>
+          <t>回答（返答）：</t>
         </is>
       </c>
       <c r="B113" s="27" t="n"/>
@@ -2876,10 +2881,10 @@
       <c r="I113" s="27" t="n"/>
       <c r="J113" s="57" t="n"/>
     </row>
-    <row r="114" ht="26" customHeight="1" s="6">
+    <row r="114" ht="18" customHeight="1" s="6">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>回答（疑問文）：</t>
+          <t>一度も訪れたことがありません。</t>
         </is>
       </c>
       <c r="B114" s="27" t="n"/>
@@ -2892,10 +2897,10 @@
       <c r="I114" s="27" t="n"/>
       <c r="J114" s="57" t="n"/>
     </row>
-    <row r="115" ht="20" customHeight="1" s="6">
+    <row r="115" ht="22" customHeight="1" s="6">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>5回訪れたことがあります。</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B115" s="27" t="n"/>
@@ -2908,10 +2913,10 @@
       <c r="I115" s="27" t="n"/>
       <c r="J115" s="57" t="n"/>
     </row>
-    <row r="116" ht="26" customHeight="1" s="6">
+    <row r="116" ht="22" customHeight="1" s="6">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>回答（返答）：</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B116" s="27" t="n"/>
@@ -2924,10 +2929,10 @@
       <c r="I116" s="27" t="n"/>
       <c r="J116" s="57" t="n"/>
     </row>
-    <row r="117" ht="20" customHeight="1" s="6">
+    <row r="117" ht="22" customHeight="1" s="6">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>一度も訪れたことがありません。</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B117" s="27" t="n"/>
@@ -2940,12 +2945,8 @@
       <c r="I117" s="27" t="n"/>
       <c r="J117" s="57" t="n"/>
     </row>
-    <row r="118" ht="26" customHeight="1" s="6">
-      <c r="A118" s="11" t="inlineStr">
-        <is>
-          <t>回答（基本形）：</t>
-        </is>
-      </c>
+    <row r="118" ht="6" customHeight="1" s="6">
+      <c r="A118" s="11" t="n"/>
       <c r="B118" s="27" t="n"/>
       <c r="C118" s="27" t="n"/>
       <c r="D118" s="27" t="n"/>
@@ -2956,26 +2957,29 @@
       <c r="I118" s="27" t="n"/>
       <c r="J118" s="57" t="n"/>
     </row>
-    <row r="119" ht="26" customHeight="1" s="6">
-      <c r="A119" s="11" t="inlineStr">
-        <is>
-          <t>回答（言いかえ）：</t>
-        </is>
-      </c>
-      <c r="B119" s="27" t="n"/>
-      <c r="C119" s="27" t="n"/>
-      <c r="D119" s="27" t="n"/>
-      <c r="E119" s="27" t="n"/>
-      <c r="F119" s="27" t="n"/>
-      <c r="G119" s="27" t="n"/>
-      <c r="H119" s="27" t="n"/>
-      <c r="I119" s="27" t="n"/>
-      <c r="J119" s="57" t="n"/>
-    </row>
-    <row r="120" ht="26" customHeight="1" s="6">
-      <c r="A120" s="11" t="inlineStr">
-        <is>
-          <t>回答（短縮形）：</t>
+    <row r="119" ht="18" customHeight="1" s="6">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>5．主語は「私たち」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B119" s="25" t="n"/>
+      <c r="C119" s="25" t="n"/>
+      <c r="D119" s="25" t="n"/>
+      <c r="E119" s="25" t="n"/>
+      <c r="F119" s="25" t="n"/>
+      <c r="G119" s="25" t="n"/>
+      <c r="H119" s="25" t="n"/>
+      <c r="I119" s="25" t="n"/>
+      <c r="J119" s="56" t="n"/>
+    </row>
+    <row r="120" ht="60" customHeight="1" s="6">
+      <c r="A120" s="55" t="inlineStr">
+        <is>
+          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
+※疑問文では ever、否定では never または not ... before を使います。
+※回数は four times / five times のように表します。
+※相手が答える形なので、返答では I / we ではなく you を使います。</t>
         </is>
       </c>
       <c r="B120" s="27" t="n"/>
@@ -2988,40 +2992,42 @@
       <c r="I120" s="27" t="n"/>
       <c r="J120" s="57" t="n"/>
     </row>
-    <row r="121" ht="6" customHeight="1" s="6">
-      <c r="A121" s="11" t="n"/>
-      <c r="B121" s="27" t="n"/>
-      <c r="C121" s="27" t="n"/>
-      <c r="D121" s="27" t="n"/>
-      <c r="E121" s="27" t="n"/>
-      <c r="F121" s="27" t="n"/>
-      <c r="G121" s="27" t="n"/>
-      <c r="H121" s="27" t="n"/>
-      <c r="I121" s="27" t="n"/>
-      <c r="J121" s="57" t="n"/>
+    <row r="121" ht="18" customHeight="1" s="6">
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>【基本】訪れたことがある・ない</t>
+        </is>
+      </c>
+      <c r="B121" s="25" t="n"/>
+      <c r="C121" s="25" t="n"/>
+      <c r="D121" s="25" t="n"/>
+      <c r="E121" s="25" t="n"/>
+      <c r="F121" s="25" t="n"/>
+      <c r="G121" s="25" t="n"/>
+      <c r="H121" s="25" t="n"/>
+      <c r="I121" s="25" t="n"/>
+      <c r="J121" s="56" t="n"/>
     </row>
     <row r="122" ht="18" customHeight="1" s="6">
-      <c r="A122" s="9" t="inlineStr">
-        <is>
-          <t>8．主語は「リョウタロウ」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B122" s="25" t="n"/>
-      <c r="C122" s="25" t="n"/>
-      <c r="D122" s="25" t="n"/>
-      <c r="E122" s="25" t="n"/>
-      <c r="F122" s="25" t="n"/>
-      <c r="G122" s="25" t="n"/>
-      <c r="H122" s="25" t="n"/>
-      <c r="I122" s="25" t="n"/>
-      <c r="J122" s="56" t="n"/>
-    </row>
-    <row r="123" ht="60" customHeight="1" s="6">
-      <c r="A123" s="55" t="inlineStr">
-        <is>
-          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
-※回数は four times / five times のように表します。
-※否定では never または not ... before を使います。</t>
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>私たちは京都を訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B122" s="27" t="n"/>
+      <c r="C122" s="27" t="n"/>
+      <c r="D122" s="27" t="n"/>
+      <c r="E122" s="27" t="n"/>
+      <c r="F122" s="27" t="n"/>
+      <c r="G122" s="27" t="n"/>
+      <c r="H122" s="27" t="n"/>
+      <c r="I122" s="27" t="n"/>
+      <c r="J122" s="57" t="n"/>
+    </row>
+    <row r="123" ht="22" customHeight="1" s="6">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B123" s="27" t="n"/>
@@ -3034,10 +3040,10 @@
       <c r="I123" s="27" t="n"/>
       <c r="J123" s="57" t="n"/>
     </row>
-    <row r="124" ht="20" customHeight="1" s="6">
+    <row r="124" ht="18" customHeight="1" s="6">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>リョウタロウは京都を4回訪れたことがあります。</t>
+          <t>私たちはまだ一度も京都を訪れたことがありません。</t>
         </is>
       </c>
       <c r="B124" s="27" t="n"/>
@@ -3050,7 +3056,7 @@
       <c r="I124" s="27" t="n"/>
       <c r="J124" s="57" t="n"/>
     </row>
-    <row r="125" ht="26" customHeight="1" s="6">
+    <row r="125" ht="22" customHeight="1" s="6">
       <c r="A125" s="11" t="inlineStr">
         <is>
           <t>回答（基本形）：</t>
@@ -3066,10 +3072,10 @@
       <c r="I125" s="27" t="n"/>
       <c r="J125" s="57" t="n"/>
     </row>
-    <row r="126" ht="20" customHeight="1" s="6">
+    <row r="126" ht="22" customHeight="1" s="6">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>リョウタロウはまだ一度も京都を訪れたことがありません。</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B126" s="27" t="n"/>
@@ -3082,10 +3088,10 @@
       <c r="I126" s="27" t="n"/>
       <c r="J126" s="57" t="n"/>
     </row>
-    <row r="127" ht="26" customHeight="1" s="6">
+    <row r="127" ht="22" customHeight="1" s="6">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B127" s="27" t="n"/>
@@ -3098,10 +3104,10 @@
       <c r="I127" s="27" t="n"/>
       <c r="J127" s="57" t="n"/>
     </row>
-    <row r="128" ht="26" customHeight="1" s="6">
+    <row r="128" ht="18" customHeight="1" s="6">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>私たちは京都を訪れたことがありますか。</t>
         </is>
       </c>
       <c r="B128" s="27" t="n"/>
@@ -3114,10 +3120,10 @@
       <c r="I128" s="27" t="n"/>
       <c r="J128" s="57" t="n"/>
     </row>
-    <row r="129" ht="26" customHeight="1" s="6">
+    <row r="129" ht="22" customHeight="1" s="6">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（疑問文）：</t>
         </is>
       </c>
       <c r="B129" s="27" t="n"/>
@@ -3130,10 +3136,10 @@
       <c r="I129" s="27" t="n"/>
       <c r="J129" s="57" t="n"/>
     </row>
-    <row r="130" ht="20" customHeight="1" s="6">
+    <row r="130" ht="18" customHeight="1" s="6">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>リョウタロウは京都を何回訪れたことがありますか。</t>
+          <t>はい、あります。</t>
         </is>
       </c>
       <c r="B130" s="27" t="n"/>
@@ -3146,10 +3152,10 @@
       <c r="I130" s="27" t="n"/>
       <c r="J130" s="57" t="n"/>
     </row>
-    <row r="131" ht="26" customHeight="1" s="6">
+    <row r="131" ht="22" customHeight="1" s="6">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>回答（疑問文）：</t>
+          <t>回答（返答）：</t>
         </is>
       </c>
       <c r="B131" s="27" t="n"/>
@@ -3162,10 +3168,10 @@
       <c r="I131" s="27" t="n"/>
       <c r="J131" s="57" t="n"/>
     </row>
-    <row r="132" ht="20" customHeight="1" s="6">
+    <row r="132" ht="18" customHeight="1" s="6">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>5回訪れたことがあります。</t>
+          <t>いいえ、ありません。</t>
         </is>
       </c>
       <c r="B132" s="27" t="n"/>
@@ -3178,10 +3184,10 @@
       <c r="I132" s="27" t="n"/>
       <c r="J132" s="57" t="n"/>
     </row>
-    <row r="133" ht="26" customHeight="1" s="6">
+    <row r="133" ht="22" customHeight="1" s="6">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>回答（返答）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B133" s="27" t="n"/>
@@ -3194,10 +3200,10 @@
       <c r="I133" s="27" t="n"/>
       <c r="J133" s="57" t="n"/>
     </row>
-    <row r="134" ht="20" customHeight="1" s="6">
+    <row r="134" ht="22" customHeight="1" s="6">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>一度も訪れたことがありません。</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B134" s="27" t="n"/>
@@ -3210,10 +3216,10 @@
       <c r="I134" s="27" t="n"/>
       <c r="J134" s="57" t="n"/>
     </row>
-    <row r="135" ht="26" customHeight="1" s="6">
+    <row r="135" ht="22" customHeight="1" s="6">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B135" s="27" t="n"/>
@@ -3226,26 +3232,26 @@
       <c r="I135" s="27" t="n"/>
       <c r="J135" s="57" t="n"/>
     </row>
-    <row r="136" ht="26" customHeight="1" s="6">
-      <c r="A136" s="11" t="inlineStr">
-        <is>
-          <t>回答（言いかえ）：</t>
-        </is>
-      </c>
-      <c r="B136" s="27" t="n"/>
-      <c r="C136" s="27" t="n"/>
-      <c r="D136" s="27" t="n"/>
-      <c r="E136" s="27" t="n"/>
-      <c r="F136" s="27" t="n"/>
-      <c r="G136" s="27" t="n"/>
-      <c r="H136" s="27" t="n"/>
-      <c r="I136" s="27" t="n"/>
-      <c r="J136" s="57" t="n"/>
-    </row>
-    <row r="137" ht="26" customHeight="1" s="6">
+    <row r="136" ht="18" customHeight="1" s="6">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>【回数】何回訪れたことがあるか</t>
+        </is>
+      </c>
+      <c r="B136" s="25" t="n"/>
+      <c r="C136" s="25" t="n"/>
+      <c r="D136" s="25" t="n"/>
+      <c r="E136" s="25" t="n"/>
+      <c r="F136" s="25" t="n"/>
+      <c r="G136" s="25" t="n"/>
+      <c r="H136" s="25" t="n"/>
+      <c r="I136" s="25" t="n"/>
+      <c r="J136" s="56" t="n"/>
+    </row>
+    <row r="137" ht="18" customHeight="1" s="6">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>私たちは京都を4回訪れたことがあります。</t>
         </is>
       </c>
       <c r="B137" s="27" t="n"/>
@@ -3258,8 +3264,12 @@
       <c r="I137" s="27" t="n"/>
       <c r="J137" s="57" t="n"/>
     </row>
-    <row r="138" ht="6" customHeight="1" s="6">
-      <c r="A138" s="11" t="n"/>
+    <row r="138" ht="22" customHeight="1" s="6">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
       <c r="B138" s="27" t="n"/>
       <c r="C138" s="27" t="n"/>
       <c r="D138" s="27" t="n"/>
@@ -3271,27 +3281,25 @@
       <c r="J138" s="57" t="n"/>
     </row>
     <row r="139" ht="18" customHeight="1" s="6">
-      <c r="A139" s="9" t="inlineStr">
-        <is>
-          <t>9．主語は「チサコ」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B139" s="25" t="n"/>
-      <c r="C139" s="25" t="n"/>
-      <c r="D139" s="25" t="n"/>
-      <c r="E139" s="25" t="n"/>
-      <c r="F139" s="25" t="n"/>
-      <c r="G139" s="25" t="n"/>
-      <c r="H139" s="25" t="n"/>
-      <c r="I139" s="25" t="n"/>
-      <c r="J139" s="56" t="n"/>
-    </row>
-    <row r="140" ht="60" customHeight="1" s="6">
-      <c r="A140" s="55" t="inlineStr">
-        <is>
-          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
-※回数は four times / five times のように表します。
-※否定では never または not ... before を使います。</t>
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>私たちは京都を何回訪れたことがありますか。</t>
+        </is>
+      </c>
+      <c r="B139" s="27" t="n"/>
+      <c r="C139" s="27" t="n"/>
+      <c r="D139" s="27" t="n"/>
+      <c r="E139" s="27" t="n"/>
+      <c r="F139" s="27" t="n"/>
+      <c r="G139" s="27" t="n"/>
+      <c r="H139" s="27" t="n"/>
+      <c r="I139" s="27" t="n"/>
+      <c r="J139" s="57" t="n"/>
+    </row>
+    <row r="140" ht="22" customHeight="1" s="6">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>回答（疑問文）：</t>
         </is>
       </c>
       <c r="B140" s="27" t="n"/>
@@ -3304,10 +3312,10 @@
       <c r="I140" s="27" t="n"/>
       <c r="J140" s="57" t="n"/>
     </row>
-    <row r="141" ht="20" customHeight="1" s="6">
+    <row r="141" ht="18" customHeight="1" s="6">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>チサコは京都を4回訪れたことがあります。</t>
+          <t>5回訪れたことがあります。</t>
         </is>
       </c>
       <c r="B141" s="27" t="n"/>
@@ -3320,10 +3328,10 @@
       <c r="I141" s="27" t="n"/>
       <c r="J141" s="57" t="n"/>
     </row>
-    <row r="142" ht="26" customHeight="1" s="6">
+    <row r="142" ht="22" customHeight="1" s="6">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（返答）：</t>
         </is>
       </c>
       <c r="B142" s="27" t="n"/>
@@ -3336,10 +3344,10 @@
       <c r="I142" s="27" t="n"/>
       <c r="J142" s="57" t="n"/>
     </row>
-    <row r="143" ht="20" customHeight="1" s="6">
+    <row r="143" ht="18" customHeight="1" s="6">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>チサコはまだ一度も京都を訪れたことがありません。</t>
+          <t>一度も訪れたことがありません。</t>
         </is>
       </c>
       <c r="B143" s="27" t="n"/>
@@ -3352,7 +3360,7 @@
       <c r="I143" s="27" t="n"/>
       <c r="J143" s="57" t="n"/>
     </row>
-    <row r="144" ht="26" customHeight="1" s="6">
+    <row r="144" ht="22" customHeight="1" s="6">
       <c r="A144" s="11" t="inlineStr">
         <is>
           <t>回答（基本形）：</t>
@@ -3368,7 +3376,7 @@
       <c r="I144" s="27" t="n"/>
       <c r="J144" s="57" t="n"/>
     </row>
-    <row r="145" ht="26" customHeight="1" s="6">
+    <row r="145" ht="22" customHeight="1" s="6">
       <c r="A145" s="11" t="inlineStr">
         <is>
           <t>回答（言いかえ）：</t>
@@ -3384,7 +3392,7 @@
       <c r="I145" s="27" t="n"/>
       <c r="J145" s="57" t="n"/>
     </row>
-    <row r="146" ht="26" customHeight="1" s="6">
+    <row r="146" ht="22" customHeight="1" s="6">
       <c r="A146" s="11" t="inlineStr">
         <is>
           <t>回答（短縮形）：</t>
@@ -3400,12 +3408,8 @@
       <c r="I146" s="27" t="n"/>
       <c r="J146" s="57" t="n"/>
     </row>
-    <row r="147" ht="20" customHeight="1" s="6">
-      <c r="A147" s="11" t="inlineStr">
-        <is>
-          <t>チサコは京都を何回訪れたことがありますか。</t>
-        </is>
-      </c>
+    <row r="147" ht="6" customHeight="1" s="6">
+      <c r="A147" s="11" t="n"/>
       <c r="B147" s="27" t="n"/>
       <c r="C147" s="27" t="n"/>
       <c r="D147" s="27" t="n"/>
@@ -3416,26 +3420,28 @@
       <c r="I147" s="27" t="n"/>
       <c r="J147" s="57" t="n"/>
     </row>
-    <row r="148" ht="26" customHeight="1" s="6">
-      <c r="A148" s="11" t="inlineStr">
-        <is>
-          <t>回答（疑問文）：</t>
-        </is>
-      </c>
-      <c r="B148" s="27" t="n"/>
-      <c r="C148" s="27" t="n"/>
-      <c r="D148" s="27" t="n"/>
-      <c r="E148" s="27" t="n"/>
-      <c r="F148" s="27" t="n"/>
-      <c r="G148" s="27" t="n"/>
-      <c r="H148" s="27" t="n"/>
-      <c r="I148" s="27" t="n"/>
-      <c r="J148" s="57" t="n"/>
-    </row>
-    <row r="149" ht="20" customHeight="1" s="6">
-      <c r="A149" s="11" t="inlineStr">
-        <is>
-          <t>5回訪れたことがあります。</t>
+    <row r="148" ht="18" customHeight="1" s="6">
+      <c r="A148" s="9" t="inlineStr">
+        <is>
+          <t>6．主語は「あなたたち」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B148" s="25" t="n"/>
+      <c r="C148" s="25" t="n"/>
+      <c r="D148" s="25" t="n"/>
+      <c r="E148" s="25" t="n"/>
+      <c r="F148" s="25" t="n"/>
+      <c r="G148" s="25" t="n"/>
+      <c r="H148" s="25" t="n"/>
+      <c r="I148" s="25" t="n"/>
+      <c r="J148" s="56" t="n"/>
+    </row>
+    <row r="149" ht="60" customHeight="1" s="6">
+      <c r="A149" s="55" t="inlineStr">
+        <is>
+          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
+※疑問文では ever、否定では never または not ... before を使います。
+※回数は four times / five times のように表します。</t>
         </is>
       </c>
       <c r="B149" s="27" t="n"/>
@@ -3448,26 +3454,26 @@
       <c r="I149" s="27" t="n"/>
       <c r="J149" s="57" t="n"/>
     </row>
-    <row r="150" ht="26" customHeight="1" s="6">
-      <c r="A150" s="11" t="inlineStr">
-        <is>
-          <t>回答（返答）：</t>
-        </is>
-      </c>
-      <c r="B150" s="27" t="n"/>
-      <c r="C150" s="27" t="n"/>
-      <c r="D150" s="27" t="n"/>
-      <c r="E150" s="27" t="n"/>
-      <c r="F150" s="27" t="n"/>
-      <c r="G150" s="27" t="n"/>
-      <c r="H150" s="27" t="n"/>
-      <c r="I150" s="27" t="n"/>
-      <c r="J150" s="57" t="n"/>
-    </row>
-    <row r="151" ht="20" customHeight="1" s="6">
+    <row r="150" ht="18" customHeight="1" s="6">
+      <c r="A150" s="9" t="inlineStr">
+        <is>
+          <t>【基本】訪れたことがある・ない</t>
+        </is>
+      </c>
+      <c r="B150" s="25" t="n"/>
+      <c r="C150" s="25" t="n"/>
+      <c r="D150" s="25" t="n"/>
+      <c r="E150" s="25" t="n"/>
+      <c r="F150" s="25" t="n"/>
+      <c r="G150" s="25" t="n"/>
+      <c r="H150" s="25" t="n"/>
+      <c r="I150" s="25" t="n"/>
+      <c r="J150" s="56" t="n"/>
+    </row>
+    <row r="151" ht="18" customHeight="1" s="6">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>一度も訪れたことがありません。</t>
+          <t>あなたたちは京都を訪れたことがあります。</t>
         </is>
       </c>
       <c r="B151" s="27" t="n"/>
@@ -3480,7 +3486,7 @@
       <c r="I151" s="27" t="n"/>
       <c r="J151" s="57" t="n"/>
     </row>
-    <row r="152" ht="26" customHeight="1" s="6">
+    <row r="152" ht="22" customHeight="1" s="6">
       <c r="A152" s="11" t="inlineStr">
         <is>
           <t>回答（基本形）：</t>
@@ -3496,10 +3502,10 @@
       <c r="I152" s="27" t="n"/>
       <c r="J152" s="57" t="n"/>
     </row>
-    <row r="153" ht="26" customHeight="1" s="6">
+    <row r="153" ht="18" customHeight="1" s="6">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>あなたたちはまだ一度も京都を訪れたことがありません。</t>
         </is>
       </c>
       <c r="B153" s="27" t="n"/>
@@ -3512,10 +3518,10 @@
       <c r="I153" s="27" t="n"/>
       <c r="J153" s="57" t="n"/>
     </row>
-    <row r="154" ht="26" customHeight="1" s="6">
+    <row r="154" ht="22" customHeight="1" s="6">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B154" s="27" t="n"/>
@@ -3528,8 +3534,12 @@
       <c r="I154" s="27" t="n"/>
       <c r="J154" s="57" t="n"/>
     </row>
-    <row r="155" ht="6" customHeight="1" s="6">
-      <c r="A155" s="11" t="n"/>
+    <row r="155" ht="22" customHeight="1" s="6">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ）：</t>
+        </is>
+      </c>
       <c r="B155" s="27" t="n"/>
       <c r="C155" s="27" t="n"/>
       <c r="D155" s="27" t="n"/>
@@ -3540,176 +3550,2002 @@
       <c r="I155" s="27" t="n"/>
       <c r="J155" s="57" t="n"/>
     </row>
+    <row r="156" ht="22" customHeight="1" s="6">
+      <c r="A156" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
+        </is>
+      </c>
+      <c r="B156" s="27" t="n"/>
+      <c r="C156" s="27" t="n"/>
+      <c r="D156" s="27" t="n"/>
+      <c r="E156" s="27" t="n"/>
+      <c r="F156" s="27" t="n"/>
+      <c r="G156" s="27" t="n"/>
+      <c r="H156" s="27" t="n"/>
+      <c r="I156" s="27" t="n"/>
+      <c r="J156" s="57" t="n"/>
+    </row>
+    <row r="157" ht="18" customHeight="1" s="6">
+      <c r="A157" s="11" t="inlineStr">
+        <is>
+          <t>あなたたちは京都を訪れたことがありますか。</t>
+        </is>
+      </c>
+      <c r="B157" s="27" t="n"/>
+      <c r="C157" s="27" t="n"/>
+      <c r="D157" s="27" t="n"/>
+      <c r="E157" s="27" t="n"/>
+      <c r="F157" s="27" t="n"/>
+      <c r="G157" s="27" t="n"/>
+      <c r="H157" s="27" t="n"/>
+      <c r="I157" s="27" t="n"/>
+      <c r="J157" s="57" t="n"/>
+    </row>
+    <row r="158" ht="22" customHeight="1" s="6">
+      <c r="A158" s="11" t="inlineStr">
+        <is>
+          <t>回答（疑問文）：</t>
+        </is>
+      </c>
+      <c r="B158" s="27" t="n"/>
+      <c r="C158" s="27" t="n"/>
+      <c r="D158" s="27" t="n"/>
+      <c r="E158" s="27" t="n"/>
+      <c r="F158" s="27" t="n"/>
+      <c r="G158" s="27" t="n"/>
+      <c r="H158" s="27" t="n"/>
+      <c r="I158" s="27" t="n"/>
+      <c r="J158" s="57" t="n"/>
+    </row>
+    <row r="159" ht="18" customHeight="1" s="6">
+      <c r="A159" s="11" t="inlineStr">
+        <is>
+          <t>はい、あります。</t>
+        </is>
+      </c>
+      <c r="B159" s="27" t="n"/>
+      <c r="C159" s="27" t="n"/>
+      <c r="D159" s="27" t="n"/>
+      <c r="E159" s="27" t="n"/>
+      <c r="F159" s="27" t="n"/>
+      <c r="G159" s="27" t="n"/>
+      <c r="H159" s="27" t="n"/>
+      <c r="I159" s="27" t="n"/>
+      <c r="J159" s="57" t="n"/>
+    </row>
+    <row r="160" ht="22" customHeight="1" s="6">
+      <c r="A160" s="11" t="inlineStr">
+        <is>
+          <t>回答（返答）：</t>
+        </is>
+      </c>
+      <c r="B160" s="27" t="n"/>
+      <c r="C160" s="27" t="n"/>
+      <c r="D160" s="27" t="n"/>
+      <c r="E160" s="27" t="n"/>
+      <c r="F160" s="27" t="n"/>
+      <c r="G160" s="27" t="n"/>
+      <c r="H160" s="27" t="n"/>
+      <c r="I160" s="27" t="n"/>
+      <c r="J160" s="57" t="n"/>
+    </row>
+    <row r="161" ht="18" customHeight="1" s="6">
+      <c r="A161" s="11" t="inlineStr">
+        <is>
+          <t>いいえ、ありません。</t>
+        </is>
+      </c>
+      <c r="B161" s="27" t="n"/>
+      <c r="C161" s="27" t="n"/>
+      <c r="D161" s="27" t="n"/>
+      <c r="E161" s="27" t="n"/>
+      <c r="F161" s="27" t="n"/>
+      <c r="G161" s="27" t="n"/>
+      <c r="H161" s="27" t="n"/>
+      <c r="I161" s="27" t="n"/>
+      <c r="J161" s="57" t="n"/>
+    </row>
+    <row r="162" ht="22" customHeight="1" s="6">
+      <c r="A162" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B162" s="27" t="n"/>
+      <c r="C162" s="27" t="n"/>
+      <c r="D162" s="27" t="n"/>
+      <c r="E162" s="27" t="n"/>
+      <c r="F162" s="27" t="n"/>
+      <c r="G162" s="27" t="n"/>
+      <c r="H162" s="27" t="n"/>
+      <c r="I162" s="27" t="n"/>
+      <c r="J162" s="57" t="n"/>
+    </row>
+    <row r="163" ht="22" customHeight="1" s="6">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ）：</t>
+        </is>
+      </c>
+      <c r="B163" s="27" t="n"/>
+      <c r="C163" s="27" t="n"/>
+      <c r="D163" s="27" t="n"/>
+      <c r="E163" s="27" t="n"/>
+      <c r="F163" s="27" t="n"/>
+      <c r="G163" s="27" t="n"/>
+      <c r="H163" s="27" t="n"/>
+      <c r="I163" s="27" t="n"/>
+      <c r="J163" s="57" t="n"/>
+    </row>
+    <row r="164" ht="22" customHeight="1" s="6">
+      <c r="A164" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
+        </is>
+      </c>
+      <c r="B164" s="27" t="n"/>
+      <c r="C164" s="27" t="n"/>
+      <c r="D164" s="27" t="n"/>
+      <c r="E164" s="27" t="n"/>
+      <c r="F164" s="27" t="n"/>
+      <c r="G164" s="27" t="n"/>
+      <c r="H164" s="27" t="n"/>
+      <c r="I164" s="27" t="n"/>
+      <c r="J164" s="57" t="n"/>
+    </row>
+    <row r="165" ht="18" customHeight="1" s="6">
+      <c r="A165" s="9" t="inlineStr">
+        <is>
+          <t>【回数】何回訪れたことがあるか</t>
+        </is>
+      </c>
+      <c r="B165" s="25" t="n"/>
+      <c r="C165" s="25" t="n"/>
+      <c r="D165" s="25" t="n"/>
+      <c r="E165" s="25" t="n"/>
+      <c r="F165" s="25" t="n"/>
+      <c r="G165" s="25" t="n"/>
+      <c r="H165" s="25" t="n"/>
+      <c r="I165" s="25" t="n"/>
+      <c r="J165" s="56" t="n"/>
+    </row>
+    <row r="166" ht="18" customHeight="1" s="6">
+      <c r="A166" s="11" t="inlineStr">
+        <is>
+          <t>あなたたちは京都を4回訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B166" s="27" t="n"/>
+      <c r="C166" s="27" t="n"/>
+      <c r="D166" s="27" t="n"/>
+      <c r="E166" s="27" t="n"/>
+      <c r="F166" s="27" t="n"/>
+      <c r="G166" s="27" t="n"/>
+      <c r="H166" s="27" t="n"/>
+      <c r="I166" s="27" t="n"/>
+      <c r="J166" s="57" t="n"/>
+    </row>
+    <row r="167" ht="22" customHeight="1" s="6">
+      <c r="A167" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B167" s="27" t="n"/>
+      <c r="C167" s="27" t="n"/>
+      <c r="D167" s="27" t="n"/>
+      <c r="E167" s="27" t="n"/>
+      <c r="F167" s="27" t="n"/>
+      <c r="G167" s="27" t="n"/>
+      <c r="H167" s="27" t="n"/>
+      <c r="I167" s="27" t="n"/>
+      <c r="J167" s="57" t="n"/>
+    </row>
+    <row r="168" ht="18" customHeight="1" s="6">
+      <c r="A168" s="11" t="inlineStr">
+        <is>
+          <t>あなたたちは京都を何回訪れたことがありますか。</t>
+        </is>
+      </c>
+      <c r="B168" s="27" t="n"/>
+      <c r="C168" s="27" t="n"/>
+      <c r="D168" s="27" t="n"/>
+      <c r="E168" s="27" t="n"/>
+      <c r="F168" s="27" t="n"/>
+      <c r="G168" s="27" t="n"/>
+      <c r="H168" s="27" t="n"/>
+      <c r="I168" s="27" t="n"/>
+      <c r="J168" s="57" t="n"/>
+    </row>
+    <row r="169" ht="22" customHeight="1" s="6">
+      <c r="A169" s="11" t="inlineStr">
+        <is>
+          <t>回答（疑問文）：</t>
+        </is>
+      </c>
+      <c r="B169" s="27" t="n"/>
+      <c r="C169" s="27" t="n"/>
+      <c r="D169" s="27" t="n"/>
+      <c r="E169" s="27" t="n"/>
+      <c r="F169" s="27" t="n"/>
+      <c r="G169" s="27" t="n"/>
+      <c r="H169" s="27" t="n"/>
+      <c r="I169" s="27" t="n"/>
+      <c r="J169" s="57" t="n"/>
+    </row>
+    <row r="170" ht="18" customHeight="1" s="6">
+      <c r="A170" s="11" t="inlineStr">
+        <is>
+          <t>5回訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B170" s="27" t="n"/>
+      <c r="C170" s="27" t="n"/>
+      <c r="D170" s="27" t="n"/>
+      <c r="E170" s="27" t="n"/>
+      <c r="F170" s="27" t="n"/>
+      <c r="G170" s="27" t="n"/>
+      <c r="H170" s="27" t="n"/>
+      <c r="I170" s="27" t="n"/>
+      <c r="J170" s="57" t="n"/>
+    </row>
+    <row r="171" ht="22" customHeight="1" s="6">
+      <c r="A171" s="11" t="inlineStr">
+        <is>
+          <t>回答（返答）：</t>
+        </is>
+      </c>
+      <c r="B171" s="27" t="n"/>
+      <c r="C171" s="27" t="n"/>
+      <c r="D171" s="27" t="n"/>
+      <c r="E171" s="27" t="n"/>
+      <c r="F171" s="27" t="n"/>
+      <c r="G171" s="27" t="n"/>
+      <c r="H171" s="27" t="n"/>
+      <c r="I171" s="27" t="n"/>
+      <c r="J171" s="57" t="n"/>
+    </row>
+    <row r="172" ht="18" customHeight="1" s="6">
+      <c r="A172" s="11" t="inlineStr">
+        <is>
+          <t>一度も訪れたことがありません。</t>
+        </is>
+      </c>
+      <c r="B172" s="27" t="n"/>
+      <c r="C172" s="27" t="n"/>
+      <c r="D172" s="27" t="n"/>
+      <c r="E172" s="27" t="n"/>
+      <c r="F172" s="27" t="n"/>
+      <c r="G172" s="27" t="n"/>
+      <c r="H172" s="27" t="n"/>
+      <c r="I172" s="27" t="n"/>
+      <c r="J172" s="57" t="n"/>
+    </row>
+    <row r="173" ht="22" customHeight="1" s="6">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B173" s="27" t="n"/>
+      <c r="C173" s="27" t="n"/>
+      <c r="D173" s="27" t="n"/>
+      <c r="E173" s="27" t="n"/>
+      <c r="F173" s="27" t="n"/>
+      <c r="G173" s="27" t="n"/>
+      <c r="H173" s="27" t="n"/>
+      <c r="I173" s="27" t="n"/>
+      <c r="J173" s="57" t="n"/>
+    </row>
+    <row r="174" ht="22" customHeight="1" s="6">
+      <c r="A174" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ）：</t>
+        </is>
+      </c>
+      <c r="B174" s="27" t="n"/>
+      <c r="C174" s="27" t="n"/>
+      <c r="D174" s="27" t="n"/>
+      <c r="E174" s="27" t="n"/>
+      <c r="F174" s="27" t="n"/>
+      <c r="G174" s="27" t="n"/>
+      <c r="H174" s="27" t="n"/>
+      <c r="I174" s="27" t="n"/>
+      <c r="J174" s="57" t="n"/>
+    </row>
+    <row r="175" ht="22" customHeight="1" s="6">
+      <c r="A175" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
+        </is>
+      </c>
+      <c r="B175" s="27" t="n"/>
+      <c r="C175" s="27" t="n"/>
+      <c r="D175" s="27" t="n"/>
+      <c r="E175" s="27" t="n"/>
+      <c r="F175" s="27" t="n"/>
+      <c r="G175" s="27" t="n"/>
+      <c r="H175" s="27" t="n"/>
+      <c r="I175" s="27" t="n"/>
+      <c r="J175" s="57" t="n"/>
+    </row>
+    <row r="176" ht="6" customHeight="1" s="6">
+      <c r="A176" s="11" t="n"/>
+      <c r="B176" s="27" t="n"/>
+      <c r="C176" s="27" t="n"/>
+      <c r="D176" s="27" t="n"/>
+      <c r="E176" s="27" t="n"/>
+      <c r="F176" s="27" t="n"/>
+      <c r="G176" s="27" t="n"/>
+      <c r="H176" s="27" t="n"/>
+      <c r="I176" s="27" t="n"/>
+      <c r="J176" s="57" t="n"/>
+    </row>
+    <row r="177" ht="18" customHeight="1" s="6">
+      <c r="A177" s="9" t="inlineStr">
+        <is>
+          <t>7．主語は「彼ら」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B177" s="25" t="n"/>
+      <c r="C177" s="25" t="n"/>
+      <c r="D177" s="25" t="n"/>
+      <c r="E177" s="25" t="n"/>
+      <c r="F177" s="25" t="n"/>
+      <c r="G177" s="25" t="n"/>
+      <c r="H177" s="25" t="n"/>
+      <c r="I177" s="25" t="n"/>
+      <c r="J177" s="56" t="n"/>
+    </row>
+    <row r="178" ht="60" customHeight="1" s="6">
+      <c r="A178" s="55" t="inlineStr">
+        <is>
+          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
+※疑問文では ever、否定では never または not ... before を使います。
+※回数は four times / five times のように表します。</t>
+        </is>
+      </c>
+      <c r="B178" s="27" t="n"/>
+      <c r="C178" s="27" t="n"/>
+      <c r="D178" s="27" t="n"/>
+      <c r="E178" s="27" t="n"/>
+      <c r="F178" s="27" t="n"/>
+      <c r="G178" s="27" t="n"/>
+      <c r="H178" s="27" t="n"/>
+      <c r="I178" s="27" t="n"/>
+      <c r="J178" s="57" t="n"/>
+    </row>
+    <row r="179" ht="18" customHeight="1" s="6">
+      <c r="A179" s="9" t="inlineStr">
+        <is>
+          <t>【基本】訪れたことがある・ない</t>
+        </is>
+      </c>
+      <c r="B179" s="25" t="n"/>
+      <c r="C179" s="25" t="n"/>
+      <c r="D179" s="25" t="n"/>
+      <c r="E179" s="25" t="n"/>
+      <c r="F179" s="25" t="n"/>
+      <c r="G179" s="25" t="n"/>
+      <c r="H179" s="25" t="n"/>
+      <c r="I179" s="25" t="n"/>
+      <c r="J179" s="56" t="n"/>
+    </row>
+    <row r="180" ht="18" customHeight="1" s="6">
+      <c r="A180" s="11" t="inlineStr">
+        <is>
+          <t>彼らは京都を訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B180" s="27" t="n"/>
+      <c r="C180" s="27" t="n"/>
+      <c r="D180" s="27" t="n"/>
+      <c r="E180" s="27" t="n"/>
+      <c r="F180" s="27" t="n"/>
+      <c r="G180" s="27" t="n"/>
+      <c r="H180" s="27" t="n"/>
+      <c r="I180" s="27" t="n"/>
+      <c r="J180" s="57" t="n"/>
+    </row>
+    <row r="181" ht="22" customHeight="1" s="6">
+      <c r="A181" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B181" s="27" t="n"/>
+      <c r="C181" s="27" t="n"/>
+      <c r="D181" s="27" t="n"/>
+      <c r="E181" s="27" t="n"/>
+      <c r="F181" s="27" t="n"/>
+      <c r="G181" s="27" t="n"/>
+      <c r="H181" s="27" t="n"/>
+      <c r="I181" s="27" t="n"/>
+      <c r="J181" s="57" t="n"/>
+    </row>
+    <row r="182" ht="18" customHeight="1" s="6">
+      <c r="A182" s="11" t="inlineStr">
+        <is>
+          <t>彼らはまだ一度も京都を訪れたことがありません。</t>
+        </is>
+      </c>
+      <c r="B182" s="27" t="n"/>
+      <c r="C182" s="27" t="n"/>
+      <c r="D182" s="27" t="n"/>
+      <c r="E182" s="27" t="n"/>
+      <c r="F182" s="27" t="n"/>
+      <c r="G182" s="27" t="n"/>
+      <c r="H182" s="27" t="n"/>
+      <c r="I182" s="27" t="n"/>
+      <c r="J182" s="57" t="n"/>
+    </row>
+    <row r="183" ht="22" customHeight="1" s="6">
+      <c r="A183" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B183" s="27" t="n"/>
+      <c r="C183" s="27" t="n"/>
+      <c r="D183" s="27" t="n"/>
+      <c r="E183" s="27" t="n"/>
+      <c r="F183" s="27" t="n"/>
+      <c r="G183" s="27" t="n"/>
+      <c r="H183" s="27" t="n"/>
+      <c r="I183" s="27" t="n"/>
+      <c r="J183" s="57" t="n"/>
+    </row>
+    <row r="184" ht="22" customHeight="1" s="6">
+      <c r="A184" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ）：</t>
+        </is>
+      </c>
+      <c r="B184" s="27" t="n"/>
+      <c r="C184" s="27" t="n"/>
+      <c r="D184" s="27" t="n"/>
+      <c r="E184" s="27" t="n"/>
+      <c r="F184" s="27" t="n"/>
+      <c r="G184" s="27" t="n"/>
+      <c r="H184" s="27" t="n"/>
+      <c r="I184" s="27" t="n"/>
+      <c r="J184" s="57" t="n"/>
+    </row>
+    <row r="185" ht="22" customHeight="1" s="6">
+      <c r="A185" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
+        </is>
+      </c>
+      <c r="B185" s="27" t="n"/>
+      <c r="C185" s="27" t="n"/>
+      <c r="D185" s="27" t="n"/>
+      <c r="E185" s="27" t="n"/>
+      <c r="F185" s="27" t="n"/>
+      <c r="G185" s="27" t="n"/>
+      <c r="H185" s="27" t="n"/>
+      <c r="I185" s="27" t="n"/>
+      <c r="J185" s="57" t="n"/>
+    </row>
+    <row r="186" ht="18" customHeight="1" s="6">
+      <c r="A186" s="11" t="inlineStr">
+        <is>
+          <t>彼らは京都を訪れたことがありますか。</t>
+        </is>
+      </c>
+      <c r="B186" s="27" t="n"/>
+      <c r="C186" s="27" t="n"/>
+      <c r="D186" s="27" t="n"/>
+      <c r="E186" s="27" t="n"/>
+      <c r="F186" s="27" t="n"/>
+      <c r="G186" s="27" t="n"/>
+      <c r="H186" s="27" t="n"/>
+      <c r="I186" s="27" t="n"/>
+      <c r="J186" s="57" t="n"/>
+    </row>
+    <row r="187" ht="22" customHeight="1" s="6">
+      <c r="A187" s="11" t="inlineStr">
+        <is>
+          <t>回答（疑問文）：</t>
+        </is>
+      </c>
+      <c r="B187" s="27" t="n"/>
+      <c r="C187" s="27" t="n"/>
+      <c r="D187" s="27" t="n"/>
+      <c r="E187" s="27" t="n"/>
+      <c r="F187" s="27" t="n"/>
+      <c r="G187" s="27" t="n"/>
+      <c r="H187" s="27" t="n"/>
+      <c r="I187" s="27" t="n"/>
+      <c r="J187" s="57" t="n"/>
+    </row>
+    <row r="188" ht="18" customHeight="1" s="6">
+      <c r="A188" s="11" t="inlineStr">
+        <is>
+          <t>はい、あります。</t>
+        </is>
+      </c>
+      <c r="B188" s="27" t="n"/>
+      <c r="C188" s="27" t="n"/>
+      <c r="D188" s="27" t="n"/>
+      <c r="E188" s="27" t="n"/>
+      <c r="F188" s="27" t="n"/>
+      <c r="G188" s="27" t="n"/>
+      <c r="H188" s="27" t="n"/>
+      <c r="I188" s="27" t="n"/>
+      <c r="J188" s="57" t="n"/>
+    </row>
+    <row r="189" ht="22" customHeight="1" s="6">
+      <c r="A189" s="11" t="inlineStr">
+        <is>
+          <t>回答（返答）：</t>
+        </is>
+      </c>
+      <c r="B189" s="27" t="n"/>
+      <c r="C189" s="27" t="n"/>
+      <c r="D189" s="27" t="n"/>
+      <c r="E189" s="27" t="n"/>
+      <c r="F189" s="27" t="n"/>
+      <c r="G189" s="27" t="n"/>
+      <c r="H189" s="27" t="n"/>
+      <c r="I189" s="27" t="n"/>
+      <c r="J189" s="57" t="n"/>
+    </row>
+    <row r="190" ht="18" customHeight="1" s="6">
+      <c r="A190" s="11" t="inlineStr">
+        <is>
+          <t>いいえ、ありません。</t>
+        </is>
+      </c>
+      <c r="B190" s="27" t="n"/>
+      <c r="C190" s="27" t="n"/>
+      <c r="D190" s="27" t="n"/>
+      <c r="E190" s="27" t="n"/>
+      <c r="F190" s="27" t="n"/>
+      <c r="G190" s="27" t="n"/>
+      <c r="H190" s="27" t="n"/>
+      <c r="I190" s="27" t="n"/>
+      <c r="J190" s="57" t="n"/>
+    </row>
+    <row r="191" ht="22" customHeight="1" s="6">
+      <c r="A191" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B191" s="27" t="n"/>
+      <c r="C191" s="27" t="n"/>
+      <c r="D191" s="27" t="n"/>
+      <c r="E191" s="27" t="n"/>
+      <c r="F191" s="27" t="n"/>
+      <c r="G191" s="27" t="n"/>
+      <c r="H191" s="27" t="n"/>
+      <c r="I191" s="27" t="n"/>
+      <c r="J191" s="57" t="n"/>
+    </row>
+    <row r="192" ht="22" customHeight="1" s="6">
+      <c r="A192" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ）：</t>
+        </is>
+      </c>
+      <c r="B192" s="27" t="n"/>
+      <c r="C192" s="27" t="n"/>
+      <c r="D192" s="27" t="n"/>
+      <c r="E192" s="27" t="n"/>
+      <c r="F192" s="27" t="n"/>
+      <c r="G192" s="27" t="n"/>
+      <c r="H192" s="27" t="n"/>
+      <c r="I192" s="27" t="n"/>
+      <c r="J192" s="57" t="n"/>
+    </row>
+    <row r="193" ht="22" customHeight="1" s="6">
+      <c r="A193" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
+        </is>
+      </c>
+      <c r="B193" s="27" t="n"/>
+      <c r="C193" s="27" t="n"/>
+      <c r="D193" s="27" t="n"/>
+      <c r="E193" s="27" t="n"/>
+      <c r="F193" s="27" t="n"/>
+      <c r="G193" s="27" t="n"/>
+      <c r="H193" s="27" t="n"/>
+      <c r="I193" s="27" t="n"/>
+      <c r="J193" s="57" t="n"/>
+    </row>
+    <row r="194" ht="18" customHeight="1" s="6">
+      <c r="A194" s="9" t="inlineStr">
+        <is>
+          <t>【回数】何回訪れたことがあるか</t>
+        </is>
+      </c>
+      <c r="B194" s="25" t="n"/>
+      <c r="C194" s="25" t="n"/>
+      <c r="D194" s="25" t="n"/>
+      <c r="E194" s="25" t="n"/>
+      <c r="F194" s="25" t="n"/>
+      <c r="G194" s="25" t="n"/>
+      <c r="H194" s="25" t="n"/>
+      <c r="I194" s="25" t="n"/>
+      <c r="J194" s="56" t="n"/>
+    </row>
+    <row r="195" ht="18" customHeight="1" s="6">
+      <c r="A195" s="11" t="inlineStr">
+        <is>
+          <t>彼らは京都を4回訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B195" s="27" t="n"/>
+      <c r="C195" s="27" t="n"/>
+      <c r="D195" s="27" t="n"/>
+      <c r="E195" s="27" t="n"/>
+      <c r="F195" s="27" t="n"/>
+      <c r="G195" s="27" t="n"/>
+      <c r="H195" s="27" t="n"/>
+      <c r="I195" s="27" t="n"/>
+      <c r="J195" s="57" t="n"/>
+    </row>
+    <row r="196" ht="22" customHeight="1" s="6">
+      <c r="A196" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B196" s="27" t="n"/>
+      <c r="C196" s="27" t="n"/>
+      <c r="D196" s="27" t="n"/>
+      <c r="E196" s="27" t="n"/>
+      <c r="F196" s="27" t="n"/>
+      <c r="G196" s="27" t="n"/>
+      <c r="H196" s="27" t="n"/>
+      <c r="I196" s="27" t="n"/>
+      <c r="J196" s="57" t="n"/>
+    </row>
+    <row r="197" ht="18" customHeight="1" s="6">
+      <c r="A197" s="11" t="inlineStr">
+        <is>
+          <t>彼らは京都を何回訪れたことがありますか。</t>
+        </is>
+      </c>
+      <c r="B197" s="27" t="n"/>
+      <c r="C197" s="27" t="n"/>
+      <c r="D197" s="27" t="n"/>
+      <c r="E197" s="27" t="n"/>
+      <c r="F197" s="27" t="n"/>
+      <c r="G197" s="27" t="n"/>
+      <c r="H197" s="27" t="n"/>
+      <c r="I197" s="27" t="n"/>
+      <c r="J197" s="57" t="n"/>
+    </row>
+    <row r="198" ht="22" customHeight="1" s="6">
+      <c r="A198" s="11" t="inlineStr">
+        <is>
+          <t>回答（疑問文）：</t>
+        </is>
+      </c>
+      <c r="B198" s="27" t="n"/>
+      <c r="C198" s="27" t="n"/>
+      <c r="D198" s="27" t="n"/>
+      <c r="E198" s="27" t="n"/>
+      <c r="F198" s="27" t="n"/>
+      <c r="G198" s="27" t="n"/>
+      <c r="H198" s="27" t="n"/>
+      <c r="I198" s="27" t="n"/>
+      <c r="J198" s="57" t="n"/>
+    </row>
+    <row r="199" ht="18" customHeight="1" s="6">
+      <c r="A199" s="11" t="inlineStr">
+        <is>
+          <t>5回訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B199" s="27" t="n"/>
+      <c r="C199" s="27" t="n"/>
+      <c r="D199" s="27" t="n"/>
+      <c r="E199" s="27" t="n"/>
+      <c r="F199" s="27" t="n"/>
+      <c r="G199" s="27" t="n"/>
+      <c r="H199" s="27" t="n"/>
+      <c r="I199" s="27" t="n"/>
+      <c r="J199" s="57" t="n"/>
+    </row>
+    <row r="200" ht="22" customHeight="1" s="6">
+      <c r="A200" s="11" t="inlineStr">
+        <is>
+          <t>回答（返答）：</t>
+        </is>
+      </c>
+      <c r="B200" s="27" t="n"/>
+      <c r="C200" s="27" t="n"/>
+      <c r="D200" s="27" t="n"/>
+      <c r="E200" s="27" t="n"/>
+      <c r="F200" s="27" t="n"/>
+      <c r="G200" s="27" t="n"/>
+      <c r="H200" s="27" t="n"/>
+      <c r="I200" s="27" t="n"/>
+      <c r="J200" s="57" t="n"/>
+    </row>
+    <row r="201" ht="18" customHeight="1" s="6">
+      <c r="A201" s="11" t="inlineStr">
+        <is>
+          <t>一度も訪れたことがありません。</t>
+        </is>
+      </c>
+      <c r="B201" s="27" t="n"/>
+      <c r="C201" s="27" t="n"/>
+      <c r="D201" s="27" t="n"/>
+      <c r="E201" s="27" t="n"/>
+      <c r="F201" s="27" t="n"/>
+      <c r="G201" s="27" t="n"/>
+      <c r="H201" s="27" t="n"/>
+      <c r="I201" s="27" t="n"/>
+      <c r="J201" s="57" t="n"/>
+    </row>
+    <row r="202" ht="22" customHeight="1" s="6">
+      <c r="A202" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B202" s="27" t="n"/>
+      <c r="C202" s="27" t="n"/>
+      <c r="D202" s="27" t="n"/>
+      <c r="E202" s="27" t="n"/>
+      <c r="F202" s="27" t="n"/>
+      <c r="G202" s="27" t="n"/>
+      <c r="H202" s="27" t="n"/>
+      <c r="I202" s="27" t="n"/>
+      <c r="J202" s="57" t="n"/>
+    </row>
+    <row r="203" ht="22" customHeight="1" s="6">
+      <c r="A203" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ）：</t>
+        </is>
+      </c>
+      <c r="B203" s="27" t="n"/>
+      <c r="C203" s="27" t="n"/>
+      <c r="D203" s="27" t="n"/>
+      <c r="E203" s="27" t="n"/>
+      <c r="F203" s="27" t="n"/>
+      <c r="G203" s="27" t="n"/>
+      <c r="H203" s="27" t="n"/>
+      <c r="I203" s="27" t="n"/>
+      <c r="J203" s="57" t="n"/>
+    </row>
+    <row r="204" ht="22" customHeight="1" s="6">
+      <c r="A204" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
+        </is>
+      </c>
+      <c r="B204" s="27" t="n"/>
+      <c r="C204" s="27" t="n"/>
+      <c r="D204" s="27" t="n"/>
+      <c r="E204" s="27" t="n"/>
+      <c r="F204" s="27" t="n"/>
+      <c r="G204" s="27" t="n"/>
+      <c r="H204" s="27" t="n"/>
+      <c r="I204" s="27" t="n"/>
+      <c r="J204" s="57" t="n"/>
+    </row>
+    <row r="205" ht="6" customHeight="1" s="6">
+      <c r="A205" s="11" t="n"/>
+      <c r="B205" s="27" t="n"/>
+      <c r="C205" s="27" t="n"/>
+      <c r="D205" s="27" t="n"/>
+      <c r="E205" s="27" t="n"/>
+      <c r="F205" s="27" t="n"/>
+      <c r="G205" s="27" t="n"/>
+      <c r="H205" s="27" t="n"/>
+      <c r="I205" s="27" t="n"/>
+      <c r="J205" s="57" t="n"/>
+    </row>
+    <row r="206" ht="18" customHeight="1" s="6">
+      <c r="A206" s="9" t="inlineStr">
+        <is>
+          <t>8．主語は「リョウタロウ」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B206" s="25" t="n"/>
+      <c r="C206" s="25" t="n"/>
+      <c r="D206" s="25" t="n"/>
+      <c r="E206" s="25" t="n"/>
+      <c r="F206" s="25" t="n"/>
+      <c r="G206" s="25" t="n"/>
+      <c r="H206" s="25" t="n"/>
+      <c r="I206" s="25" t="n"/>
+      <c r="J206" s="56" t="n"/>
+    </row>
+    <row r="207" ht="60" customHeight="1" s="6">
+      <c r="A207" s="55" t="inlineStr">
+        <is>
+          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
+※疑問文では ever、否定では never または not ... before を使います。
+※回数は four times / five times のように表します。</t>
+        </is>
+      </c>
+      <c r="B207" s="27" t="n"/>
+      <c r="C207" s="27" t="n"/>
+      <c r="D207" s="27" t="n"/>
+      <c r="E207" s="27" t="n"/>
+      <c r="F207" s="27" t="n"/>
+      <c r="G207" s="27" t="n"/>
+      <c r="H207" s="27" t="n"/>
+      <c r="I207" s="27" t="n"/>
+      <c r="J207" s="57" t="n"/>
+    </row>
+    <row r="208" ht="18" customHeight="1" s="6">
+      <c r="A208" s="9" t="inlineStr">
+        <is>
+          <t>【基本】訪れたことがある・ない</t>
+        </is>
+      </c>
+      <c r="B208" s="25" t="n"/>
+      <c r="C208" s="25" t="n"/>
+      <c r="D208" s="25" t="n"/>
+      <c r="E208" s="25" t="n"/>
+      <c r="F208" s="25" t="n"/>
+      <c r="G208" s="25" t="n"/>
+      <c r="H208" s="25" t="n"/>
+      <c r="I208" s="25" t="n"/>
+      <c r="J208" s="56" t="n"/>
+    </row>
+    <row r="209" ht="18" customHeight="1" s="6">
+      <c r="A209" s="11" t="inlineStr">
+        <is>
+          <t>リョウタロウは京都を訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B209" s="27" t="n"/>
+      <c r="C209" s="27" t="n"/>
+      <c r="D209" s="27" t="n"/>
+      <c r="E209" s="27" t="n"/>
+      <c r="F209" s="27" t="n"/>
+      <c r="G209" s="27" t="n"/>
+      <c r="H209" s="27" t="n"/>
+      <c r="I209" s="27" t="n"/>
+      <c r="J209" s="57" t="n"/>
+    </row>
+    <row r="210" ht="22" customHeight="1" s="6">
+      <c r="A210" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B210" s="27" t="n"/>
+      <c r="C210" s="27" t="n"/>
+      <c r="D210" s="27" t="n"/>
+      <c r="E210" s="27" t="n"/>
+      <c r="F210" s="27" t="n"/>
+      <c r="G210" s="27" t="n"/>
+      <c r="H210" s="27" t="n"/>
+      <c r="I210" s="27" t="n"/>
+      <c r="J210" s="57" t="n"/>
+    </row>
+    <row r="211" ht="18" customHeight="1" s="6">
+      <c r="A211" s="11" t="inlineStr">
+        <is>
+          <t>リョウタロウはまだ一度も京都を訪れたことがありません。</t>
+        </is>
+      </c>
+      <c r="B211" s="27" t="n"/>
+      <c r="C211" s="27" t="n"/>
+      <c r="D211" s="27" t="n"/>
+      <c r="E211" s="27" t="n"/>
+      <c r="F211" s="27" t="n"/>
+      <c r="G211" s="27" t="n"/>
+      <c r="H211" s="27" t="n"/>
+      <c r="I211" s="27" t="n"/>
+      <c r="J211" s="57" t="n"/>
+    </row>
+    <row r="212" ht="22" customHeight="1" s="6">
+      <c r="A212" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B212" s="27" t="n"/>
+      <c r="C212" s="27" t="n"/>
+      <c r="D212" s="27" t="n"/>
+      <c r="E212" s="27" t="n"/>
+      <c r="F212" s="27" t="n"/>
+      <c r="G212" s="27" t="n"/>
+      <c r="H212" s="27" t="n"/>
+      <c r="I212" s="27" t="n"/>
+      <c r="J212" s="57" t="n"/>
+    </row>
+    <row r="213" ht="22" customHeight="1" s="6">
+      <c r="A213" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ）：</t>
+        </is>
+      </c>
+      <c r="B213" s="27" t="n"/>
+      <c r="C213" s="27" t="n"/>
+      <c r="D213" s="27" t="n"/>
+      <c r="E213" s="27" t="n"/>
+      <c r="F213" s="27" t="n"/>
+      <c r="G213" s="27" t="n"/>
+      <c r="H213" s="27" t="n"/>
+      <c r="I213" s="27" t="n"/>
+      <c r="J213" s="57" t="n"/>
+    </row>
+    <row r="214" ht="22" customHeight="1" s="6">
+      <c r="A214" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
+        </is>
+      </c>
+      <c r="B214" s="27" t="n"/>
+      <c r="C214" s="27" t="n"/>
+      <c r="D214" s="27" t="n"/>
+      <c r="E214" s="27" t="n"/>
+      <c r="F214" s="27" t="n"/>
+      <c r="G214" s="27" t="n"/>
+      <c r="H214" s="27" t="n"/>
+      <c r="I214" s="27" t="n"/>
+      <c r="J214" s="57" t="n"/>
+    </row>
+    <row r="215" ht="18" customHeight="1" s="6">
+      <c r="A215" s="11" t="inlineStr">
+        <is>
+          <t>リョウタロウは京都を訪れたことがありますか。</t>
+        </is>
+      </c>
+      <c r="B215" s="27" t="n"/>
+      <c r="C215" s="27" t="n"/>
+      <c r="D215" s="27" t="n"/>
+      <c r="E215" s="27" t="n"/>
+      <c r="F215" s="27" t="n"/>
+      <c r="G215" s="27" t="n"/>
+      <c r="H215" s="27" t="n"/>
+      <c r="I215" s="27" t="n"/>
+      <c r="J215" s="57" t="n"/>
+    </row>
+    <row r="216" ht="22" customHeight="1" s="6">
+      <c r="A216" s="11" t="inlineStr">
+        <is>
+          <t>回答（疑問文）：</t>
+        </is>
+      </c>
+      <c r="B216" s="27" t="n"/>
+      <c r="C216" s="27" t="n"/>
+      <c r="D216" s="27" t="n"/>
+      <c r="E216" s="27" t="n"/>
+      <c r="F216" s="27" t="n"/>
+      <c r="G216" s="27" t="n"/>
+      <c r="H216" s="27" t="n"/>
+      <c r="I216" s="27" t="n"/>
+      <c r="J216" s="57" t="n"/>
+    </row>
+    <row r="217" ht="18" customHeight="1" s="6">
+      <c r="A217" s="11" t="inlineStr">
+        <is>
+          <t>はい、あります。</t>
+        </is>
+      </c>
+      <c r="B217" s="27" t="n"/>
+      <c r="C217" s="27" t="n"/>
+      <c r="D217" s="27" t="n"/>
+      <c r="E217" s="27" t="n"/>
+      <c r="F217" s="27" t="n"/>
+      <c r="G217" s="27" t="n"/>
+      <c r="H217" s="27" t="n"/>
+      <c r="I217" s="27" t="n"/>
+      <c r="J217" s="57" t="n"/>
+    </row>
+    <row r="218" ht="22" customHeight="1" s="6">
+      <c r="A218" s="11" t="inlineStr">
+        <is>
+          <t>回答（返答）：</t>
+        </is>
+      </c>
+      <c r="B218" s="27" t="n"/>
+      <c r="C218" s="27" t="n"/>
+      <c r="D218" s="27" t="n"/>
+      <c r="E218" s="27" t="n"/>
+      <c r="F218" s="27" t="n"/>
+      <c r="G218" s="27" t="n"/>
+      <c r="H218" s="27" t="n"/>
+      <c r="I218" s="27" t="n"/>
+      <c r="J218" s="57" t="n"/>
+    </row>
+    <row r="219" ht="18" customHeight="1" s="6">
+      <c r="A219" s="11" t="inlineStr">
+        <is>
+          <t>いいえ、ありません。</t>
+        </is>
+      </c>
+      <c r="B219" s="27" t="n"/>
+      <c r="C219" s="27" t="n"/>
+      <c r="D219" s="27" t="n"/>
+      <c r="E219" s="27" t="n"/>
+      <c r="F219" s="27" t="n"/>
+      <c r="G219" s="27" t="n"/>
+      <c r="H219" s="27" t="n"/>
+      <c r="I219" s="27" t="n"/>
+      <c r="J219" s="57" t="n"/>
+    </row>
+    <row r="220" ht="22" customHeight="1" s="6">
+      <c r="A220" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B220" s="27" t="n"/>
+      <c r="C220" s="27" t="n"/>
+      <c r="D220" s="27" t="n"/>
+      <c r="E220" s="27" t="n"/>
+      <c r="F220" s="27" t="n"/>
+      <c r="G220" s="27" t="n"/>
+      <c r="H220" s="27" t="n"/>
+      <c r="I220" s="27" t="n"/>
+      <c r="J220" s="57" t="n"/>
+    </row>
+    <row r="221" ht="22" customHeight="1" s="6">
+      <c r="A221" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ）：</t>
+        </is>
+      </c>
+      <c r="B221" s="27" t="n"/>
+      <c r="C221" s="27" t="n"/>
+      <c r="D221" s="27" t="n"/>
+      <c r="E221" s="27" t="n"/>
+      <c r="F221" s="27" t="n"/>
+      <c r="G221" s="27" t="n"/>
+      <c r="H221" s="27" t="n"/>
+      <c r="I221" s="27" t="n"/>
+      <c r="J221" s="57" t="n"/>
+    </row>
+    <row r="222" ht="22" customHeight="1" s="6">
+      <c r="A222" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
+        </is>
+      </c>
+      <c r="B222" s="27" t="n"/>
+      <c r="C222" s="27" t="n"/>
+      <c r="D222" s="27" t="n"/>
+      <c r="E222" s="27" t="n"/>
+      <c r="F222" s="27" t="n"/>
+      <c r="G222" s="27" t="n"/>
+      <c r="H222" s="27" t="n"/>
+      <c r="I222" s="27" t="n"/>
+      <c r="J222" s="57" t="n"/>
+    </row>
+    <row r="223" ht="18" customHeight="1" s="6">
+      <c r="A223" s="9" t="inlineStr">
+        <is>
+          <t>【回数】何回訪れたことがあるか</t>
+        </is>
+      </c>
+      <c r="B223" s="25" t="n"/>
+      <c r="C223" s="25" t="n"/>
+      <c r="D223" s="25" t="n"/>
+      <c r="E223" s="25" t="n"/>
+      <c r="F223" s="25" t="n"/>
+      <c r="G223" s="25" t="n"/>
+      <c r="H223" s="25" t="n"/>
+      <c r="I223" s="25" t="n"/>
+      <c r="J223" s="56" t="n"/>
+    </row>
+    <row r="224" ht="18" customHeight="1" s="6">
+      <c r="A224" s="11" t="inlineStr">
+        <is>
+          <t>リョウタロウは京都を4回訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B224" s="27" t="n"/>
+      <c r="C224" s="27" t="n"/>
+      <c r="D224" s="27" t="n"/>
+      <c r="E224" s="27" t="n"/>
+      <c r="F224" s="27" t="n"/>
+      <c r="G224" s="27" t="n"/>
+      <c r="H224" s="27" t="n"/>
+      <c r="I224" s="27" t="n"/>
+      <c r="J224" s="57" t="n"/>
+    </row>
+    <row r="225" ht="22" customHeight="1" s="6">
+      <c r="A225" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B225" s="27" t="n"/>
+      <c r="C225" s="27" t="n"/>
+      <c r="D225" s="27" t="n"/>
+      <c r="E225" s="27" t="n"/>
+      <c r="F225" s="27" t="n"/>
+      <c r="G225" s="27" t="n"/>
+      <c r="H225" s="27" t="n"/>
+      <c r="I225" s="27" t="n"/>
+      <c r="J225" s="57" t="n"/>
+    </row>
+    <row r="226" ht="18" customHeight="1" s="6">
+      <c r="A226" s="11" t="inlineStr">
+        <is>
+          <t>リョウタロウは京都を何回訪れたことがありますか。</t>
+        </is>
+      </c>
+      <c r="B226" s="27" t="n"/>
+      <c r="C226" s="27" t="n"/>
+      <c r="D226" s="27" t="n"/>
+      <c r="E226" s="27" t="n"/>
+      <c r="F226" s="27" t="n"/>
+      <c r="G226" s="27" t="n"/>
+      <c r="H226" s="27" t="n"/>
+      <c r="I226" s="27" t="n"/>
+      <c r="J226" s="57" t="n"/>
+    </row>
+    <row r="227" ht="22" customHeight="1" s="6">
+      <c r="A227" s="11" t="inlineStr">
+        <is>
+          <t>回答（疑問文）：</t>
+        </is>
+      </c>
+      <c r="B227" s="27" t="n"/>
+      <c r="C227" s="27" t="n"/>
+      <c r="D227" s="27" t="n"/>
+      <c r="E227" s="27" t="n"/>
+      <c r="F227" s="27" t="n"/>
+      <c r="G227" s="27" t="n"/>
+      <c r="H227" s="27" t="n"/>
+      <c r="I227" s="27" t="n"/>
+      <c r="J227" s="57" t="n"/>
+    </row>
+    <row r="228" ht="18" customHeight="1" s="6">
+      <c r="A228" s="11" t="inlineStr">
+        <is>
+          <t>5回訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B228" s="27" t="n"/>
+      <c r="C228" s="27" t="n"/>
+      <c r="D228" s="27" t="n"/>
+      <c r="E228" s="27" t="n"/>
+      <c r="F228" s="27" t="n"/>
+      <c r="G228" s="27" t="n"/>
+      <c r="H228" s="27" t="n"/>
+      <c r="I228" s="27" t="n"/>
+      <c r="J228" s="57" t="n"/>
+    </row>
+    <row r="229" ht="22" customHeight="1" s="6">
+      <c r="A229" s="11" t="inlineStr">
+        <is>
+          <t>回答（返答）：</t>
+        </is>
+      </c>
+      <c r="B229" s="27" t="n"/>
+      <c r="C229" s="27" t="n"/>
+      <c r="D229" s="27" t="n"/>
+      <c r="E229" s="27" t="n"/>
+      <c r="F229" s="27" t="n"/>
+      <c r="G229" s="27" t="n"/>
+      <c r="H229" s="27" t="n"/>
+      <c r="I229" s="27" t="n"/>
+      <c r="J229" s="57" t="n"/>
+    </row>
+    <row r="230" ht="18" customHeight="1" s="6">
+      <c r="A230" s="11" t="inlineStr">
+        <is>
+          <t>一度も訪れたことがありません。</t>
+        </is>
+      </c>
+      <c r="B230" s="27" t="n"/>
+      <c r="C230" s="27" t="n"/>
+      <c r="D230" s="27" t="n"/>
+      <c r="E230" s="27" t="n"/>
+      <c r="F230" s="27" t="n"/>
+      <c r="G230" s="27" t="n"/>
+      <c r="H230" s="27" t="n"/>
+      <c r="I230" s="27" t="n"/>
+      <c r="J230" s="57" t="n"/>
+    </row>
+    <row r="231" ht="22" customHeight="1" s="6">
+      <c r="A231" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B231" s="27" t="n"/>
+      <c r="C231" s="27" t="n"/>
+      <c r="D231" s="27" t="n"/>
+      <c r="E231" s="27" t="n"/>
+      <c r="F231" s="27" t="n"/>
+      <c r="G231" s="27" t="n"/>
+      <c r="H231" s="27" t="n"/>
+      <c r="I231" s="27" t="n"/>
+      <c r="J231" s="57" t="n"/>
+    </row>
+    <row r="232" ht="22" customHeight="1" s="6">
+      <c r="A232" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ）：</t>
+        </is>
+      </c>
+      <c r="B232" s="27" t="n"/>
+      <c r="C232" s="27" t="n"/>
+      <c r="D232" s="27" t="n"/>
+      <c r="E232" s="27" t="n"/>
+      <c r="F232" s="27" t="n"/>
+      <c r="G232" s="27" t="n"/>
+      <c r="H232" s="27" t="n"/>
+      <c r="I232" s="27" t="n"/>
+      <c r="J232" s="57" t="n"/>
+    </row>
+    <row r="233" ht="22" customHeight="1" s="6">
+      <c r="A233" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
+        </is>
+      </c>
+      <c r="B233" s="27" t="n"/>
+      <c r="C233" s="27" t="n"/>
+      <c r="D233" s="27" t="n"/>
+      <c r="E233" s="27" t="n"/>
+      <c r="F233" s="27" t="n"/>
+      <c r="G233" s="27" t="n"/>
+      <c r="H233" s="27" t="n"/>
+      <c r="I233" s="27" t="n"/>
+      <c r="J233" s="57" t="n"/>
+    </row>
+    <row r="234" ht="6" customHeight="1" s="6">
+      <c r="A234" s="11" t="n"/>
+      <c r="B234" s="27" t="n"/>
+      <c r="C234" s="27" t="n"/>
+      <c r="D234" s="27" t="n"/>
+      <c r="E234" s="27" t="n"/>
+      <c r="F234" s="27" t="n"/>
+      <c r="G234" s="27" t="n"/>
+      <c r="H234" s="27" t="n"/>
+      <c r="I234" s="27" t="n"/>
+      <c r="J234" s="57" t="n"/>
+    </row>
+    <row r="235" ht="18" customHeight="1" s="6">
+      <c r="A235" s="9" t="inlineStr">
+        <is>
+          <t>9．主語は「チサコ」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B235" s="25" t="n"/>
+      <c r="C235" s="25" t="n"/>
+      <c r="D235" s="25" t="n"/>
+      <c r="E235" s="25" t="n"/>
+      <c r="F235" s="25" t="n"/>
+      <c r="G235" s="25" t="n"/>
+      <c r="H235" s="25" t="n"/>
+      <c r="I235" s="25" t="n"/>
+      <c r="J235" s="56" t="n"/>
+    </row>
+    <row r="236" ht="60" customHeight="1" s="6">
+      <c r="A236" s="55" t="inlineStr">
+        <is>
+          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
+※疑問文では ever、否定では never または not ... before を使います。
+※回数は four times / five times のように表します。</t>
+        </is>
+      </c>
+      <c r="B236" s="27" t="n"/>
+      <c r="C236" s="27" t="n"/>
+      <c r="D236" s="27" t="n"/>
+      <c r="E236" s="27" t="n"/>
+      <c r="F236" s="27" t="n"/>
+      <c r="G236" s="27" t="n"/>
+      <c r="H236" s="27" t="n"/>
+      <c r="I236" s="27" t="n"/>
+      <c r="J236" s="57" t="n"/>
+    </row>
+    <row r="237" ht="18" customHeight="1" s="6">
+      <c r="A237" s="9" t="inlineStr">
+        <is>
+          <t>【基本】訪れたことがある・ない</t>
+        </is>
+      </c>
+      <c r="B237" s="25" t="n"/>
+      <c r="C237" s="25" t="n"/>
+      <c r="D237" s="25" t="n"/>
+      <c r="E237" s="25" t="n"/>
+      <c r="F237" s="25" t="n"/>
+      <c r="G237" s="25" t="n"/>
+      <c r="H237" s="25" t="n"/>
+      <c r="I237" s="25" t="n"/>
+      <c r="J237" s="56" t="n"/>
+    </row>
+    <row r="238" ht="18" customHeight="1" s="6">
+      <c r="A238" s="11" t="inlineStr">
+        <is>
+          <t>チサコは京都を訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B238" s="27" t="n"/>
+      <c r="C238" s="27" t="n"/>
+      <c r="D238" s="27" t="n"/>
+      <c r="E238" s="27" t="n"/>
+      <c r="F238" s="27" t="n"/>
+      <c r="G238" s="27" t="n"/>
+      <c r="H238" s="27" t="n"/>
+      <c r="I238" s="27" t="n"/>
+      <c r="J238" s="57" t="n"/>
+    </row>
+    <row r="239" ht="22" customHeight="1" s="6">
+      <c r="A239" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B239" s="27" t="n"/>
+      <c r="C239" s="27" t="n"/>
+      <c r="D239" s="27" t="n"/>
+      <c r="E239" s="27" t="n"/>
+      <c r="F239" s="27" t="n"/>
+      <c r="G239" s="27" t="n"/>
+      <c r="H239" s="27" t="n"/>
+      <c r="I239" s="27" t="n"/>
+      <c r="J239" s="57" t="n"/>
+    </row>
+    <row r="240" ht="18" customHeight="1" s="6">
+      <c r="A240" s="11" t="inlineStr">
+        <is>
+          <t>チサコはまだ一度も京都を訪れたことがありません。</t>
+        </is>
+      </c>
+      <c r="B240" s="27" t="n"/>
+      <c r="C240" s="27" t="n"/>
+      <c r="D240" s="27" t="n"/>
+      <c r="E240" s="27" t="n"/>
+      <c r="F240" s="27" t="n"/>
+      <c r="G240" s="27" t="n"/>
+      <c r="H240" s="27" t="n"/>
+      <c r="I240" s="27" t="n"/>
+      <c r="J240" s="57" t="n"/>
+    </row>
+    <row r="241" ht="22" customHeight="1" s="6">
+      <c r="A241" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B241" s="27" t="n"/>
+      <c r="C241" s="27" t="n"/>
+      <c r="D241" s="27" t="n"/>
+      <c r="E241" s="27" t="n"/>
+      <c r="F241" s="27" t="n"/>
+      <c r="G241" s="27" t="n"/>
+      <c r="H241" s="27" t="n"/>
+      <c r="I241" s="27" t="n"/>
+      <c r="J241" s="57" t="n"/>
+    </row>
+    <row r="242" ht="22" customHeight="1" s="6">
+      <c r="A242" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ）：</t>
+        </is>
+      </c>
+      <c r="B242" s="27" t="n"/>
+      <c r="C242" s="27" t="n"/>
+      <c r="D242" s="27" t="n"/>
+      <c r="E242" s="27" t="n"/>
+      <c r="F242" s="27" t="n"/>
+      <c r="G242" s="27" t="n"/>
+      <c r="H242" s="27" t="n"/>
+      <c r="I242" s="27" t="n"/>
+      <c r="J242" s="57" t="n"/>
+    </row>
+    <row r="243" ht="22" customHeight="1" s="6">
+      <c r="A243" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
+        </is>
+      </c>
+      <c r="B243" s="27" t="n"/>
+      <c r="C243" s="27" t="n"/>
+      <c r="D243" s="27" t="n"/>
+      <c r="E243" s="27" t="n"/>
+      <c r="F243" s="27" t="n"/>
+      <c r="G243" s="27" t="n"/>
+      <c r="H243" s="27" t="n"/>
+      <c r="I243" s="27" t="n"/>
+      <c r="J243" s="57" t="n"/>
+    </row>
+    <row r="244" ht="18" customHeight="1" s="6">
+      <c r="A244" s="11" t="inlineStr">
+        <is>
+          <t>チサコは京都を訪れたことがありますか。</t>
+        </is>
+      </c>
+      <c r="B244" s="27" t="n"/>
+      <c r="C244" s="27" t="n"/>
+      <c r="D244" s="27" t="n"/>
+      <c r="E244" s="27" t="n"/>
+      <c r="F244" s="27" t="n"/>
+      <c r="G244" s="27" t="n"/>
+      <c r="H244" s="27" t="n"/>
+      <c r="I244" s="27" t="n"/>
+      <c r="J244" s="57" t="n"/>
+    </row>
+    <row r="245" ht="22" customHeight="1" s="6">
+      <c r="A245" s="11" t="inlineStr">
+        <is>
+          <t>回答（疑問文）：</t>
+        </is>
+      </c>
+      <c r="B245" s="27" t="n"/>
+      <c r="C245" s="27" t="n"/>
+      <c r="D245" s="27" t="n"/>
+      <c r="E245" s="27" t="n"/>
+      <c r="F245" s="27" t="n"/>
+      <c r="G245" s="27" t="n"/>
+      <c r="H245" s="27" t="n"/>
+      <c r="I245" s="27" t="n"/>
+      <c r="J245" s="57" t="n"/>
+    </row>
+    <row r="246" ht="18" customHeight="1" s="6">
+      <c r="A246" s="11" t="inlineStr">
+        <is>
+          <t>はい、あります。</t>
+        </is>
+      </c>
+      <c r="B246" s="27" t="n"/>
+      <c r="C246" s="27" t="n"/>
+      <c r="D246" s="27" t="n"/>
+      <c r="E246" s="27" t="n"/>
+      <c r="F246" s="27" t="n"/>
+      <c r="G246" s="27" t="n"/>
+      <c r="H246" s="27" t="n"/>
+      <c r="I246" s="27" t="n"/>
+      <c r="J246" s="57" t="n"/>
+    </row>
+    <row r="247" ht="22" customHeight="1" s="6">
+      <c r="A247" s="11" t="inlineStr">
+        <is>
+          <t>回答（返答）：</t>
+        </is>
+      </c>
+      <c r="B247" s="27" t="n"/>
+      <c r="C247" s="27" t="n"/>
+      <c r="D247" s="27" t="n"/>
+      <c r="E247" s="27" t="n"/>
+      <c r="F247" s="27" t="n"/>
+      <c r="G247" s="27" t="n"/>
+      <c r="H247" s="27" t="n"/>
+      <c r="I247" s="27" t="n"/>
+      <c r="J247" s="57" t="n"/>
+    </row>
+    <row r="248" ht="18" customHeight="1" s="6">
+      <c r="A248" s="11" t="inlineStr">
+        <is>
+          <t>いいえ、ありません。</t>
+        </is>
+      </c>
+      <c r="B248" s="27" t="n"/>
+      <c r="C248" s="27" t="n"/>
+      <c r="D248" s="27" t="n"/>
+      <c r="E248" s="27" t="n"/>
+      <c r="F248" s="27" t="n"/>
+      <c r="G248" s="27" t="n"/>
+      <c r="H248" s="27" t="n"/>
+      <c r="I248" s="27" t="n"/>
+      <c r="J248" s="57" t="n"/>
+    </row>
+    <row r="249" ht="22" customHeight="1" s="6">
+      <c r="A249" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B249" s="27" t="n"/>
+      <c r="C249" s="27" t="n"/>
+      <c r="D249" s="27" t="n"/>
+      <c r="E249" s="27" t="n"/>
+      <c r="F249" s="27" t="n"/>
+      <c r="G249" s="27" t="n"/>
+      <c r="H249" s="27" t="n"/>
+      <c r="I249" s="27" t="n"/>
+      <c r="J249" s="57" t="n"/>
+    </row>
+    <row r="250" ht="22" customHeight="1" s="6">
+      <c r="A250" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ）：</t>
+        </is>
+      </c>
+      <c r="B250" s="27" t="n"/>
+      <c r="C250" s="27" t="n"/>
+      <c r="D250" s="27" t="n"/>
+      <c r="E250" s="27" t="n"/>
+      <c r="F250" s="27" t="n"/>
+      <c r="G250" s="27" t="n"/>
+      <c r="H250" s="27" t="n"/>
+      <c r="I250" s="27" t="n"/>
+      <c r="J250" s="57" t="n"/>
+    </row>
+    <row r="251" ht="22" customHeight="1" s="6">
+      <c r="A251" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
+        </is>
+      </c>
+      <c r="B251" s="27" t="n"/>
+      <c r="C251" s="27" t="n"/>
+      <c r="D251" s="27" t="n"/>
+      <c r="E251" s="27" t="n"/>
+      <c r="F251" s="27" t="n"/>
+      <c r="G251" s="27" t="n"/>
+      <c r="H251" s="27" t="n"/>
+      <c r="I251" s="27" t="n"/>
+      <c r="J251" s="57" t="n"/>
+    </row>
+    <row r="252" ht="18" customHeight="1" s="6">
+      <c r="A252" s="9" t="inlineStr">
+        <is>
+          <t>【回数】何回訪れたことがあるか</t>
+        </is>
+      </c>
+      <c r="B252" s="25" t="n"/>
+      <c r="C252" s="25" t="n"/>
+      <c r="D252" s="25" t="n"/>
+      <c r="E252" s="25" t="n"/>
+      <c r="F252" s="25" t="n"/>
+      <c r="G252" s="25" t="n"/>
+      <c r="H252" s="25" t="n"/>
+      <c r="I252" s="25" t="n"/>
+      <c r="J252" s="56" t="n"/>
+    </row>
+    <row r="253" ht="18" customHeight="1" s="6">
+      <c r="A253" s="11" t="inlineStr">
+        <is>
+          <t>チサコは京都を4回訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B253" s="27" t="n"/>
+      <c r="C253" s="27" t="n"/>
+      <c r="D253" s="27" t="n"/>
+      <c r="E253" s="27" t="n"/>
+      <c r="F253" s="27" t="n"/>
+      <c r="G253" s="27" t="n"/>
+      <c r="H253" s="27" t="n"/>
+      <c r="I253" s="27" t="n"/>
+      <c r="J253" s="57" t="n"/>
+    </row>
+    <row r="254" ht="22" customHeight="1" s="6">
+      <c r="A254" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B254" s="27" t="n"/>
+      <c r="C254" s="27" t="n"/>
+      <c r="D254" s="27" t="n"/>
+      <c r="E254" s="27" t="n"/>
+      <c r="F254" s="27" t="n"/>
+      <c r="G254" s="27" t="n"/>
+      <c r="H254" s="27" t="n"/>
+      <c r="I254" s="27" t="n"/>
+      <c r="J254" s="57" t="n"/>
+    </row>
+    <row r="255" ht="18" customHeight="1" s="6">
+      <c r="A255" s="11" t="inlineStr">
+        <is>
+          <t>チサコは京都を何回訪れたことがありますか。</t>
+        </is>
+      </c>
+      <c r="B255" s="27" t="n"/>
+      <c r="C255" s="27" t="n"/>
+      <c r="D255" s="27" t="n"/>
+      <c r="E255" s="27" t="n"/>
+      <c r="F255" s="27" t="n"/>
+      <c r="G255" s="27" t="n"/>
+      <c r="H255" s="27" t="n"/>
+      <c r="I255" s="27" t="n"/>
+      <c r="J255" s="57" t="n"/>
+    </row>
+    <row r="256" ht="22" customHeight="1" s="6">
+      <c r="A256" s="11" t="inlineStr">
+        <is>
+          <t>回答（疑問文）：</t>
+        </is>
+      </c>
+      <c r="B256" s="27" t="n"/>
+      <c r="C256" s="27" t="n"/>
+      <c r="D256" s="27" t="n"/>
+      <c r="E256" s="27" t="n"/>
+      <c r="F256" s="27" t="n"/>
+      <c r="G256" s="27" t="n"/>
+      <c r="H256" s="27" t="n"/>
+      <c r="I256" s="27" t="n"/>
+      <c r="J256" s="57" t="n"/>
+    </row>
+    <row r="257" ht="18" customHeight="1" s="6">
+      <c r="A257" s="11" t="inlineStr">
+        <is>
+          <t>5回訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B257" s="27" t="n"/>
+      <c r="C257" s="27" t="n"/>
+      <c r="D257" s="27" t="n"/>
+      <c r="E257" s="27" t="n"/>
+      <c r="F257" s="27" t="n"/>
+      <c r="G257" s="27" t="n"/>
+      <c r="H257" s="27" t="n"/>
+      <c r="I257" s="27" t="n"/>
+      <c r="J257" s="57" t="n"/>
+    </row>
+    <row r="258" ht="22" customHeight="1" s="6">
+      <c r="A258" s="11" t="inlineStr">
+        <is>
+          <t>回答（返答）：</t>
+        </is>
+      </c>
+      <c r="B258" s="27" t="n"/>
+      <c r="C258" s="27" t="n"/>
+      <c r="D258" s="27" t="n"/>
+      <c r="E258" s="27" t="n"/>
+      <c r="F258" s="27" t="n"/>
+      <c r="G258" s="27" t="n"/>
+      <c r="H258" s="27" t="n"/>
+      <c r="I258" s="27" t="n"/>
+      <c r="J258" s="57" t="n"/>
+    </row>
+    <row r="259" ht="18" customHeight="1" s="6">
+      <c r="A259" s="11" t="inlineStr">
+        <is>
+          <t>一度も訪れたことがありません。</t>
+        </is>
+      </c>
+      <c r="B259" s="27" t="n"/>
+      <c r="C259" s="27" t="n"/>
+      <c r="D259" s="27" t="n"/>
+      <c r="E259" s="27" t="n"/>
+      <c r="F259" s="27" t="n"/>
+      <c r="G259" s="27" t="n"/>
+      <c r="H259" s="27" t="n"/>
+      <c r="I259" s="27" t="n"/>
+      <c r="J259" s="57" t="n"/>
+    </row>
+    <row r="260" ht="22" customHeight="1" s="6">
+      <c r="A260" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B260" s="27" t="n"/>
+      <c r="C260" s="27" t="n"/>
+      <c r="D260" s="27" t="n"/>
+      <c r="E260" s="27" t="n"/>
+      <c r="F260" s="27" t="n"/>
+      <c r="G260" s="27" t="n"/>
+      <c r="H260" s="27" t="n"/>
+      <c r="I260" s="27" t="n"/>
+      <c r="J260" s="57" t="n"/>
+    </row>
+    <row r="261" ht="22" customHeight="1" s="6">
+      <c r="A261" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ）：</t>
+        </is>
+      </c>
+      <c r="B261" s="27" t="n"/>
+      <c r="C261" s="27" t="n"/>
+      <c r="D261" s="27" t="n"/>
+      <c r="E261" s="27" t="n"/>
+      <c r="F261" s="27" t="n"/>
+      <c r="G261" s="27" t="n"/>
+      <c r="H261" s="27" t="n"/>
+      <c r="I261" s="27" t="n"/>
+      <c r="J261" s="57" t="n"/>
+    </row>
+    <row r="262" ht="22" customHeight="1" s="6">
+      <c r="A262" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
+        </is>
+      </c>
+      <c r="B262" s="27" t="n"/>
+      <c r="C262" s="27" t="n"/>
+      <c r="D262" s="27" t="n"/>
+      <c r="E262" s="27" t="n"/>
+      <c r="F262" s="27" t="n"/>
+      <c r="G262" s="27" t="n"/>
+      <c r="H262" s="27" t="n"/>
+      <c r="I262" s="27" t="n"/>
+      <c r="J262" s="57" t="n"/>
+    </row>
+    <row r="263" ht="6" customHeight="1" s="6">
+      <c r="A263" s="11" t="n"/>
+      <c r="B263" s="27" t="n"/>
+      <c r="C263" s="27" t="n"/>
+      <c r="D263" s="27" t="n"/>
+      <c r="E263" s="27" t="n"/>
+      <c r="F263" s="27" t="n"/>
+      <c r="G263" s="27" t="n"/>
+      <c r="H263" s="27" t="n"/>
+      <c r="I263" s="27" t="n"/>
+      <c r="J263" s="57" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="155">
+  <mergeCells count="263">
     <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A194:J194"/>
+    <mergeCell ref="A234:J234"/>
+    <mergeCell ref="A181:J181"/>
     <mergeCell ref="A91:J91"/>
+    <mergeCell ref="A184:J184"/>
     <mergeCell ref="A43:J43"/>
+    <mergeCell ref="A156:J156"/>
+    <mergeCell ref="A171:J171"/>
+    <mergeCell ref="A165:J165"/>
     <mergeCell ref="A52:J52"/>
     <mergeCell ref="A63:J63"/>
+    <mergeCell ref="A155:J155"/>
     <mergeCell ref="A115:J115"/>
-    <mergeCell ref="A155:J155"/>
     <mergeCell ref="A93:J93"/>
+    <mergeCell ref="A220:J220"/>
+    <mergeCell ref="A173:J173"/>
+    <mergeCell ref="A229:J229"/>
     <mergeCell ref="A130:J130"/>
     <mergeCell ref="A77:J77"/>
+    <mergeCell ref="A83:J83"/>
     <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A83:J83"/>
     <mergeCell ref="A148:J148"/>
+    <mergeCell ref="A261:J261"/>
+    <mergeCell ref="A157:J157"/>
+    <mergeCell ref="A222:J222"/>
+    <mergeCell ref="A138:J138"/>
     <mergeCell ref="A49:J49"/>
-    <mergeCell ref="A138:J138"/>
     <mergeCell ref="A132:J132"/>
     <mergeCell ref="A36:J36"/>
     <mergeCell ref="A119:J119"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A69:J69"/>
+    <mergeCell ref="A196:J196"/>
+    <mergeCell ref="A174:J174"/>
+    <mergeCell ref="A256:J256"/>
+    <mergeCell ref="A205:J205"/>
+    <mergeCell ref="A183:J183"/>
     <mergeCell ref="A66:J66"/>
     <mergeCell ref="A118:J118"/>
     <mergeCell ref="A75:J75"/>
     <mergeCell ref="A133:J133"/>
+    <mergeCell ref="A246:J246"/>
+    <mergeCell ref="A198:J198"/>
+    <mergeCell ref="A233:J233"/>
+    <mergeCell ref="A238:J238"/>
     <mergeCell ref="A120:J120"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A55:J55"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A239:J239"/>
     <mergeCell ref="A95:J95"/>
+    <mergeCell ref="A248:J248"/>
     <mergeCell ref="A104:J104"/>
+    <mergeCell ref="A175:J175"/>
     <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A263:J263"/>
     <mergeCell ref="A32:J32"/>
     <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A159:J159"/>
     <mergeCell ref="A97:J97"/>
+    <mergeCell ref="A219:J219"/>
+    <mergeCell ref="A224:J224"/>
     <mergeCell ref="A106:J106"/>
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A200:J200"/>
     <mergeCell ref="A81:J81"/>
+    <mergeCell ref="A209:J209"/>
+    <mergeCell ref="A96:J96"/>
     <mergeCell ref="A38:J38"/>
-    <mergeCell ref="A96:J96"/>
     <mergeCell ref="A121:J121"/>
     <mergeCell ref="A147:J147"/>
+    <mergeCell ref="A161:J161"/>
     <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A170:J170"/>
     <mergeCell ref="A44:J44"/>
     <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A202:J202"/>
     <mergeCell ref="A58:J58"/>
+    <mergeCell ref="A258:J258"/>
     <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A211:J211"/>
     <mergeCell ref="A67:J67"/>
     <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A186:J186"/>
+    <mergeCell ref="A257:J257"/>
     <mergeCell ref="A73:J73"/>
     <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A201:J201"/>
+    <mergeCell ref="A226:J226"/>
     <mergeCell ref="A82:J82"/>
+    <mergeCell ref="A260:J260"/>
     <mergeCell ref="A60:J60"/>
+    <mergeCell ref="A241:J241"/>
     <mergeCell ref="A123:J123"/>
+    <mergeCell ref="A250:J250"/>
+    <mergeCell ref="A197:J197"/>
+    <mergeCell ref="A228:J228"/>
     <mergeCell ref="A110:J110"/>
     <mergeCell ref="A146:J146"/>
     <mergeCell ref="A124:J124"/>
+    <mergeCell ref="A237:J237"/>
     <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A172:J172"/>
     <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A187:J187"/>
+    <mergeCell ref="A212:J212"/>
+    <mergeCell ref="A221:J221"/>
     <mergeCell ref="A25:J25"/>
+    <mergeCell ref="A243:J243"/>
+    <mergeCell ref="A252:J252"/>
     <mergeCell ref="A108:J108"/>
     <mergeCell ref="A84:J84"/>
+    <mergeCell ref="A236:J236"/>
     <mergeCell ref="A149:J149"/>
+    <mergeCell ref="A214:J214"/>
     <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A189:J189"/>
+    <mergeCell ref="A158:J158"/>
+    <mergeCell ref="A223:J223"/>
     <mergeCell ref="A50:J50"/>
+    <mergeCell ref="A204:J204"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A86:J86"/>
     <mergeCell ref="A42:J42"/>
+    <mergeCell ref="A213:J213"/>
     <mergeCell ref="A151:J151"/>
     <mergeCell ref="A47:J47"/>
+    <mergeCell ref="A160:J160"/>
     <mergeCell ref="A141:J141"/>
+    <mergeCell ref="A254:J254"/>
     <mergeCell ref="A135:J135"/>
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="A150:J150"/>
+    <mergeCell ref="A206:J206"/>
+    <mergeCell ref="A144:J144"/>
     <mergeCell ref="A62:J62"/>
-    <mergeCell ref="A144:J144"/>
     <mergeCell ref="A122:J122"/>
+    <mergeCell ref="A215:J215"/>
+    <mergeCell ref="A262:J262"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A125:J125"/>
+    <mergeCell ref="A190:J190"/>
     <mergeCell ref="A72:J72"/>
     <mergeCell ref="A134:J134"/>
+    <mergeCell ref="A199:J199"/>
     <mergeCell ref="A28:J28"/>
     <mergeCell ref="A112:J112"/>
     <mergeCell ref="A152:J152"/>
     <mergeCell ref="A127:J127"/>
+    <mergeCell ref="A167:J167"/>
+    <mergeCell ref="A249:J249"/>
+    <mergeCell ref="A176:J176"/>
     <mergeCell ref="A30:J30"/>
     <mergeCell ref="A114:J114"/>
     <mergeCell ref="A59:J59"/>
+    <mergeCell ref="A182:J182"/>
     <mergeCell ref="A64:J64"/>
     <mergeCell ref="A98:J98"/>
+    <mergeCell ref="A191:J191"/>
+    <mergeCell ref="A169:J169"/>
+    <mergeCell ref="A225:J225"/>
     <mergeCell ref="A51:J51"/>
     <mergeCell ref="A107:J107"/>
+    <mergeCell ref="A178:J178"/>
     <mergeCell ref="A79:J79"/>
     <mergeCell ref="A61:J61"/>
     <mergeCell ref="A88:J88"/>
     <mergeCell ref="A70:J70"/>
     <mergeCell ref="A153:J153"/>
+    <mergeCell ref="A162:J162"/>
+    <mergeCell ref="A227:J227"/>
     <mergeCell ref="A54:J54"/>
     <mergeCell ref="A137:J137"/>
+    <mergeCell ref="A177:J177"/>
     <mergeCell ref="A90:J90"/>
     <mergeCell ref="A41:J41"/>
+    <mergeCell ref="A217:J217"/>
     <mergeCell ref="A99:J99"/>
+    <mergeCell ref="A164:J164"/>
     <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A145:J145"/>
     <mergeCell ref="A56:J56"/>
     <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A145:J145"/>
     <mergeCell ref="A139:J139"/>
     <mergeCell ref="A154:J154"/>
+    <mergeCell ref="A163:J163"/>
     <mergeCell ref="A101:J101"/>
+    <mergeCell ref="A242:J242"/>
+    <mergeCell ref="A195:J195"/>
+    <mergeCell ref="A251:J251"/>
     <mergeCell ref="A76:J76"/>
     <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A203:J203"/>
     <mergeCell ref="A116:J116"/>
     <mergeCell ref="A85:J85"/>
     <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A188:J188"/>
+    <mergeCell ref="A244:J244"/>
+    <mergeCell ref="A259:J259"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A100:J100"/>
+    <mergeCell ref="A253:J253"/>
     <mergeCell ref="A131:J131"/>
     <mergeCell ref="A126:J126"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A100:J100"/>
-    <mergeCell ref="A140:J140"/>
     <mergeCell ref="A53:J53"/>
     <mergeCell ref="A35:J35"/>
     <mergeCell ref="A109:J109"/>
+    <mergeCell ref="A140:J140"/>
+    <mergeCell ref="A180:J180"/>
+    <mergeCell ref="A231:J231"/>
+    <mergeCell ref="A240:J240"/>
     <mergeCell ref="A129:J129"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="A68:J68"/>
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A102:J102"/>
     <mergeCell ref="A117:J117"/>
+    <mergeCell ref="A230:J230"/>
     <mergeCell ref="A111:J111"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="A143:J143"/>
+    <mergeCell ref="A245:J245"/>
     <mergeCell ref="A92:J92"/>
     <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A166:J166"/>
     <mergeCell ref="A48:J48"/>
+    <mergeCell ref="A232:J232"/>
     <mergeCell ref="A142:J142"/>
+    <mergeCell ref="A207:J207"/>
     <mergeCell ref="A11:J11"/>
     <mergeCell ref="A103:J103"/>
     <mergeCell ref="A94:J94"/>
     <mergeCell ref="A45:J45"/>
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A216:J216"/>
+    <mergeCell ref="A168:J168"/>
     <mergeCell ref="A78:J78"/>
     <mergeCell ref="A87:J87"/>
     <mergeCell ref="A65:J65"/>
+    <mergeCell ref="A218:J218"/>
     <mergeCell ref="A128:J128"/>
+    <mergeCell ref="A193:J193"/>
+    <mergeCell ref="A255:J255"/>
     <mergeCell ref="A80:J80"/>
     <mergeCell ref="A46:J46"/>
     <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A208:J208"/>
     <mergeCell ref="A89:J89"/>
     <mergeCell ref="A136:J136"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="A105:J105"/>
+    <mergeCell ref="A192:J192"/>
     <mergeCell ref="A57:J57"/>
     <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A210:J210"/>
     <mergeCell ref="A113:J113"/>
+    <mergeCell ref="A179:J179"/>
+    <mergeCell ref="A235:J235"/>
+    <mergeCell ref="A247:J247"/>
     <mergeCell ref="A71:J71"/>
+    <mergeCell ref="A185:J185"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1" gridLines="1"/>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1" verticalDpi="0"/>
   <rowBreaks count="8" manualBreakCount="8">
-    <brk id="19" min="0" max="16383" man="1"/>
-    <brk id="36" min="0" max="16383" man="1"/>
-    <brk id="53" min="0" max="16383" man="1"/>
-    <brk id="70" min="0" max="16383" man="1"/>
-    <brk id="87" min="0" max="16383" man="1"/>
-    <brk id="104" min="0" max="16383" man="1"/>
-    <brk id="121" min="0" max="16383" man="1"/>
-    <brk id="138" min="0" max="16383" man="1"/>
+    <brk id="31" min="0" max="16383" man="1"/>
+    <brk id="60" min="0" max="16383" man="1"/>
+    <brk id="89" min="0" max="16383" man="1"/>
+    <brk id="118" min="0" max="16383" man="1"/>
+    <brk id="147" min="0" max="16383" man="1"/>
+    <brk id="176" min="0" max="16383" man="1"/>
+    <brk id="205" min="0" max="16383" man="1"/>
+    <brk id="234" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -3720,7 +5556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J155"/>
+  <dimension ref="A1:J263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <sheetData>
     <row r="1" ht="20" customHeight="1" s="6">
@@ -3771,8 +5607,8 @@
       <c r="A4" s="55" t="inlineStr">
         <is>
           <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
+※疑問文では ever、否定では never または not ... before を使います。
 ※回数は four times / five times のように表します。
-※否定では never または not ... before を使います。
 ※相手が答える形なので、返答では I / we ではなく you を使います。</t>
         </is>
       </c>
@@ -3786,26 +5622,26 @@
       <c r="I4" s="27" t="n"/>
       <c r="J4" s="57" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1" s="6">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>私は京都を4回訪れたことがあります。</t>
-        </is>
-      </c>
-      <c r="B5" s="27" t="n"/>
-      <c r="C5" s="27" t="n"/>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="27" t="n"/>
-      <c r="F5" s="27" t="n"/>
-      <c r="G5" s="27" t="n"/>
-      <c r="H5" s="27" t="n"/>
-      <c r="I5" s="27" t="n"/>
-      <c r="J5" s="57" t="n"/>
-    </row>
-    <row r="6" ht="26" customHeight="1" s="6">
+    <row r="5" ht="18" customHeight="1" s="6">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>【基本】訪れたことがある・ない</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="25" t="n"/>
+      <c r="I5" s="25" t="n"/>
+      <c r="J5" s="56" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：I have visited Kyoto four times.</t>
+          <t>私は京都を訪れたことがあります。</t>
         </is>
       </c>
       <c r="B6" s="27" t="n"/>
@@ -3818,10 +5654,10 @@
       <c r="I6" s="27" t="n"/>
       <c r="J6" s="57" t="n"/>
     </row>
-    <row r="7" ht="20" customHeight="1" s="6">
+    <row r="7" ht="22" customHeight="1" s="6">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>私はまだ一度も京都を訪れたことがありません。</t>
+          <t>正解（基本形）：I have visited Kyoto before.</t>
         </is>
       </c>
       <c r="B7" s="27" t="n"/>
@@ -3834,10 +5670,10 @@
       <c r="I7" s="27" t="n"/>
       <c r="J7" s="57" t="n"/>
     </row>
-    <row r="8" ht="26" customHeight="1" s="6">
+    <row r="8" ht="18" customHeight="1" s="6">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：I have never visited Kyoto.</t>
+          <t>私はまだ一度も京都を訪れたことがありません。</t>
         </is>
       </c>
       <c r="B8" s="27" t="n"/>
@@ -3850,10 +5686,10 @@
       <c r="I8" s="27" t="n"/>
       <c r="J8" s="57" t="n"/>
     </row>
-    <row r="9" ht="26" customHeight="1" s="6">
+    <row r="9" ht="22" customHeight="1" s="6">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：I have not visited Kyoto before.</t>
+          <t>正解（基本形）：I have never visited Kyoto.</t>
         </is>
       </c>
       <c r="B9" s="27" t="n"/>
@@ -3866,10 +5702,10 @@
       <c r="I9" s="27" t="n"/>
       <c r="J9" s="57" t="n"/>
     </row>
-    <row r="10" ht="26" customHeight="1" s="6">
+    <row r="10" ht="22" customHeight="1" s="6">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：I haven't visited Kyoto before.</t>
+          <t>正解（言いかえ）：I have not visited Kyoto before.</t>
         </is>
       </c>
       <c r="B10" s="27" t="n"/>
@@ -3882,10 +5718,10 @@
       <c r="I10" s="27" t="n"/>
       <c r="J10" s="57" t="n"/>
     </row>
-    <row r="11" ht="20" customHeight="1" s="6">
+    <row r="11" ht="22" customHeight="1" s="6">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>私は京都を何回訪れたことがありますか。</t>
+          <t>正解（短縮形）：I haven't visited Kyoto before.</t>
         </is>
       </c>
       <c r="B11" s="27" t="n"/>
@@ -3898,10 +5734,10 @@
       <c r="I11" s="27" t="n"/>
       <c r="J11" s="57" t="n"/>
     </row>
-    <row r="12" ht="26" customHeight="1" s="6">
+    <row r="12" ht="18" customHeight="1" s="6">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>正解（疑問文）：How many times have I visited Kyoto?</t>
+          <t>私は京都を訪れたことがありますか。</t>
         </is>
       </c>
       <c r="B12" s="27" t="n"/>
@@ -3914,10 +5750,10 @@
       <c r="I12" s="27" t="n"/>
       <c r="J12" s="57" t="n"/>
     </row>
-    <row r="13" ht="20" customHeight="1" s="6">
+    <row r="13" ht="22" customHeight="1" s="6">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>5回訪れたことがあります。</t>
+          <t>正解（疑問文）：Have I ever visited Kyoto?</t>
         </is>
       </c>
       <c r="B13" s="27" t="n"/>
@@ -3930,10 +5766,10 @@
       <c r="I13" s="27" t="n"/>
       <c r="J13" s="57" t="n"/>
     </row>
-    <row r="14" ht="26" customHeight="1" s="6">
+    <row r="14" ht="18" customHeight="1" s="6">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>正解（返答）：You have visited Kyoto five times.</t>
+          <t>はい、あります。</t>
         </is>
       </c>
       <c r="B14" s="27" t="n"/>
@@ -3946,10 +5782,10 @@
       <c r="I14" s="27" t="n"/>
       <c r="J14" s="57" t="n"/>
     </row>
-    <row r="15" ht="20" customHeight="1" s="6">
+    <row r="15" ht="22" customHeight="1" s="6">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>一度も訪れたことがありません。</t>
+          <t>正解（返答）：Yes, you have.</t>
         </is>
       </c>
       <c r="B15" s="27" t="n"/>
@@ -3962,10 +5798,10 @@
       <c r="I15" s="27" t="n"/>
       <c r="J15" s="57" t="n"/>
     </row>
-    <row r="16" ht="26" customHeight="1" s="6">
+    <row r="16" ht="18" customHeight="1" s="6">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：You have never visited Kyoto.</t>
+          <t>いいえ、ありません。</t>
         </is>
       </c>
       <c r="B16" s="27" t="n"/>
@@ -3978,10 +5814,10 @@
       <c r="I16" s="27" t="n"/>
       <c r="J16" s="57" t="n"/>
     </row>
-    <row r="17" ht="26" customHeight="1" s="6">
+    <row r="17" ht="22" customHeight="1" s="6">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：You have not visited Kyoto before.</t>
+          <t>正解（基本形）：No, you have never visited Kyoto.</t>
         </is>
       </c>
       <c r="B17" s="27" t="n"/>
@@ -3994,10 +5830,10 @@
       <c r="I17" s="27" t="n"/>
       <c r="J17" s="57" t="n"/>
     </row>
-    <row r="18" ht="26" customHeight="1" s="6">
+    <row r="18" ht="22" customHeight="1" s="6">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：You haven't visited Kyoto before.</t>
+          <t>正解（言いかえ）：No, you have not visited Kyoto before.</t>
         </is>
       </c>
       <c r="B18" s="27" t="n"/>
@@ -4010,8 +5846,12 @@
       <c r="I18" s="27" t="n"/>
       <c r="J18" s="57" t="n"/>
     </row>
-    <row r="19" ht="6" customHeight="1" s="6">
-      <c r="A19" s="11" t="n"/>
+    <row r="19" ht="22" customHeight="1" s="6">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：No, you haven't visited Kyoto before.</t>
+        </is>
+      </c>
       <c r="B19" s="27" t="n"/>
       <c r="C19" s="27" t="n"/>
       <c r="D19" s="27" t="n"/>
@@ -4025,7 +5865,7 @@
     <row r="20" ht="18" customHeight="1" s="6">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>2．主語は「あなた」で書いてください。</t>
+          <t>【回数】何回訪れたことがあるか</t>
         </is>
       </c>
       <c r="B20" s="25" t="n"/>
@@ -4038,12 +5878,10 @@
       <c r="I20" s="25" t="n"/>
       <c r="J20" s="56" t="n"/>
     </row>
-    <row r="21" ht="60" customHeight="1" s="6">
-      <c r="A21" s="55" t="inlineStr">
-        <is>
-          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
-※回数は four times / five times のように表します。
-※否定では never または not ... before を使います。</t>
+    <row r="21" ht="18" customHeight="1" s="6">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>私は京都を4回訪れたことがあります。</t>
         </is>
       </c>
       <c r="B21" s="27" t="n"/>
@@ -4056,10 +5894,10 @@
       <c r="I21" s="27" t="n"/>
       <c r="J21" s="57" t="n"/>
     </row>
-    <row r="22" ht="20" customHeight="1" s="6">
+    <row r="22" ht="22" customHeight="1" s="6">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>あなたは京都を4回訪れたことがあります。</t>
+          <t>正解（基本形）：I have visited Kyoto four times.</t>
         </is>
       </c>
       <c r="B22" s="27" t="n"/>
@@ -4072,10 +5910,10 @@
       <c r="I22" s="27" t="n"/>
       <c r="J22" s="57" t="n"/>
     </row>
-    <row r="23" ht="26" customHeight="1" s="6">
+    <row r="23" ht="18" customHeight="1" s="6">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：You have visited Kyoto four times.</t>
+          <t>私は京都を何回訪れたことがありますか。</t>
         </is>
       </c>
       <c r="B23" s="27" t="n"/>
@@ -4088,10 +5926,10 @@
       <c r="I23" s="27" t="n"/>
       <c r="J23" s="57" t="n"/>
     </row>
-    <row r="24" ht="20" customHeight="1" s="6">
+    <row r="24" ht="22" customHeight="1" s="6">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>あなたはまだ一度も京都を訪れたことがありません。</t>
+          <t>正解（疑問文）：How many times have I visited Kyoto?</t>
         </is>
       </c>
       <c r="B24" s="27" t="n"/>
@@ -4104,10 +5942,10 @@
       <c r="I24" s="27" t="n"/>
       <c r="J24" s="57" t="n"/>
     </row>
-    <row r="25" ht="26" customHeight="1" s="6">
+    <row r="25" ht="18" customHeight="1" s="6">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：You have never visited Kyoto.</t>
+          <t>5回訪れたことがあります。</t>
         </is>
       </c>
       <c r="B25" s="27" t="n"/>
@@ -4120,10 +5958,10 @@
       <c r="I25" s="27" t="n"/>
       <c r="J25" s="57" t="n"/>
     </row>
-    <row r="26" ht="26" customHeight="1" s="6">
+    <row r="26" ht="22" customHeight="1" s="6">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：You have not visited Kyoto before.</t>
+          <t>正解（返答）：You have visited Kyoto five times.</t>
         </is>
       </c>
       <c r="B26" s="27" t="n"/>
@@ -4136,10 +5974,10 @@
       <c r="I26" s="27" t="n"/>
       <c r="J26" s="57" t="n"/>
     </row>
-    <row r="27" ht="26" customHeight="1" s="6">
+    <row r="27" ht="18" customHeight="1" s="6">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：You haven't visited Kyoto before.</t>
+          <t>一度も訪れたことがありません。</t>
         </is>
       </c>
       <c r="B27" s="27" t="n"/>
@@ -4152,10 +5990,10 @@
       <c r="I27" s="27" t="n"/>
       <c r="J27" s="57" t="n"/>
     </row>
-    <row r="28" ht="20" customHeight="1" s="6">
+    <row r="28" ht="22" customHeight="1" s="6">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>あなたは京都を何回訪れたことがありますか。</t>
+          <t>正解（基本形）：You have never visited Kyoto.</t>
         </is>
       </c>
       <c r="B28" s="27" t="n"/>
@@ -4168,10 +6006,10 @@
       <c r="I28" s="27" t="n"/>
       <c r="J28" s="57" t="n"/>
     </row>
-    <row r="29" ht="26" customHeight="1" s="6">
+    <row r="29" ht="22" customHeight="1" s="6">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>正解（疑問文）：How many times have you visited Kyoto?</t>
+          <t>正解（言いかえ）：You have not visited Kyoto before.</t>
         </is>
       </c>
       <c r="B29" s="27" t="n"/>
@@ -4184,10 +6022,10 @@
       <c r="I29" s="27" t="n"/>
       <c r="J29" s="57" t="n"/>
     </row>
-    <row r="30" ht="20" customHeight="1" s="6">
+    <row r="30" ht="22" customHeight="1" s="6">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>5回訪れたことがあります。</t>
+          <t>正解（短縮形）：You haven't visited Kyoto before.</t>
         </is>
       </c>
       <c r="B30" s="27" t="n"/>
@@ -4200,12 +6038,8 @@
       <c r="I30" s="27" t="n"/>
       <c r="J30" s="57" t="n"/>
     </row>
-    <row r="31" ht="26" customHeight="1" s="6">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>正解（返答）：I have visited Kyoto five times.</t>
-        </is>
-      </c>
+    <row r="31" ht="6" customHeight="1" s="6">
+      <c r="A31" s="11" t="n"/>
       <c r="B31" s="27" t="n"/>
       <c r="C31" s="27" t="n"/>
       <c r="D31" s="27" t="n"/>
@@ -4216,26 +6050,28 @@
       <c r="I31" s="27" t="n"/>
       <c r="J31" s="57" t="n"/>
     </row>
-    <row r="32" ht="20" customHeight="1" s="6">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>一度も訪れたことがありません。</t>
-        </is>
-      </c>
-      <c r="B32" s="27" t="n"/>
-      <c r="C32" s="27" t="n"/>
-      <c r="D32" s="27" t="n"/>
-      <c r="E32" s="27" t="n"/>
-      <c r="F32" s="27" t="n"/>
-      <c r="G32" s="27" t="n"/>
-      <c r="H32" s="27" t="n"/>
-      <c r="I32" s="27" t="n"/>
-      <c r="J32" s="57" t="n"/>
-    </row>
-    <row r="33" ht="26" customHeight="1" s="6">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>正解（基本形）：I have never visited Kyoto.</t>
+    <row r="32" ht="18" customHeight="1" s="6">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>2．主語は「あなた」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="n"/>
+      <c r="C32" s="25" t="n"/>
+      <c r="D32" s="25" t="n"/>
+      <c r="E32" s="25" t="n"/>
+      <c r="F32" s="25" t="n"/>
+      <c r="G32" s="25" t="n"/>
+      <c r="H32" s="25" t="n"/>
+      <c r="I32" s="25" t="n"/>
+      <c r="J32" s="56" t="n"/>
+    </row>
+    <row r="33" ht="60" customHeight="1" s="6">
+      <c r="A33" s="55" t="inlineStr">
+        <is>
+          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
+※疑問文では ever、否定では never または not ... before を使います。
+※回数は four times / five times のように表します。</t>
         </is>
       </c>
       <c r="B33" s="27" t="n"/>
@@ -4248,26 +6084,26 @@
       <c r="I33" s="27" t="n"/>
       <c r="J33" s="57" t="n"/>
     </row>
-    <row r="34" ht="26" customHeight="1" s="6">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>正解（言いかえ）：I have not visited Kyoto before.</t>
-        </is>
-      </c>
-      <c r="B34" s="27" t="n"/>
-      <c r="C34" s="27" t="n"/>
-      <c r="D34" s="27" t="n"/>
-      <c r="E34" s="27" t="n"/>
-      <c r="F34" s="27" t="n"/>
-      <c r="G34" s="27" t="n"/>
-      <c r="H34" s="27" t="n"/>
-      <c r="I34" s="27" t="n"/>
-      <c r="J34" s="57" t="n"/>
-    </row>
-    <row r="35" ht="26" customHeight="1" s="6">
+    <row r="34" ht="18" customHeight="1" s="6">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>【基本】訪れたことがある・ない</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="n"/>
+      <c r="C34" s="25" t="n"/>
+      <c r="D34" s="25" t="n"/>
+      <c r="E34" s="25" t="n"/>
+      <c r="F34" s="25" t="n"/>
+      <c r="G34" s="25" t="n"/>
+      <c r="H34" s="25" t="n"/>
+      <c r="I34" s="25" t="n"/>
+      <c r="J34" s="56" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1" s="6">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：I haven't visited Kyoto before.</t>
+          <t>あなたは京都を訪れたことがあります。</t>
         </is>
       </c>
       <c r="B35" s="27" t="n"/>
@@ -4280,8 +6116,12 @@
       <c r="I35" s="27" t="n"/>
       <c r="J35" s="57" t="n"/>
     </row>
-    <row r="36" ht="6" customHeight="1" s="6">
-      <c r="A36" s="11" t="n"/>
+    <row r="36" ht="22" customHeight="1" s="6">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：You have visited Kyoto before.</t>
+        </is>
+      </c>
       <c r="B36" s="27" t="n"/>
       <c r="C36" s="27" t="n"/>
       <c r="D36" s="27" t="n"/>
@@ -4293,27 +6133,25 @@
       <c r="J36" s="57" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="6">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>3．主語は「彼」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B37" s="25" t="n"/>
-      <c r="C37" s="25" t="n"/>
-      <c r="D37" s="25" t="n"/>
-      <c r="E37" s="25" t="n"/>
-      <c r="F37" s="25" t="n"/>
-      <c r="G37" s="25" t="n"/>
-      <c r="H37" s="25" t="n"/>
-      <c r="I37" s="25" t="n"/>
-      <c r="J37" s="56" t="n"/>
-    </row>
-    <row r="38" ht="60" customHeight="1" s="6">
-      <c r="A38" s="55" t="inlineStr">
-        <is>
-          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
-※回数は four times / five times のように表します。
-※否定では never または not ... before を使います。</t>
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>あなたはまだ一度も京都を訪れたことがありません。</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="n"/>
+      <c r="C37" s="27" t="n"/>
+      <c r="D37" s="27" t="n"/>
+      <c r="E37" s="27" t="n"/>
+      <c r="F37" s="27" t="n"/>
+      <c r="G37" s="27" t="n"/>
+      <c r="H37" s="27" t="n"/>
+      <c r="I37" s="27" t="n"/>
+      <c r="J37" s="57" t="n"/>
+    </row>
+    <row r="38" ht="22" customHeight="1" s="6">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：You have never visited Kyoto.</t>
         </is>
       </c>
       <c r="B38" s="27" t="n"/>
@@ -4326,10 +6164,10 @@
       <c r="I38" s="27" t="n"/>
       <c r="J38" s="57" t="n"/>
     </row>
-    <row r="39" ht="20" customHeight="1" s="6">
+    <row r="39" ht="22" customHeight="1" s="6">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>彼は京都を4回訪れたことがあります。</t>
+          <t>正解（言いかえ）：You have not visited Kyoto before.</t>
         </is>
       </c>
       <c r="B39" s="27" t="n"/>
@@ -4342,10 +6180,10 @@
       <c r="I39" s="27" t="n"/>
       <c r="J39" s="57" t="n"/>
     </row>
-    <row r="40" ht="26" customHeight="1" s="6">
+    <row r="40" ht="22" customHeight="1" s="6">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：He has visited Kyoto four times.</t>
+          <t>正解（短縮形）：You haven't visited Kyoto before.</t>
         </is>
       </c>
       <c r="B40" s="27" t="n"/>
@@ -4358,10 +6196,10 @@
       <c r="I40" s="27" t="n"/>
       <c r="J40" s="57" t="n"/>
     </row>
-    <row r="41" ht="20" customHeight="1" s="6">
+    <row r="41" ht="18" customHeight="1" s="6">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>彼はまだ一度も京都を訪れたことがありません。</t>
+          <t>あなたは京都を訪れたことがありますか。</t>
         </is>
       </c>
       <c r="B41" s="27" t="n"/>
@@ -4374,10 +6212,10 @@
       <c r="I41" s="27" t="n"/>
       <c r="J41" s="57" t="n"/>
     </row>
-    <row r="42" ht="26" customHeight="1" s="6">
+    <row r="42" ht="22" customHeight="1" s="6">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：He has never visited Kyoto.</t>
+          <t>正解（疑問文）：Have you ever visited Kyoto?</t>
         </is>
       </c>
       <c r="B42" s="27" t="n"/>
@@ -4390,10 +6228,10 @@
       <c r="I42" s="27" t="n"/>
       <c r="J42" s="57" t="n"/>
     </row>
-    <row r="43" ht="26" customHeight="1" s="6">
+    <row r="43" ht="18" customHeight="1" s="6">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：He has not visited Kyoto before.</t>
+          <t>はい、あります。</t>
         </is>
       </c>
       <c r="B43" s="27" t="n"/>
@@ -4406,10 +6244,10 @@
       <c r="I43" s="27" t="n"/>
       <c r="J43" s="57" t="n"/>
     </row>
-    <row r="44" ht="26" customHeight="1" s="6">
+    <row r="44" ht="22" customHeight="1" s="6">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：He hasn't visited Kyoto before.</t>
+          <t>正解（返答）：Yes, I have.</t>
         </is>
       </c>
       <c r="B44" s="27" t="n"/>
@@ -4422,10 +6260,10 @@
       <c r="I44" s="27" t="n"/>
       <c r="J44" s="57" t="n"/>
     </row>
-    <row r="45" ht="20" customHeight="1" s="6">
+    <row r="45" ht="18" customHeight="1" s="6">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>彼は京都を何回訪れたことがありますか。</t>
+          <t>いいえ、ありません。</t>
         </is>
       </c>
       <c r="B45" s="27" t="n"/>
@@ -4438,10 +6276,10 @@
       <c r="I45" s="27" t="n"/>
       <c r="J45" s="57" t="n"/>
     </row>
-    <row r="46" ht="26" customHeight="1" s="6">
+    <row r="46" ht="22" customHeight="1" s="6">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>正解（疑問文）：How many times has he visited Kyoto?</t>
+          <t>正解（基本形）：No, I have never visited Kyoto.</t>
         </is>
       </c>
       <c r="B46" s="27" t="n"/>
@@ -4454,10 +6292,10 @@
       <c r="I46" s="27" t="n"/>
       <c r="J46" s="57" t="n"/>
     </row>
-    <row r="47" ht="20" customHeight="1" s="6">
+    <row r="47" ht="22" customHeight="1" s="6">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>5回訪れたことがあります。</t>
+          <t>正解（言いかえ）：No, I have not visited Kyoto before.</t>
         </is>
       </c>
       <c r="B47" s="27" t="n"/>
@@ -4470,10 +6308,10 @@
       <c r="I47" s="27" t="n"/>
       <c r="J47" s="57" t="n"/>
     </row>
-    <row r="48" ht="26" customHeight="1" s="6">
+    <row r="48" ht="22" customHeight="1" s="6">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>正解（返答）：He has visited Kyoto five times.</t>
+          <t>正解（短縮形）：No, I haven't visited Kyoto before.</t>
         </is>
       </c>
       <c r="B48" s="27" t="n"/>
@@ -4486,26 +6324,26 @@
       <c r="I48" s="27" t="n"/>
       <c r="J48" s="57" t="n"/>
     </row>
-    <row r="49" ht="20" customHeight="1" s="6">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>一度も訪れたことがありません。</t>
-        </is>
-      </c>
-      <c r="B49" s="27" t="n"/>
-      <c r="C49" s="27" t="n"/>
-      <c r="D49" s="27" t="n"/>
-      <c r="E49" s="27" t="n"/>
-      <c r="F49" s="27" t="n"/>
-      <c r="G49" s="27" t="n"/>
-      <c r="H49" s="27" t="n"/>
-      <c r="I49" s="27" t="n"/>
-      <c r="J49" s="57" t="n"/>
-    </row>
-    <row r="50" ht="26" customHeight="1" s="6">
+    <row r="49" ht="18" customHeight="1" s="6">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>【回数】何回訪れたことがあるか</t>
+        </is>
+      </c>
+      <c r="B49" s="25" t="n"/>
+      <c r="C49" s="25" t="n"/>
+      <c r="D49" s="25" t="n"/>
+      <c r="E49" s="25" t="n"/>
+      <c r="F49" s="25" t="n"/>
+      <c r="G49" s="25" t="n"/>
+      <c r="H49" s="25" t="n"/>
+      <c r="I49" s="25" t="n"/>
+      <c r="J49" s="56" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1" s="6">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：He has never visited Kyoto.</t>
+          <t>あなたは京都を4回訪れたことがあります。</t>
         </is>
       </c>
       <c r="B50" s="27" t="n"/>
@@ -4518,10 +6356,10 @@
       <c r="I50" s="27" t="n"/>
       <c r="J50" s="57" t="n"/>
     </row>
-    <row r="51" ht="26" customHeight="1" s="6">
+    <row r="51" ht="22" customHeight="1" s="6">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：He has not visited Kyoto before.</t>
+          <t>正解（基本形）：You have visited Kyoto four times.</t>
         </is>
       </c>
       <c r="B51" s="27" t="n"/>
@@ -4534,10 +6372,10 @@
       <c r="I51" s="27" t="n"/>
       <c r="J51" s="57" t="n"/>
     </row>
-    <row r="52" ht="26" customHeight="1" s="6">
+    <row r="52" ht="18" customHeight="1" s="6">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：He hasn't visited Kyoto before.</t>
+          <t>あなたは京都を何回訪れたことがありますか。</t>
         </is>
       </c>
       <c r="B52" s="27" t="n"/>
@@ -4550,8 +6388,12 @@
       <c r="I52" s="27" t="n"/>
       <c r="J52" s="57" t="n"/>
     </row>
-    <row r="53" ht="6" customHeight="1" s="6">
-      <c r="A53" s="11" t="n"/>
+    <row r="53" ht="22" customHeight="1" s="6">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>正解（疑問文）：How many times have you visited Kyoto?</t>
+        </is>
+      </c>
       <c r="B53" s="27" t="n"/>
       <c r="C53" s="27" t="n"/>
       <c r="D53" s="27" t="n"/>
@@ -4563,27 +6405,25 @@
       <c r="J53" s="57" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1" s="6">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>4．主語は「彼女」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B54" s="25" t="n"/>
-      <c r="C54" s="25" t="n"/>
-      <c r="D54" s="25" t="n"/>
-      <c r="E54" s="25" t="n"/>
-      <c r="F54" s="25" t="n"/>
-      <c r="G54" s="25" t="n"/>
-      <c r="H54" s="25" t="n"/>
-      <c r="I54" s="25" t="n"/>
-      <c r="J54" s="56" t="n"/>
-    </row>
-    <row r="55" ht="60" customHeight="1" s="6">
-      <c r="A55" s="55" t="inlineStr">
-        <is>
-          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
-※回数は four times / five times のように表します。
-※否定では never または not ... before を使います。</t>
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>5回訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B54" s="27" t="n"/>
+      <c r="C54" s="27" t="n"/>
+      <c r="D54" s="27" t="n"/>
+      <c r="E54" s="27" t="n"/>
+      <c r="F54" s="27" t="n"/>
+      <c r="G54" s="27" t="n"/>
+      <c r="H54" s="27" t="n"/>
+      <c r="I54" s="27" t="n"/>
+      <c r="J54" s="57" t="n"/>
+    </row>
+    <row r="55" ht="22" customHeight="1" s="6">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>正解（返答）：I have visited Kyoto five times.</t>
         </is>
       </c>
       <c r="B55" s="27" t="n"/>
@@ -4596,10 +6436,10 @@
       <c r="I55" s="27" t="n"/>
       <c r="J55" s="57" t="n"/>
     </row>
-    <row r="56" ht="20" customHeight="1" s="6">
+    <row r="56" ht="18" customHeight="1" s="6">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>彼女は京都を4回訪れたことがあります。</t>
+          <t>一度も訪れたことがありません。</t>
         </is>
       </c>
       <c r="B56" s="27" t="n"/>
@@ -4612,10 +6452,10 @@
       <c r="I56" s="27" t="n"/>
       <c r="J56" s="57" t="n"/>
     </row>
-    <row r="57" ht="26" customHeight="1" s="6">
+    <row r="57" ht="22" customHeight="1" s="6">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：She has visited Kyoto four times.</t>
+          <t>正解（基本形）：I have never visited Kyoto.</t>
         </is>
       </c>
       <c r="B57" s="27" t="n"/>
@@ -4628,10 +6468,10 @@
       <c r="I57" s="27" t="n"/>
       <c r="J57" s="57" t="n"/>
     </row>
-    <row r="58" ht="20" customHeight="1" s="6">
+    <row r="58" ht="22" customHeight="1" s="6">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>彼女はまだ一度も京都を訪れたことがありません。</t>
+          <t>正解（言いかえ）：I have not visited Kyoto before.</t>
         </is>
       </c>
       <c r="B58" s="27" t="n"/>
@@ -4644,10 +6484,10 @@
       <c r="I58" s="27" t="n"/>
       <c r="J58" s="57" t="n"/>
     </row>
-    <row r="59" ht="26" customHeight="1" s="6">
+    <row r="59" ht="22" customHeight="1" s="6">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：She has never visited Kyoto.</t>
+          <t>正解（短縮形）：I haven't visited Kyoto before.</t>
         </is>
       </c>
       <c r="B59" s="27" t="n"/>
@@ -4660,12 +6500,8 @@
       <c r="I59" s="27" t="n"/>
       <c r="J59" s="57" t="n"/>
     </row>
-    <row r="60" ht="26" customHeight="1" s="6">
-      <c r="A60" s="11" t="inlineStr">
-        <is>
-          <t>正解（言いかえ）：She has not visited Kyoto before.</t>
-        </is>
-      </c>
+    <row r="60" ht="6" customHeight="1" s="6">
+      <c r="A60" s="11" t="n"/>
       <c r="B60" s="27" t="n"/>
       <c r="C60" s="27" t="n"/>
       <c r="D60" s="27" t="n"/>
@@ -4676,26 +6512,28 @@
       <c r="I60" s="27" t="n"/>
       <c r="J60" s="57" t="n"/>
     </row>
-    <row r="61" ht="26" customHeight="1" s="6">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t>正解（短縮形）：She hasn't visited Kyoto before.</t>
-        </is>
-      </c>
-      <c r="B61" s="27" t="n"/>
-      <c r="C61" s="27" t="n"/>
-      <c r="D61" s="27" t="n"/>
-      <c r="E61" s="27" t="n"/>
-      <c r="F61" s="27" t="n"/>
-      <c r="G61" s="27" t="n"/>
-      <c r="H61" s="27" t="n"/>
-      <c r="I61" s="27" t="n"/>
-      <c r="J61" s="57" t="n"/>
-    </row>
-    <row r="62" ht="20" customHeight="1" s="6">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t>彼女は京都を何回訪れたことがありますか。</t>
+    <row r="61" ht="18" customHeight="1" s="6">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>3．主語は「彼」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B61" s="25" t="n"/>
+      <c r="C61" s="25" t="n"/>
+      <c r="D61" s="25" t="n"/>
+      <c r="E61" s="25" t="n"/>
+      <c r="F61" s="25" t="n"/>
+      <c r="G61" s="25" t="n"/>
+      <c r="H61" s="25" t="n"/>
+      <c r="I61" s="25" t="n"/>
+      <c r="J61" s="56" t="n"/>
+    </row>
+    <row r="62" ht="60" customHeight="1" s="6">
+      <c r="A62" s="55" t="inlineStr">
+        <is>
+          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
+※疑問文では ever、否定では never または not ... before を使います。
+※回数は four times / five times のように表します。</t>
         </is>
       </c>
       <c r="B62" s="27" t="n"/>
@@ -4708,26 +6546,26 @@
       <c r="I62" s="27" t="n"/>
       <c r="J62" s="57" t="n"/>
     </row>
-    <row r="63" ht="26" customHeight="1" s="6">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t>正解（疑問文）：How many times has she visited Kyoto?</t>
-        </is>
-      </c>
-      <c r="B63" s="27" t="n"/>
-      <c r="C63" s="27" t="n"/>
-      <c r="D63" s="27" t="n"/>
-      <c r="E63" s="27" t="n"/>
-      <c r="F63" s="27" t="n"/>
-      <c r="G63" s="27" t="n"/>
-      <c r="H63" s="27" t="n"/>
-      <c r="I63" s="27" t="n"/>
-      <c r="J63" s="57" t="n"/>
-    </row>
-    <row r="64" ht="20" customHeight="1" s="6">
+    <row r="63" ht="18" customHeight="1" s="6">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>【基本】訪れたことがある・ない</t>
+        </is>
+      </c>
+      <c r="B63" s="25" t="n"/>
+      <c r="C63" s="25" t="n"/>
+      <c r="D63" s="25" t="n"/>
+      <c r="E63" s="25" t="n"/>
+      <c r="F63" s="25" t="n"/>
+      <c r="G63" s="25" t="n"/>
+      <c r="H63" s="25" t="n"/>
+      <c r="I63" s="25" t="n"/>
+      <c r="J63" s="56" t="n"/>
+    </row>
+    <row r="64" ht="18" customHeight="1" s="6">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>5回訪れたことがあります。</t>
+          <t>彼は京都を訪れたことがあります。</t>
         </is>
       </c>
       <c r="B64" s="27" t="n"/>
@@ -4740,10 +6578,10 @@
       <c r="I64" s="27" t="n"/>
       <c r="J64" s="57" t="n"/>
     </row>
-    <row r="65" ht="26" customHeight="1" s="6">
+    <row r="65" ht="22" customHeight="1" s="6">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>正解（返答）：She has visited Kyoto five times.</t>
+          <t>正解（基本形）：He has visited Kyoto before.</t>
         </is>
       </c>
       <c r="B65" s="27" t="n"/>
@@ -4756,10 +6594,10 @@
       <c r="I65" s="27" t="n"/>
       <c r="J65" s="57" t="n"/>
     </row>
-    <row r="66" ht="20" customHeight="1" s="6">
+    <row r="66" ht="18" customHeight="1" s="6">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>一度も訪れたことがありません。</t>
+          <t>彼はまだ一度も京都を訪れたことがありません。</t>
         </is>
       </c>
       <c r="B66" s="27" t="n"/>
@@ -4772,10 +6610,10 @@
       <c r="I66" s="27" t="n"/>
       <c r="J66" s="57" t="n"/>
     </row>
-    <row r="67" ht="26" customHeight="1" s="6">
+    <row r="67" ht="22" customHeight="1" s="6">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：She has never visited Kyoto.</t>
+          <t>正解（基本形）：He has never visited Kyoto.</t>
         </is>
       </c>
       <c r="B67" s="27" t="n"/>
@@ -4788,10 +6626,10 @@
       <c r="I67" s="27" t="n"/>
       <c r="J67" s="57" t="n"/>
     </row>
-    <row r="68" ht="26" customHeight="1" s="6">
+    <row r="68" ht="22" customHeight="1" s="6">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：She has not visited Kyoto before.</t>
+          <t>正解（言いかえ）：He has not visited Kyoto before.</t>
         </is>
       </c>
       <c r="B68" s="27" t="n"/>
@@ -4804,10 +6642,10 @@
       <c r="I68" s="27" t="n"/>
       <c r="J68" s="57" t="n"/>
     </row>
-    <row r="69" ht="26" customHeight="1" s="6">
+    <row r="69" ht="22" customHeight="1" s="6">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：She hasn't visited Kyoto before.</t>
+          <t>正解（短縮形）：He hasn't visited Kyoto before.</t>
         </is>
       </c>
       <c r="B69" s="27" t="n"/>
@@ -4820,8 +6658,12 @@
       <c r="I69" s="27" t="n"/>
       <c r="J69" s="57" t="n"/>
     </row>
-    <row r="70" ht="6" customHeight="1" s="6">
-      <c r="A70" s="11" t="n"/>
+    <row r="70" ht="18" customHeight="1" s="6">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>彼は京都を訪れたことがありますか。</t>
+        </is>
+      </c>
       <c r="B70" s="27" t="n"/>
       <c r="C70" s="27" t="n"/>
       <c r="D70" s="27" t="n"/>
@@ -4832,29 +6674,26 @@
       <c r="I70" s="27" t="n"/>
       <c r="J70" s="57" t="n"/>
     </row>
-    <row r="71" ht="18" customHeight="1" s="6">
-      <c r="A71" s="9" t="inlineStr">
-        <is>
-          <t>5．主語は「私たち」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B71" s="25" t="n"/>
-      <c r="C71" s="25" t="n"/>
-      <c r="D71" s="25" t="n"/>
-      <c r="E71" s="25" t="n"/>
-      <c r="F71" s="25" t="n"/>
-      <c r="G71" s="25" t="n"/>
-      <c r="H71" s="25" t="n"/>
-      <c r="I71" s="25" t="n"/>
-      <c r="J71" s="56" t="n"/>
-    </row>
-    <row r="72" ht="60" customHeight="1" s="6">
-      <c r="A72" s="55" t="inlineStr">
-        <is>
-          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
-※回数は four times / five times のように表します。
-※否定では never または not ... before を使います。
-※相手が答える形なので、返答では I / we ではなく you を使います。</t>
+    <row r="71" ht="22" customHeight="1" s="6">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>正解（疑問文）：Has he ever visited Kyoto?</t>
+        </is>
+      </c>
+      <c r="B71" s="27" t="n"/>
+      <c r="C71" s="27" t="n"/>
+      <c r="D71" s="27" t="n"/>
+      <c r="E71" s="27" t="n"/>
+      <c r="F71" s="27" t="n"/>
+      <c r="G71" s="27" t="n"/>
+      <c r="H71" s="27" t="n"/>
+      <c r="I71" s="27" t="n"/>
+      <c r="J71" s="57" t="n"/>
+    </row>
+    <row r="72" ht="18" customHeight="1" s="6">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>はい、あります。</t>
         </is>
       </c>
       <c r="B72" s="27" t="n"/>
@@ -4867,10 +6706,10 @@
       <c r="I72" s="27" t="n"/>
       <c r="J72" s="57" t="n"/>
     </row>
-    <row r="73" ht="20" customHeight="1" s="6">
+    <row r="73" ht="22" customHeight="1" s="6">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>私たちは京都を4回訪れたことがあります。</t>
+          <t>正解（返答）：Yes, he has.</t>
         </is>
       </c>
       <c r="B73" s="27" t="n"/>
@@ -4883,10 +6722,10 @@
       <c r="I73" s="27" t="n"/>
       <c r="J73" s="57" t="n"/>
     </row>
-    <row r="74" ht="26" customHeight="1" s="6">
+    <row r="74" ht="18" customHeight="1" s="6">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：We have visited Kyoto four times.</t>
+          <t>いいえ、ありません。</t>
         </is>
       </c>
       <c r="B74" s="27" t="n"/>
@@ -4899,10 +6738,10 @@
       <c r="I74" s="27" t="n"/>
       <c r="J74" s="57" t="n"/>
     </row>
-    <row r="75" ht="20" customHeight="1" s="6">
+    <row r="75" ht="22" customHeight="1" s="6">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>私たちはまだ一度も京都を訪れたことがありません。</t>
+          <t>正解（基本形）：No, he has never visited Kyoto.</t>
         </is>
       </c>
       <c r="B75" s="27" t="n"/>
@@ -4915,10 +6754,10 @@
       <c r="I75" s="27" t="n"/>
       <c r="J75" s="57" t="n"/>
     </row>
-    <row r="76" ht="26" customHeight="1" s="6">
+    <row r="76" ht="22" customHeight="1" s="6">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：We have never visited Kyoto.</t>
+          <t>正解（言いかえ）：No, he has not visited Kyoto before.</t>
         </is>
       </c>
       <c r="B76" s="27" t="n"/>
@@ -4931,10 +6770,10 @@
       <c r="I76" s="27" t="n"/>
       <c r="J76" s="57" t="n"/>
     </row>
-    <row r="77" ht="26" customHeight="1" s="6">
+    <row r="77" ht="22" customHeight="1" s="6">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：We have not visited Kyoto before.</t>
+          <t>正解（短縮形）：No, he hasn't visited Kyoto before.</t>
         </is>
       </c>
       <c r="B77" s="27" t="n"/>
@@ -4947,26 +6786,26 @@
       <c r="I77" s="27" t="n"/>
       <c r="J77" s="57" t="n"/>
     </row>
-    <row r="78" ht="26" customHeight="1" s="6">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t>正解（短縮形）：We haven't visited Kyoto before.</t>
-        </is>
-      </c>
-      <c r="B78" s="27" t="n"/>
-      <c r="C78" s="27" t="n"/>
-      <c r="D78" s="27" t="n"/>
-      <c r="E78" s="27" t="n"/>
-      <c r="F78" s="27" t="n"/>
-      <c r="G78" s="27" t="n"/>
-      <c r="H78" s="27" t="n"/>
-      <c r="I78" s="27" t="n"/>
-      <c r="J78" s="57" t="n"/>
-    </row>
-    <row r="79" ht="20" customHeight="1" s="6">
+    <row r="78" ht="18" customHeight="1" s="6">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>【回数】何回訪れたことがあるか</t>
+        </is>
+      </c>
+      <c r="B78" s="25" t="n"/>
+      <c r="C78" s="25" t="n"/>
+      <c r="D78" s="25" t="n"/>
+      <c r="E78" s="25" t="n"/>
+      <c r="F78" s="25" t="n"/>
+      <c r="G78" s="25" t="n"/>
+      <c r="H78" s="25" t="n"/>
+      <c r="I78" s="25" t="n"/>
+      <c r="J78" s="56" t="n"/>
+    </row>
+    <row r="79" ht="18" customHeight="1" s="6">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>私たちは京都を何回訪れたことがありますか。</t>
+          <t>彼は京都を4回訪れたことがあります。</t>
         </is>
       </c>
       <c r="B79" s="27" t="n"/>
@@ -4979,10 +6818,10 @@
       <c r="I79" s="27" t="n"/>
       <c r="J79" s="57" t="n"/>
     </row>
-    <row r="80" ht="26" customHeight="1" s="6">
+    <row r="80" ht="22" customHeight="1" s="6">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>正解（疑問文）：How many times have we visited Kyoto?</t>
+          <t>正解（基本形）：He has visited Kyoto four times.</t>
         </is>
       </c>
       <c r="B80" s="27" t="n"/>
@@ -4995,10 +6834,10 @@
       <c r="I80" s="27" t="n"/>
       <c r="J80" s="57" t="n"/>
     </row>
-    <row r="81" ht="20" customHeight="1" s="6">
+    <row r="81" ht="18" customHeight="1" s="6">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>5回訪れたことがあります。</t>
+          <t>彼は京都を何回訪れたことがありますか。</t>
         </is>
       </c>
       <c r="B81" s="27" t="n"/>
@@ -5011,10 +6850,10 @@
       <c r="I81" s="27" t="n"/>
       <c r="J81" s="57" t="n"/>
     </row>
-    <row r="82" ht="26" customHeight="1" s="6">
+    <row r="82" ht="22" customHeight="1" s="6">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>正解（返答）：You have visited Kyoto five times.</t>
+          <t>正解（疑問文）：How many times has he visited Kyoto?</t>
         </is>
       </c>
       <c r="B82" s="27" t="n"/>
@@ -5027,10 +6866,10 @@
       <c r="I82" s="27" t="n"/>
       <c r="J82" s="57" t="n"/>
     </row>
-    <row r="83" ht="20" customHeight="1" s="6">
+    <row r="83" ht="18" customHeight="1" s="6">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>一度も訪れたことがありません。</t>
+          <t>5回訪れたことがあります。</t>
         </is>
       </c>
       <c r="B83" s="27" t="n"/>
@@ -5043,10 +6882,10 @@
       <c r="I83" s="27" t="n"/>
       <c r="J83" s="57" t="n"/>
     </row>
-    <row r="84" ht="26" customHeight="1" s="6">
+    <row r="84" ht="22" customHeight="1" s="6">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：You have never visited Kyoto.</t>
+          <t>正解（返答）：He has visited Kyoto five times.</t>
         </is>
       </c>
       <c r="B84" s="27" t="n"/>
@@ -5059,10 +6898,10 @@
       <c r="I84" s="27" t="n"/>
       <c r="J84" s="57" t="n"/>
     </row>
-    <row r="85" ht="26" customHeight="1" s="6">
+    <row r="85" ht="18" customHeight="1" s="6">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：You have not visited Kyoto before.</t>
+          <t>一度も訪れたことがありません。</t>
         </is>
       </c>
       <c r="B85" s="27" t="n"/>
@@ -5075,10 +6914,10 @@
       <c r="I85" s="27" t="n"/>
       <c r="J85" s="57" t="n"/>
     </row>
-    <row r="86" ht="26" customHeight="1" s="6">
+    <row r="86" ht="22" customHeight="1" s="6">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：You haven't visited Kyoto before.</t>
+          <t>正解（基本形）：He has never visited Kyoto.</t>
         </is>
       </c>
       <c r="B86" s="27" t="n"/>
@@ -5091,8 +6930,12 @@
       <c r="I86" s="27" t="n"/>
       <c r="J86" s="57" t="n"/>
     </row>
-    <row r="87" ht="6" customHeight="1" s="6">
-      <c r="A87" s="11" t="n"/>
+    <row r="87" ht="22" customHeight="1" s="6">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ）：He has not visited Kyoto before.</t>
+        </is>
+      </c>
       <c r="B87" s="27" t="n"/>
       <c r="C87" s="27" t="n"/>
       <c r="D87" s="27" t="n"/>
@@ -5103,30 +6946,24 @@
       <c r="I87" s="27" t="n"/>
       <c r="J87" s="57" t="n"/>
     </row>
-    <row r="88" ht="18" customHeight="1" s="6">
-      <c r="A88" s="9" t="inlineStr">
-        <is>
-          <t>6．主語は「あなたたち」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B88" s="25" t="n"/>
-      <c r="C88" s="25" t="n"/>
-      <c r="D88" s="25" t="n"/>
-      <c r="E88" s="25" t="n"/>
-      <c r="F88" s="25" t="n"/>
-      <c r="G88" s="25" t="n"/>
-      <c r="H88" s="25" t="n"/>
-      <c r="I88" s="25" t="n"/>
-      <c r="J88" s="56" t="n"/>
-    </row>
-    <row r="89" ht="60" customHeight="1" s="6">
-      <c r="A89" s="55" t="inlineStr">
-        <is>
-          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
-※回数は four times / five times のように表します。
-※否定では never または not ... before を使います。</t>
-        </is>
-      </c>
+    <row r="88" ht="22" customHeight="1" s="6">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：He hasn't visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B88" s="27" t="n"/>
+      <c r="C88" s="27" t="n"/>
+      <c r="D88" s="27" t="n"/>
+      <c r="E88" s="27" t="n"/>
+      <c r="F88" s="27" t="n"/>
+      <c r="G88" s="27" t="n"/>
+      <c r="H88" s="27" t="n"/>
+      <c r="I88" s="27" t="n"/>
+      <c r="J88" s="57" t="n"/>
+    </row>
+    <row r="89" ht="6" customHeight="1" s="6">
+      <c r="A89" s="11" t="n"/>
       <c r="B89" s="27" t="n"/>
       <c r="C89" s="27" t="n"/>
       <c r="D89" s="27" t="n"/>
@@ -5137,26 +6974,28 @@
       <c r="I89" s="27" t="n"/>
       <c r="J89" s="57" t="n"/>
     </row>
-    <row r="90" ht="20" customHeight="1" s="6">
-      <c r="A90" s="11" t="inlineStr">
-        <is>
-          <t>あなたたちは京都を4回訪れたことがあります。</t>
-        </is>
-      </c>
-      <c r="B90" s="27" t="n"/>
-      <c r="C90" s="27" t="n"/>
-      <c r="D90" s="27" t="n"/>
-      <c r="E90" s="27" t="n"/>
-      <c r="F90" s="27" t="n"/>
-      <c r="G90" s="27" t="n"/>
-      <c r="H90" s="27" t="n"/>
-      <c r="I90" s="27" t="n"/>
-      <c r="J90" s="57" t="n"/>
-    </row>
-    <row r="91" ht="26" customHeight="1" s="6">
-      <c r="A91" s="11" t="inlineStr">
-        <is>
-          <t>正解（基本形）：You have visited Kyoto four times.</t>
+    <row r="90" ht="18" customHeight="1" s="6">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>4．主語は「彼女」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B90" s="25" t="n"/>
+      <c r="C90" s="25" t="n"/>
+      <c r="D90" s="25" t="n"/>
+      <c r="E90" s="25" t="n"/>
+      <c r="F90" s="25" t="n"/>
+      <c r="G90" s="25" t="n"/>
+      <c r="H90" s="25" t="n"/>
+      <c r="I90" s="25" t="n"/>
+      <c r="J90" s="56" t="n"/>
+    </row>
+    <row r="91" ht="60" customHeight="1" s="6">
+      <c r="A91" s="55" t="inlineStr">
+        <is>
+          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
+※疑問文では ever、否定では never または not ... before を使います。
+※回数は four times / five times のように表します。</t>
         </is>
       </c>
       <c r="B91" s="27" t="n"/>
@@ -5169,26 +7008,26 @@
       <c r="I91" s="27" t="n"/>
       <c r="J91" s="57" t="n"/>
     </row>
-    <row r="92" ht="20" customHeight="1" s="6">
-      <c r="A92" s="11" t="inlineStr">
-        <is>
-          <t>あなたたちはまだ一度も京都を訪れたことがありません。</t>
-        </is>
-      </c>
-      <c r="B92" s="27" t="n"/>
-      <c r="C92" s="27" t="n"/>
-      <c r="D92" s="27" t="n"/>
-      <c r="E92" s="27" t="n"/>
-      <c r="F92" s="27" t="n"/>
-      <c r="G92" s="27" t="n"/>
-      <c r="H92" s="27" t="n"/>
-      <c r="I92" s="27" t="n"/>
-      <c r="J92" s="57" t="n"/>
-    </row>
-    <row r="93" ht="26" customHeight="1" s="6">
+    <row r="92" ht="18" customHeight="1" s="6">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>【基本】訪れたことがある・ない</t>
+        </is>
+      </c>
+      <c r="B92" s="25" t="n"/>
+      <c r="C92" s="25" t="n"/>
+      <c r="D92" s="25" t="n"/>
+      <c r="E92" s="25" t="n"/>
+      <c r="F92" s="25" t="n"/>
+      <c r="G92" s="25" t="n"/>
+      <c r="H92" s="25" t="n"/>
+      <c r="I92" s="25" t="n"/>
+      <c r="J92" s="56" t="n"/>
+    </row>
+    <row r="93" ht="18" customHeight="1" s="6">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：You have never visited Kyoto.</t>
+          <t>彼女は京都を訪れたことがあります。</t>
         </is>
       </c>
       <c r="B93" s="27" t="n"/>
@@ -5201,10 +7040,10 @@
       <c r="I93" s="27" t="n"/>
       <c r="J93" s="57" t="n"/>
     </row>
-    <row r="94" ht="26" customHeight="1" s="6">
+    <row r="94" ht="22" customHeight="1" s="6">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：You have not visited Kyoto before.</t>
+          <t>正解（基本形）：She has visited Kyoto before.</t>
         </is>
       </c>
       <c r="B94" s="27" t="n"/>
@@ -5217,10 +7056,10 @@
       <c r="I94" s="27" t="n"/>
       <c r="J94" s="57" t="n"/>
     </row>
-    <row r="95" ht="26" customHeight="1" s="6">
+    <row r="95" ht="18" customHeight="1" s="6">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：You haven't visited Kyoto before.</t>
+          <t>彼女はまだ一度も京都を訪れたことがありません。</t>
         </is>
       </c>
       <c r="B95" s="27" t="n"/>
@@ -5233,10 +7072,10 @@
       <c r="I95" s="27" t="n"/>
       <c r="J95" s="57" t="n"/>
     </row>
-    <row r="96" ht="20" customHeight="1" s="6">
+    <row r="96" ht="22" customHeight="1" s="6">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>あなたたちは京都を何回訪れたことがありますか。</t>
+          <t>正解（基本形）：She has never visited Kyoto.</t>
         </is>
       </c>
       <c r="B96" s="27" t="n"/>
@@ -5249,10 +7088,10 @@
       <c r="I96" s="27" t="n"/>
       <c r="J96" s="57" t="n"/>
     </row>
-    <row r="97" ht="26" customHeight="1" s="6">
+    <row r="97" ht="22" customHeight="1" s="6">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>正解（疑問文）：How many times have you visited Kyoto?</t>
+          <t>正解（言いかえ）：She has not visited Kyoto before.</t>
         </is>
       </c>
       <c r="B97" s="27" t="n"/>
@@ -5265,10 +7104,10 @@
       <c r="I97" s="27" t="n"/>
       <c r="J97" s="57" t="n"/>
     </row>
-    <row r="98" ht="20" customHeight="1" s="6">
+    <row r="98" ht="22" customHeight="1" s="6">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>5回訪れたことがあります。</t>
+          <t>正解（短縮形）：She hasn't visited Kyoto before.</t>
         </is>
       </c>
       <c r="B98" s="27" t="n"/>
@@ -5281,10 +7120,10 @@
       <c r="I98" s="27" t="n"/>
       <c r="J98" s="57" t="n"/>
     </row>
-    <row r="99" ht="26" customHeight="1" s="6">
+    <row r="99" ht="18" customHeight="1" s="6">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>正解（返答）：We have visited Kyoto five times.</t>
+          <t>彼女は京都を訪れたことがありますか。</t>
         </is>
       </c>
       <c r="B99" s="27" t="n"/>
@@ -5297,10 +7136,10 @@
       <c r="I99" s="27" t="n"/>
       <c r="J99" s="57" t="n"/>
     </row>
-    <row r="100" ht="20" customHeight="1" s="6">
+    <row r="100" ht="22" customHeight="1" s="6">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>一度も訪れたことがありません。</t>
+          <t>正解（疑問文）：Has she ever visited Kyoto?</t>
         </is>
       </c>
       <c r="B100" s="27" t="n"/>
@@ -5313,10 +7152,10 @@
       <c r="I100" s="27" t="n"/>
       <c r="J100" s="57" t="n"/>
     </row>
-    <row r="101" ht="26" customHeight="1" s="6">
+    <row r="101" ht="18" customHeight="1" s="6">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：We have never visited Kyoto.</t>
+          <t>はい、あります。</t>
         </is>
       </c>
       <c r="B101" s="27" t="n"/>
@@ -5329,10 +7168,10 @@
       <c r="I101" s="27" t="n"/>
       <c r="J101" s="57" t="n"/>
     </row>
-    <row r="102" ht="26" customHeight="1" s="6">
+    <row r="102" ht="22" customHeight="1" s="6">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：We have not visited Kyoto before.</t>
+          <t>正解（返答）：Yes, she has.</t>
         </is>
       </c>
       <c r="B102" s="27" t="n"/>
@@ -5345,10 +7184,10 @@
       <c r="I102" s="27" t="n"/>
       <c r="J102" s="57" t="n"/>
     </row>
-    <row r="103" ht="26" customHeight="1" s="6">
+    <row r="103" ht="18" customHeight="1" s="6">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：We haven't visited Kyoto before.</t>
+          <t>いいえ、ありません。</t>
         </is>
       </c>
       <c r="B103" s="27" t="n"/>
@@ -5361,8 +7200,12 @@
       <c r="I103" s="27" t="n"/>
       <c r="J103" s="57" t="n"/>
     </row>
-    <row r="104" ht="6" customHeight="1" s="6">
-      <c r="A104" s="11" t="n"/>
+    <row r="104" ht="22" customHeight="1" s="6">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：No, she has never visited Kyoto.</t>
+        </is>
+      </c>
       <c r="B104" s="27" t="n"/>
       <c r="C104" s="27" t="n"/>
       <c r="D104" s="27" t="n"/>
@@ -5373,28 +7216,26 @@
       <c r="I104" s="27" t="n"/>
       <c r="J104" s="57" t="n"/>
     </row>
-    <row r="105" ht="18" customHeight="1" s="6">
-      <c r="A105" s="9" t="inlineStr">
-        <is>
-          <t>7．主語は「彼ら」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B105" s="25" t="n"/>
-      <c r="C105" s="25" t="n"/>
-      <c r="D105" s="25" t="n"/>
-      <c r="E105" s="25" t="n"/>
-      <c r="F105" s="25" t="n"/>
-      <c r="G105" s="25" t="n"/>
-      <c r="H105" s="25" t="n"/>
-      <c r="I105" s="25" t="n"/>
-      <c r="J105" s="56" t="n"/>
-    </row>
-    <row r="106" ht="60" customHeight="1" s="6">
-      <c r="A106" s="55" t="inlineStr">
-        <is>
-          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
-※回数は four times / five times のように表します。
-※否定では never または not ... before を使います。</t>
+    <row r="105" ht="22" customHeight="1" s="6">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ）：No, she has not visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B105" s="27" t="n"/>
+      <c r="C105" s="27" t="n"/>
+      <c r="D105" s="27" t="n"/>
+      <c r="E105" s="27" t="n"/>
+      <c r="F105" s="27" t="n"/>
+      <c r="G105" s="27" t="n"/>
+      <c r="H105" s="27" t="n"/>
+      <c r="I105" s="27" t="n"/>
+      <c r="J105" s="57" t="n"/>
+    </row>
+    <row r="106" ht="22" customHeight="1" s="6">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：No, she hasn't visited Kyoto before.</t>
         </is>
       </c>
       <c r="B106" s="27" t="n"/>
@@ -5407,26 +7248,26 @@
       <c r="I106" s="27" t="n"/>
       <c r="J106" s="57" t="n"/>
     </row>
-    <row r="107" ht="20" customHeight="1" s="6">
-      <c r="A107" s="11" t="inlineStr">
-        <is>
-          <t>彼らは京都を4回訪れたことがあります。</t>
-        </is>
-      </c>
-      <c r="B107" s="27" t="n"/>
-      <c r="C107" s="27" t="n"/>
-      <c r="D107" s="27" t="n"/>
-      <c r="E107" s="27" t="n"/>
-      <c r="F107" s="27" t="n"/>
-      <c r="G107" s="27" t="n"/>
-      <c r="H107" s="27" t="n"/>
-      <c r="I107" s="27" t="n"/>
-      <c r="J107" s="57" t="n"/>
-    </row>
-    <row r="108" ht="26" customHeight="1" s="6">
+    <row r="107" ht="18" customHeight="1" s="6">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>【回数】何回訪れたことがあるか</t>
+        </is>
+      </c>
+      <c r="B107" s="25" t="n"/>
+      <c r="C107" s="25" t="n"/>
+      <c r="D107" s="25" t="n"/>
+      <c r="E107" s="25" t="n"/>
+      <c r="F107" s="25" t="n"/>
+      <c r="G107" s="25" t="n"/>
+      <c r="H107" s="25" t="n"/>
+      <c r="I107" s="25" t="n"/>
+      <c r="J107" s="56" t="n"/>
+    </row>
+    <row r="108" ht="18" customHeight="1" s="6">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：They have visited Kyoto four times.</t>
+          <t>彼女は京都を4回訪れたことがあります。</t>
         </is>
       </c>
       <c r="B108" s="27" t="n"/>
@@ -5439,10 +7280,10 @@
       <c r="I108" s="27" t="n"/>
       <c r="J108" s="57" t="n"/>
     </row>
-    <row r="109" ht="20" customHeight="1" s="6">
+    <row r="109" ht="22" customHeight="1" s="6">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>彼らはまだ一度も京都を訪れたことがありません。</t>
+          <t>正解（基本形）：She has visited Kyoto four times.</t>
         </is>
       </c>
       <c r="B109" s="27" t="n"/>
@@ -5455,10 +7296,10 @@
       <c r="I109" s="27" t="n"/>
       <c r="J109" s="57" t="n"/>
     </row>
-    <row r="110" ht="26" customHeight="1" s="6">
+    <row r="110" ht="18" customHeight="1" s="6">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：They have never visited Kyoto.</t>
+          <t>彼女は京都を何回訪れたことがありますか。</t>
         </is>
       </c>
       <c r="B110" s="27" t="n"/>
@@ -5471,10 +7312,10 @@
       <c r="I110" s="27" t="n"/>
       <c r="J110" s="57" t="n"/>
     </row>
-    <row r="111" ht="26" customHeight="1" s="6">
+    <row r="111" ht="22" customHeight="1" s="6">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：They have not visited Kyoto before.</t>
+          <t>正解（疑問文）：How many times has she visited Kyoto?</t>
         </is>
       </c>
       <c r="B111" s="27" t="n"/>
@@ -5487,10 +7328,10 @@
       <c r="I111" s="27" t="n"/>
       <c r="J111" s="57" t="n"/>
     </row>
-    <row r="112" ht="26" customHeight="1" s="6">
+    <row r="112" ht="18" customHeight="1" s="6">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：They haven't visited Kyoto before.</t>
+          <t>5回訪れたことがあります。</t>
         </is>
       </c>
       <c r="B112" s="27" t="n"/>
@@ -5503,10 +7344,10 @@
       <c r="I112" s="27" t="n"/>
       <c r="J112" s="57" t="n"/>
     </row>
-    <row r="113" ht="20" customHeight="1" s="6">
+    <row r="113" ht="22" customHeight="1" s="6">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>彼らは京都を何回訪れたことがありますか。</t>
+          <t>正解（返答）：She has visited Kyoto five times.</t>
         </is>
       </c>
       <c r="B113" s="27" t="n"/>
@@ -5519,10 +7360,10 @@
       <c r="I113" s="27" t="n"/>
       <c r="J113" s="57" t="n"/>
     </row>
-    <row r="114" ht="26" customHeight="1" s="6">
+    <row r="114" ht="18" customHeight="1" s="6">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>正解（疑問文）：How many times have they visited Kyoto?</t>
+          <t>一度も訪れたことがありません。</t>
         </is>
       </c>
       <c r="B114" s="27" t="n"/>
@@ -5535,10 +7376,10 @@
       <c r="I114" s="27" t="n"/>
       <c r="J114" s="57" t="n"/>
     </row>
-    <row r="115" ht="20" customHeight="1" s="6">
+    <row r="115" ht="22" customHeight="1" s="6">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>5回訪れたことがあります。</t>
+          <t>正解（基本形）：She has never visited Kyoto.</t>
         </is>
       </c>
       <c r="B115" s="27" t="n"/>
@@ -5551,10 +7392,10 @@
       <c r="I115" s="27" t="n"/>
       <c r="J115" s="57" t="n"/>
     </row>
-    <row r="116" ht="26" customHeight="1" s="6">
+    <row r="116" ht="22" customHeight="1" s="6">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>正解（返答）：They have visited Kyoto five times.</t>
+          <t>正解（言いかえ）：She has not visited Kyoto before.</t>
         </is>
       </c>
       <c r="B116" s="27" t="n"/>
@@ -5567,10 +7408,10 @@
       <c r="I116" s="27" t="n"/>
       <c r="J116" s="57" t="n"/>
     </row>
-    <row r="117" ht="20" customHeight="1" s="6">
+    <row r="117" ht="22" customHeight="1" s="6">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>一度も訪れたことがありません。</t>
+          <t>正解（短縮形）：She hasn't visited Kyoto before.</t>
         </is>
       </c>
       <c r="B117" s="27" t="n"/>
@@ -5583,12 +7424,8 @@
       <c r="I117" s="27" t="n"/>
       <c r="J117" s="57" t="n"/>
     </row>
-    <row r="118" ht="26" customHeight="1" s="6">
-      <c r="A118" s="11" t="inlineStr">
-        <is>
-          <t>正解（基本形）：They have never visited Kyoto.</t>
-        </is>
-      </c>
+    <row r="118" ht="6" customHeight="1" s="6">
+      <c r="A118" s="11" t="n"/>
       <c r="B118" s="27" t="n"/>
       <c r="C118" s="27" t="n"/>
       <c r="D118" s="27" t="n"/>
@@ -5599,26 +7436,29 @@
       <c r="I118" s="27" t="n"/>
       <c r="J118" s="57" t="n"/>
     </row>
-    <row r="119" ht="26" customHeight="1" s="6">
-      <c r="A119" s="11" t="inlineStr">
-        <is>
-          <t>正解（言いかえ）：They have not visited Kyoto before.</t>
-        </is>
-      </c>
-      <c r="B119" s="27" t="n"/>
-      <c r="C119" s="27" t="n"/>
-      <c r="D119" s="27" t="n"/>
-      <c r="E119" s="27" t="n"/>
-      <c r="F119" s="27" t="n"/>
-      <c r="G119" s="27" t="n"/>
-      <c r="H119" s="27" t="n"/>
-      <c r="I119" s="27" t="n"/>
-      <c r="J119" s="57" t="n"/>
-    </row>
-    <row r="120" ht="26" customHeight="1" s="6">
-      <c r="A120" s="11" t="inlineStr">
-        <is>
-          <t>正解（短縮形）：They haven't visited Kyoto before.</t>
+    <row r="119" ht="18" customHeight="1" s="6">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>5．主語は「私たち」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B119" s="25" t="n"/>
+      <c r="C119" s="25" t="n"/>
+      <c r="D119" s="25" t="n"/>
+      <c r="E119" s="25" t="n"/>
+      <c r="F119" s="25" t="n"/>
+      <c r="G119" s="25" t="n"/>
+      <c r="H119" s="25" t="n"/>
+      <c r="I119" s="25" t="n"/>
+      <c r="J119" s="56" t="n"/>
+    </row>
+    <row r="120" ht="60" customHeight="1" s="6">
+      <c r="A120" s="55" t="inlineStr">
+        <is>
+          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
+※疑問文では ever、否定では never または not ... before を使います。
+※回数は four times / five times のように表します。
+※相手が答える形なので、返答では I / we ではなく you を使います。</t>
         </is>
       </c>
       <c r="B120" s="27" t="n"/>
@@ -5631,40 +7471,42 @@
       <c r="I120" s="27" t="n"/>
       <c r="J120" s="57" t="n"/>
     </row>
-    <row r="121" ht="6" customHeight="1" s="6">
-      <c r="A121" s="11" t="n"/>
-      <c r="B121" s="27" t="n"/>
-      <c r="C121" s="27" t="n"/>
-      <c r="D121" s="27" t="n"/>
-      <c r="E121" s="27" t="n"/>
-      <c r="F121" s="27" t="n"/>
-      <c r="G121" s="27" t="n"/>
-      <c r="H121" s="27" t="n"/>
-      <c r="I121" s="27" t="n"/>
-      <c r="J121" s="57" t="n"/>
+    <row r="121" ht="18" customHeight="1" s="6">
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>【基本】訪れたことがある・ない</t>
+        </is>
+      </c>
+      <c r="B121" s="25" t="n"/>
+      <c r="C121" s="25" t="n"/>
+      <c r="D121" s="25" t="n"/>
+      <c r="E121" s="25" t="n"/>
+      <c r="F121" s="25" t="n"/>
+      <c r="G121" s="25" t="n"/>
+      <c r="H121" s="25" t="n"/>
+      <c r="I121" s="25" t="n"/>
+      <c r="J121" s="56" t="n"/>
     </row>
     <row r="122" ht="18" customHeight="1" s="6">
-      <c r="A122" s="9" t="inlineStr">
-        <is>
-          <t>8．主語は「リョウタロウ」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B122" s="25" t="n"/>
-      <c r="C122" s="25" t="n"/>
-      <c r="D122" s="25" t="n"/>
-      <c r="E122" s="25" t="n"/>
-      <c r="F122" s="25" t="n"/>
-      <c r="G122" s="25" t="n"/>
-      <c r="H122" s="25" t="n"/>
-      <c r="I122" s="25" t="n"/>
-      <c r="J122" s="56" t="n"/>
-    </row>
-    <row r="123" ht="60" customHeight="1" s="6">
-      <c r="A123" s="55" t="inlineStr">
-        <is>
-          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
-※回数は four times / five times のように表します。
-※否定では never または not ... before を使います。</t>
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>私たちは京都を訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B122" s="27" t="n"/>
+      <c r="C122" s="27" t="n"/>
+      <c r="D122" s="27" t="n"/>
+      <c r="E122" s="27" t="n"/>
+      <c r="F122" s="27" t="n"/>
+      <c r="G122" s="27" t="n"/>
+      <c r="H122" s="27" t="n"/>
+      <c r="I122" s="27" t="n"/>
+      <c r="J122" s="57" t="n"/>
+    </row>
+    <row r="123" ht="22" customHeight="1" s="6">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：We have visited Kyoto before.</t>
         </is>
       </c>
       <c r="B123" s="27" t="n"/>
@@ -5677,10 +7519,10 @@
       <c r="I123" s="27" t="n"/>
       <c r="J123" s="57" t="n"/>
     </row>
-    <row r="124" ht="20" customHeight="1" s="6">
+    <row r="124" ht="18" customHeight="1" s="6">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>リョウタロウは京都を4回訪れたことがあります。</t>
+          <t>私たちはまだ一度も京都を訪れたことがありません。</t>
         </is>
       </c>
       <c r="B124" s="27" t="n"/>
@@ -5693,10 +7535,10 @@
       <c r="I124" s="27" t="n"/>
       <c r="J124" s="57" t="n"/>
     </row>
-    <row r="125" ht="26" customHeight="1" s="6">
+    <row r="125" ht="22" customHeight="1" s="6">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：Ryoutarou has visited Kyoto four times.</t>
+          <t>正解（基本形）：We have never visited Kyoto.</t>
         </is>
       </c>
       <c r="B125" s="27" t="n"/>
@@ -5709,10 +7551,10 @@
       <c r="I125" s="27" t="n"/>
       <c r="J125" s="57" t="n"/>
     </row>
-    <row r="126" ht="20" customHeight="1" s="6">
+    <row r="126" ht="22" customHeight="1" s="6">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>リョウタロウはまだ一度も京都を訪れたことがありません。</t>
+          <t>正解（言いかえ）：We have not visited Kyoto before.</t>
         </is>
       </c>
       <c r="B126" s="27" t="n"/>
@@ -5725,10 +7567,10 @@
       <c r="I126" s="27" t="n"/>
       <c r="J126" s="57" t="n"/>
     </row>
-    <row r="127" ht="26" customHeight="1" s="6">
+    <row r="127" ht="22" customHeight="1" s="6">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：Ryoutarou has never visited Kyoto.</t>
+          <t>正解（短縮形）：We haven't visited Kyoto before.</t>
         </is>
       </c>
       <c r="B127" s="27" t="n"/>
@@ -5741,10 +7583,10 @@
       <c r="I127" s="27" t="n"/>
       <c r="J127" s="57" t="n"/>
     </row>
-    <row r="128" ht="26" customHeight="1" s="6">
+    <row r="128" ht="18" customHeight="1" s="6">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：Ryoutarou has not visited Kyoto before.</t>
+          <t>私たちは京都を訪れたことがありますか。</t>
         </is>
       </c>
       <c r="B128" s="27" t="n"/>
@@ -5757,10 +7599,10 @@
       <c r="I128" s="27" t="n"/>
       <c r="J128" s="57" t="n"/>
     </row>
-    <row r="129" ht="26" customHeight="1" s="6">
+    <row r="129" ht="22" customHeight="1" s="6">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：Ryoutarou hasn't visited Kyoto before.</t>
+          <t>正解（疑問文）：Have we ever visited Kyoto?</t>
         </is>
       </c>
       <c r="B129" s="27" t="n"/>
@@ -5773,10 +7615,10 @@
       <c r="I129" s="27" t="n"/>
       <c r="J129" s="57" t="n"/>
     </row>
-    <row r="130" ht="20" customHeight="1" s="6">
+    <row r="130" ht="18" customHeight="1" s="6">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>リョウタロウは京都を何回訪れたことがありますか。</t>
+          <t>はい、あります。</t>
         </is>
       </c>
       <c r="B130" s="27" t="n"/>
@@ -5789,10 +7631,10 @@
       <c r="I130" s="27" t="n"/>
       <c r="J130" s="57" t="n"/>
     </row>
-    <row r="131" ht="26" customHeight="1" s="6">
+    <row r="131" ht="22" customHeight="1" s="6">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>正解（疑問文）：How many times has Ryoutarou visited Kyoto?</t>
+          <t>正解（返答）：Yes, you have.</t>
         </is>
       </c>
       <c r="B131" s="27" t="n"/>
@@ -5805,10 +7647,10 @@
       <c r="I131" s="27" t="n"/>
       <c r="J131" s="57" t="n"/>
     </row>
-    <row r="132" ht="20" customHeight="1" s="6">
+    <row r="132" ht="18" customHeight="1" s="6">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>5回訪れたことがあります。</t>
+          <t>いいえ、ありません。</t>
         </is>
       </c>
       <c r="B132" s="27" t="n"/>
@@ -5821,10 +7663,10 @@
       <c r="I132" s="27" t="n"/>
       <c r="J132" s="57" t="n"/>
     </row>
-    <row r="133" ht="26" customHeight="1" s="6">
+    <row r="133" ht="22" customHeight="1" s="6">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>正解（返答）：He has visited Kyoto five times.</t>
+          <t>正解（基本形）：No, you have never visited Kyoto.</t>
         </is>
       </c>
       <c r="B133" s="27" t="n"/>
@@ -5837,10 +7679,10 @@
       <c r="I133" s="27" t="n"/>
       <c r="J133" s="57" t="n"/>
     </row>
-    <row r="134" ht="20" customHeight="1" s="6">
+    <row r="134" ht="22" customHeight="1" s="6">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>一度も訪れたことがありません。</t>
+          <t>正解（言いかえ）：No, you have not visited Kyoto before.</t>
         </is>
       </c>
       <c r="B134" s="27" t="n"/>
@@ -5853,10 +7695,10 @@
       <c r="I134" s="27" t="n"/>
       <c r="J134" s="57" t="n"/>
     </row>
-    <row r="135" ht="26" customHeight="1" s="6">
+    <row r="135" ht="22" customHeight="1" s="6">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：He has never visited Kyoto.</t>
+          <t>正解（短縮形）：No, you haven't visited Kyoto before.</t>
         </is>
       </c>
       <c r="B135" s="27" t="n"/>
@@ -5869,26 +7711,26 @@
       <c r="I135" s="27" t="n"/>
       <c r="J135" s="57" t="n"/>
     </row>
-    <row r="136" ht="26" customHeight="1" s="6">
-      <c r="A136" s="11" t="inlineStr">
-        <is>
-          <t>正解（言いかえ）：He has not visited Kyoto before.</t>
-        </is>
-      </c>
-      <c r="B136" s="27" t="n"/>
-      <c r="C136" s="27" t="n"/>
-      <c r="D136" s="27" t="n"/>
-      <c r="E136" s="27" t="n"/>
-      <c r="F136" s="27" t="n"/>
-      <c r="G136" s="27" t="n"/>
-      <c r="H136" s="27" t="n"/>
-      <c r="I136" s="27" t="n"/>
-      <c r="J136" s="57" t="n"/>
-    </row>
-    <row r="137" ht="26" customHeight="1" s="6">
+    <row r="136" ht="18" customHeight="1" s="6">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>【回数】何回訪れたことがあるか</t>
+        </is>
+      </c>
+      <c r="B136" s="25" t="n"/>
+      <c r="C136" s="25" t="n"/>
+      <c r="D136" s="25" t="n"/>
+      <c r="E136" s="25" t="n"/>
+      <c r="F136" s="25" t="n"/>
+      <c r="G136" s="25" t="n"/>
+      <c r="H136" s="25" t="n"/>
+      <c r="I136" s="25" t="n"/>
+      <c r="J136" s="56" t="n"/>
+    </row>
+    <row r="137" ht="18" customHeight="1" s="6">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：He hasn't visited Kyoto before.</t>
+          <t>私たちは京都を4回訪れたことがあります。</t>
         </is>
       </c>
       <c r="B137" s="27" t="n"/>
@@ -5901,8 +7743,12 @@
       <c r="I137" s="27" t="n"/>
       <c r="J137" s="57" t="n"/>
     </row>
-    <row r="138" ht="6" customHeight="1" s="6">
-      <c r="A138" s="11" t="n"/>
+    <row r="138" ht="22" customHeight="1" s="6">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：We have visited Kyoto four times.</t>
+        </is>
+      </c>
       <c r="B138" s="27" t="n"/>
       <c r="C138" s="27" t="n"/>
       <c r="D138" s="27" t="n"/>
@@ -5914,27 +7760,25 @@
       <c r="J138" s="57" t="n"/>
     </row>
     <row r="139" ht="18" customHeight="1" s="6">
-      <c r="A139" s="9" t="inlineStr">
-        <is>
-          <t>9．主語は「チサコ」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B139" s="25" t="n"/>
-      <c r="C139" s="25" t="n"/>
-      <c r="D139" s="25" t="n"/>
-      <c r="E139" s="25" t="n"/>
-      <c r="F139" s="25" t="n"/>
-      <c r="G139" s="25" t="n"/>
-      <c r="H139" s="25" t="n"/>
-      <c r="I139" s="25" t="n"/>
-      <c r="J139" s="56" t="n"/>
-    </row>
-    <row r="140" ht="60" customHeight="1" s="6">
-      <c r="A140" s="55" t="inlineStr">
-        <is>
-          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
-※回数は four times / five times のように表します。
-※否定では never または not ... before を使います。</t>
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>私たちは京都を何回訪れたことがありますか。</t>
+        </is>
+      </c>
+      <c r="B139" s="27" t="n"/>
+      <c r="C139" s="27" t="n"/>
+      <c r="D139" s="27" t="n"/>
+      <c r="E139" s="27" t="n"/>
+      <c r="F139" s="27" t="n"/>
+      <c r="G139" s="27" t="n"/>
+      <c r="H139" s="27" t="n"/>
+      <c r="I139" s="27" t="n"/>
+      <c r="J139" s="57" t="n"/>
+    </row>
+    <row r="140" ht="22" customHeight="1" s="6">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>正解（疑問文）：How many times have we visited Kyoto?</t>
         </is>
       </c>
       <c r="B140" s="27" t="n"/>
@@ -5947,10 +7791,10 @@
       <c r="I140" s="27" t="n"/>
       <c r="J140" s="57" t="n"/>
     </row>
-    <row r="141" ht="20" customHeight="1" s="6">
+    <row r="141" ht="18" customHeight="1" s="6">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>チサコは京都を4回訪れたことがあります。</t>
+          <t>5回訪れたことがあります。</t>
         </is>
       </c>
       <c r="B141" s="27" t="n"/>
@@ -5963,10 +7807,10 @@
       <c r="I141" s="27" t="n"/>
       <c r="J141" s="57" t="n"/>
     </row>
-    <row r="142" ht="26" customHeight="1" s="6">
+    <row r="142" ht="22" customHeight="1" s="6">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：Chisako has visited Kyoto four times.</t>
+          <t>正解（返答）：You have visited Kyoto five times.</t>
         </is>
       </c>
       <c r="B142" s="27" t="n"/>
@@ -5979,10 +7823,10 @@
       <c r="I142" s="27" t="n"/>
       <c r="J142" s="57" t="n"/>
     </row>
-    <row r="143" ht="20" customHeight="1" s="6">
+    <row r="143" ht="18" customHeight="1" s="6">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>チサコはまだ一度も京都を訪れたことがありません。</t>
+          <t>一度も訪れたことがありません。</t>
         </is>
       </c>
       <c r="B143" s="27" t="n"/>
@@ -5995,10 +7839,10 @@
       <c r="I143" s="27" t="n"/>
       <c r="J143" s="57" t="n"/>
     </row>
-    <row r="144" ht="26" customHeight="1" s="6">
+    <row r="144" ht="22" customHeight="1" s="6">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：Chisako has never visited Kyoto.</t>
+          <t>正解（基本形）：You have never visited Kyoto.</t>
         </is>
       </c>
       <c r="B144" s="27" t="n"/>
@@ -6011,10 +7855,10 @@
       <c r="I144" s="27" t="n"/>
       <c r="J144" s="57" t="n"/>
     </row>
-    <row r="145" ht="26" customHeight="1" s="6">
+    <row r="145" ht="22" customHeight="1" s="6">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：Chisako has not visited Kyoto before.</t>
+          <t>正解（言いかえ）：You have not visited Kyoto before.</t>
         </is>
       </c>
       <c r="B145" s="27" t="n"/>
@@ -6027,10 +7871,10 @@
       <c r="I145" s="27" t="n"/>
       <c r="J145" s="57" t="n"/>
     </row>
-    <row r="146" ht="26" customHeight="1" s="6">
+    <row r="146" ht="22" customHeight="1" s="6">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：Chisako hasn't visited Kyoto before.</t>
+          <t>正解（短縮形）：You haven't visited Kyoto before.</t>
         </is>
       </c>
       <c r="B146" s="27" t="n"/>
@@ -6043,12 +7887,8 @@
       <c r="I146" s="27" t="n"/>
       <c r="J146" s="57" t="n"/>
     </row>
-    <row r="147" ht="20" customHeight="1" s="6">
-      <c r="A147" s="11" t="inlineStr">
-        <is>
-          <t>チサコは京都を何回訪れたことがありますか。</t>
-        </is>
-      </c>
+    <row r="147" ht="6" customHeight="1" s="6">
+      <c r="A147" s="11" t="n"/>
       <c r="B147" s="27" t="n"/>
       <c r="C147" s="27" t="n"/>
       <c r="D147" s="27" t="n"/>
@@ -6059,26 +7899,28 @@
       <c r="I147" s="27" t="n"/>
       <c r="J147" s="57" t="n"/>
     </row>
-    <row r="148" ht="26" customHeight="1" s="6">
-      <c r="A148" s="11" t="inlineStr">
-        <is>
-          <t>正解（疑問文）：How many times has Chisako visited Kyoto?</t>
-        </is>
-      </c>
-      <c r="B148" s="27" t="n"/>
-      <c r="C148" s="27" t="n"/>
-      <c r="D148" s="27" t="n"/>
-      <c r="E148" s="27" t="n"/>
-      <c r="F148" s="27" t="n"/>
-      <c r="G148" s="27" t="n"/>
-      <c r="H148" s="27" t="n"/>
-      <c r="I148" s="27" t="n"/>
-      <c r="J148" s="57" t="n"/>
-    </row>
-    <row r="149" ht="20" customHeight="1" s="6">
-      <c r="A149" s="11" t="inlineStr">
-        <is>
-          <t>5回訪れたことがあります。</t>
+    <row r="148" ht="18" customHeight="1" s="6">
+      <c r="A148" s="9" t="inlineStr">
+        <is>
+          <t>6．主語は「あなたたち」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B148" s="25" t="n"/>
+      <c r="C148" s="25" t="n"/>
+      <c r="D148" s="25" t="n"/>
+      <c r="E148" s="25" t="n"/>
+      <c r="F148" s="25" t="n"/>
+      <c r="G148" s="25" t="n"/>
+      <c r="H148" s="25" t="n"/>
+      <c r="I148" s="25" t="n"/>
+      <c r="J148" s="56" t="n"/>
+    </row>
+    <row r="149" ht="60" customHeight="1" s="6">
+      <c r="A149" s="55" t="inlineStr">
+        <is>
+          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
+※疑問文では ever、否定では never または not ... before を使います。
+※回数は four times / five times のように表します。</t>
         </is>
       </c>
       <c r="B149" s="27" t="n"/>
@@ -6091,26 +7933,26 @@
       <c r="I149" s="27" t="n"/>
       <c r="J149" s="57" t="n"/>
     </row>
-    <row r="150" ht="26" customHeight="1" s="6">
-      <c r="A150" s="11" t="inlineStr">
-        <is>
-          <t>正解（返答）：She has visited Kyoto five times.</t>
-        </is>
-      </c>
-      <c r="B150" s="27" t="n"/>
-      <c r="C150" s="27" t="n"/>
-      <c r="D150" s="27" t="n"/>
-      <c r="E150" s="27" t="n"/>
-      <c r="F150" s="27" t="n"/>
-      <c r="G150" s="27" t="n"/>
-      <c r="H150" s="27" t="n"/>
-      <c r="I150" s="27" t="n"/>
-      <c r="J150" s="57" t="n"/>
-    </row>
-    <row r="151" ht="20" customHeight="1" s="6">
+    <row r="150" ht="18" customHeight="1" s="6">
+      <c r="A150" s="9" t="inlineStr">
+        <is>
+          <t>【基本】訪れたことがある・ない</t>
+        </is>
+      </c>
+      <c r="B150" s="25" t="n"/>
+      <c r="C150" s="25" t="n"/>
+      <c r="D150" s="25" t="n"/>
+      <c r="E150" s="25" t="n"/>
+      <c r="F150" s="25" t="n"/>
+      <c r="G150" s="25" t="n"/>
+      <c r="H150" s="25" t="n"/>
+      <c r="I150" s="25" t="n"/>
+      <c r="J150" s="56" t="n"/>
+    </row>
+    <row r="151" ht="18" customHeight="1" s="6">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>一度も訪れたことがありません。</t>
+          <t>あなたたちは京都を訪れたことがあります。</t>
         </is>
       </c>
       <c r="B151" s="27" t="n"/>
@@ -6123,10 +7965,10 @@
       <c r="I151" s="27" t="n"/>
       <c r="J151" s="57" t="n"/>
     </row>
-    <row r="152" ht="26" customHeight="1" s="6">
+    <row r="152" ht="22" customHeight="1" s="6">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：She has never visited Kyoto.</t>
+          <t>正解（基本形）：You have visited Kyoto before.</t>
         </is>
       </c>
       <c r="B152" s="27" t="n"/>
@@ -6139,10 +7981,10 @@
       <c r="I152" s="27" t="n"/>
       <c r="J152" s="57" t="n"/>
     </row>
-    <row r="153" ht="26" customHeight="1" s="6">
+    <row r="153" ht="18" customHeight="1" s="6">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：She has not visited Kyoto before.</t>
+          <t>あなたたちはまだ一度も京都を訪れたことがありません。</t>
         </is>
       </c>
       <c r="B153" s="27" t="n"/>
@@ -6155,10 +7997,10 @@
       <c r="I153" s="27" t="n"/>
       <c r="J153" s="57" t="n"/>
     </row>
-    <row r="154" ht="26" customHeight="1" s="6">
+    <row r="154" ht="22" customHeight="1" s="6">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：She hasn't visited Kyoto before.</t>
+          <t>正解（基本形）：You have never visited Kyoto.</t>
         </is>
       </c>
       <c r="B154" s="27" t="n"/>
@@ -6171,8 +8013,12 @@
       <c r="I154" s="27" t="n"/>
       <c r="J154" s="57" t="n"/>
     </row>
-    <row r="155" ht="6" customHeight="1" s="6">
-      <c r="A155" s="11" t="n"/>
+    <row r="155" ht="22" customHeight="1" s="6">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ）：You have not visited Kyoto before.</t>
+        </is>
+      </c>
       <c r="B155" s="27" t="n"/>
       <c r="C155" s="27" t="n"/>
       <c r="D155" s="27" t="n"/>
@@ -6183,176 +8029,2002 @@
       <c r="I155" s="27" t="n"/>
       <c r="J155" s="57" t="n"/>
     </row>
+    <row r="156" ht="22" customHeight="1" s="6">
+      <c r="A156" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：You haven't visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B156" s="27" t="n"/>
+      <c r="C156" s="27" t="n"/>
+      <c r="D156" s="27" t="n"/>
+      <c r="E156" s="27" t="n"/>
+      <c r="F156" s="27" t="n"/>
+      <c r="G156" s="27" t="n"/>
+      <c r="H156" s="27" t="n"/>
+      <c r="I156" s="27" t="n"/>
+      <c r="J156" s="57" t="n"/>
+    </row>
+    <row r="157" ht="18" customHeight="1" s="6">
+      <c r="A157" s="11" t="inlineStr">
+        <is>
+          <t>あなたたちは京都を訪れたことがありますか。</t>
+        </is>
+      </c>
+      <c r="B157" s="27" t="n"/>
+      <c r="C157" s="27" t="n"/>
+      <c r="D157" s="27" t="n"/>
+      <c r="E157" s="27" t="n"/>
+      <c r="F157" s="27" t="n"/>
+      <c r="G157" s="27" t="n"/>
+      <c r="H157" s="27" t="n"/>
+      <c r="I157" s="27" t="n"/>
+      <c r="J157" s="57" t="n"/>
+    </row>
+    <row r="158" ht="22" customHeight="1" s="6">
+      <c r="A158" s="11" t="inlineStr">
+        <is>
+          <t>正解（疑問文）：Have you ever visited Kyoto?</t>
+        </is>
+      </c>
+      <c r="B158" s="27" t="n"/>
+      <c r="C158" s="27" t="n"/>
+      <c r="D158" s="27" t="n"/>
+      <c r="E158" s="27" t="n"/>
+      <c r="F158" s="27" t="n"/>
+      <c r="G158" s="27" t="n"/>
+      <c r="H158" s="27" t="n"/>
+      <c r="I158" s="27" t="n"/>
+      <c r="J158" s="57" t="n"/>
+    </row>
+    <row r="159" ht="18" customHeight="1" s="6">
+      <c r="A159" s="11" t="inlineStr">
+        <is>
+          <t>はい、あります。</t>
+        </is>
+      </c>
+      <c r="B159" s="27" t="n"/>
+      <c r="C159" s="27" t="n"/>
+      <c r="D159" s="27" t="n"/>
+      <c r="E159" s="27" t="n"/>
+      <c r="F159" s="27" t="n"/>
+      <c r="G159" s="27" t="n"/>
+      <c r="H159" s="27" t="n"/>
+      <c r="I159" s="27" t="n"/>
+      <c r="J159" s="57" t="n"/>
+    </row>
+    <row r="160" ht="22" customHeight="1" s="6">
+      <c r="A160" s="11" t="inlineStr">
+        <is>
+          <t>正解（返答）：Yes, we have.</t>
+        </is>
+      </c>
+      <c r="B160" s="27" t="n"/>
+      <c r="C160" s="27" t="n"/>
+      <c r="D160" s="27" t="n"/>
+      <c r="E160" s="27" t="n"/>
+      <c r="F160" s="27" t="n"/>
+      <c r="G160" s="27" t="n"/>
+      <c r="H160" s="27" t="n"/>
+      <c r="I160" s="27" t="n"/>
+      <c r="J160" s="57" t="n"/>
+    </row>
+    <row r="161" ht="18" customHeight="1" s="6">
+      <c r="A161" s="11" t="inlineStr">
+        <is>
+          <t>いいえ、ありません。</t>
+        </is>
+      </c>
+      <c r="B161" s="27" t="n"/>
+      <c r="C161" s="27" t="n"/>
+      <c r="D161" s="27" t="n"/>
+      <c r="E161" s="27" t="n"/>
+      <c r="F161" s="27" t="n"/>
+      <c r="G161" s="27" t="n"/>
+      <c r="H161" s="27" t="n"/>
+      <c r="I161" s="27" t="n"/>
+      <c r="J161" s="57" t="n"/>
+    </row>
+    <row r="162" ht="22" customHeight="1" s="6">
+      <c r="A162" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：No, We have never visited Kyoto.</t>
+        </is>
+      </c>
+      <c r="B162" s="27" t="n"/>
+      <c r="C162" s="27" t="n"/>
+      <c r="D162" s="27" t="n"/>
+      <c r="E162" s="27" t="n"/>
+      <c r="F162" s="27" t="n"/>
+      <c r="G162" s="27" t="n"/>
+      <c r="H162" s="27" t="n"/>
+      <c r="I162" s="27" t="n"/>
+      <c r="J162" s="57" t="n"/>
+    </row>
+    <row r="163" ht="22" customHeight="1" s="6">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ）：No, We have not visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B163" s="27" t="n"/>
+      <c r="C163" s="27" t="n"/>
+      <c r="D163" s="27" t="n"/>
+      <c r="E163" s="27" t="n"/>
+      <c r="F163" s="27" t="n"/>
+      <c r="G163" s="27" t="n"/>
+      <c r="H163" s="27" t="n"/>
+      <c r="I163" s="27" t="n"/>
+      <c r="J163" s="57" t="n"/>
+    </row>
+    <row r="164" ht="22" customHeight="1" s="6">
+      <c r="A164" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：No, We haven't visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B164" s="27" t="n"/>
+      <c r="C164" s="27" t="n"/>
+      <c r="D164" s="27" t="n"/>
+      <c r="E164" s="27" t="n"/>
+      <c r="F164" s="27" t="n"/>
+      <c r="G164" s="27" t="n"/>
+      <c r="H164" s="27" t="n"/>
+      <c r="I164" s="27" t="n"/>
+      <c r="J164" s="57" t="n"/>
+    </row>
+    <row r="165" ht="18" customHeight="1" s="6">
+      <c r="A165" s="9" t="inlineStr">
+        <is>
+          <t>【回数】何回訪れたことがあるか</t>
+        </is>
+      </c>
+      <c r="B165" s="25" t="n"/>
+      <c r="C165" s="25" t="n"/>
+      <c r="D165" s="25" t="n"/>
+      <c r="E165" s="25" t="n"/>
+      <c r="F165" s="25" t="n"/>
+      <c r="G165" s="25" t="n"/>
+      <c r="H165" s="25" t="n"/>
+      <c r="I165" s="25" t="n"/>
+      <c r="J165" s="56" t="n"/>
+    </row>
+    <row r="166" ht="18" customHeight="1" s="6">
+      <c r="A166" s="11" t="inlineStr">
+        <is>
+          <t>あなたたちは京都を4回訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B166" s="27" t="n"/>
+      <c r="C166" s="27" t="n"/>
+      <c r="D166" s="27" t="n"/>
+      <c r="E166" s="27" t="n"/>
+      <c r="F166" s="27" t="n"/>
+      <c r="G166" s="27" t="n"/>
+      <c r="H166" s="27" t="n"/>
+      <c r="I166" s="27" t="n"/>
+      <c r="J166" s="57" t="n"/>
+    </row>
+    <row r="167" ht="22" customHeight="1" s="6">
+      <c r="A167" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：You have visited Kyoto four times.</t>
+        </is>
+      </c>
+      <c r="B167" s="27" t="n"/>
+      <c r="C167" s="27" t="n"/>
+      <c r="D167" s="27" t="n"/>
+      <c r="E167" s="27" t="n"/>
+      <c r="F167" s="27" t="n"/>
+      <c r="G167" s="27" t="n"/>
+      <c r="H167" s="27" t="n"/>
+      <c r="I167" s="27" t="n"/>
+      <c r="J167" s="57" t="n"/>
+    </row>
+    <row r="168" ht="18" customHeight="1" s="6">
+      <c r="A168" s="11" t="inlineStr">
+        <is>
+          <t>あなたたちは京都を何回訪れたことがありますか。</t>
+        </is>
+      </c>
+      <c r="B168" s="27" t="n"/>
+      <c r="C168" s="27" t="n"/>
+      <c r="D168" s="27" t="n"/>
+      <c r="E168" s="27" t="n"/>
+      <c r="F168" s="27" t="n"/>
+      <c r="G168" s="27" t="n"/>
+      <c r="H168" s="27" t="n"/>
+      <c r="I168" s="27" t="n"/>
+      <c r="J168" s="57" t="n"/>
+    </row>
+    <row r="169" ht="22" customHeight="1" s="6">
+      <c r="A169" s="11" t="inlineStr">
+        <is>
+          <t>正解（疑問文）：How many times have you visited Kyoto?</t>
+        </is>
+      </c>
+      <c r="B169" s="27" t="n"/>
+      <c r="C169" s="27" t="n"/>
+      <c r="D169" s="27" t="n"/>
+      <c r="E169" s="27" t="n"/>
+      <c r="F169" s="27" t="n"/>
+      <c r="G169" s="27" t="n"/>
+      <c r="H169" s="27" t="n"/>
+      <c r="I169" s="27" t="n"/>
+      <c r="J169" s="57" t="n"/>
+    </row>
+    <row r="170" ht="18" customHeight="1" s="6">
+      <c r="A170" s="11" t="inlineStr">
+        <is>
+          <t>5回訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B170" s="27" t="n"/>
+      <c r="C170" s="27" t="n"/>
+      <c r="D170" s="27" t="n"/>
+      <c r="E170" s="27" t="n"/>
+      <c r="F170" s="27" t="n"/>
+      <c r="G170" s="27" t="n"/>
+      <c r="H170" s="27" t="n"/>
+      <c r="I170" s="27" t="n"/>
+      <c r="J170" s="57" t="n"/>
+    </row>
+    <row r="171" ht="22" customHeight="1" s="6">
+      <c r="A171" s="11" t="inlineStr">
+        <is>
+          <t>正解（返答）：We have visited Kyoto five times.</t>
+        </is>
+      </c>
+      <c r="B171" s="27" t="n"/>
+      <c r="C171" s="27" t="n"/>
+      <c r="D171" s="27" t="n"/>
+      <c r="E171" s="27" t="n"/>
+      <c r="F171" s="27" t="n"/>
+      <c r="G171" s="27" t="n"/>
+      <c r="H171" s="27" t="n"/>
+      <c r="I171" s="27" t="n"/>
+      <c r="J171" s="57" t="n"/>
+    </row>
+    <row r="172" ht="18" customHeight="1" s="6">
+      <c r="A172" s="11" t="inlineStr">
+        <is>
+          <t>一度も訪れたことがありません。</t>
+        </is>
+      </c>
+      <c r="B172" s="27" t="n"/>
+      <c r="C172" s="27" t="n"/>
+      <c r="D172" s="27" t="n"/>
+      <c r="E172" s="27" t="n"/>
+      <c r="F172" s="27" t="n"/>
+      <c r="G172" s="27" t="n"/>
+      <c r="H172" s="27" t="n"/>
+      <c r="I172" s="27" t="n"/>
+      <c r="J172" s="57" t="n"/>
+    </row>
+    <row r="173" ht="22" customHeight="1" s="6">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：We have never visited Kyoto.</t>
+        </is>
+      </c>
+      <c r="B173" s="27" t="n"/>
+      <c r="C173" s="27" t="n"/>
+      <c r="D173" s="27" t="n"/>
+      <c r="E173" s="27" t="n"/>
+      <c r="F173" s="27" t="n"/>
+      <c r="G173" s="27" t="n"/>
+      <c r="H173" s="27" t="n"/>
+      <c r="I173" s="27" t="n"/>
+      <c r="J173" s="57" t="n"/>
+    </row>
+    <row r="174" ht="22" customHeight="1" s="6">
+      <c r="A174" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ）：We have not visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B174" s="27" t="n"/>
+      <c r="C174" s="27" t="n"/>
+      <c r="D174" s="27" t="n"/>
+      <c r="E174" s="27" t="n"/>
+      <c r="F174" s="27" t="n"/>
+      <c r="G174" s="27" t="n"/>
+      <c r="H174" s="27" t="n"/>
+      <c r="I174" s="27" t="n"/>
+      <c r="J174" s="57" t="n"/>
+    </row>
+    <row r="175" ht="22" customHeight="1" s="6">
+      <c r="A175" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：We haven't visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B175" s="27" t="n"/>
+      <c r="C175" s="27" t="n"/>
+      <c r="D175" s="27" t="n"/>
+      <c r="E175" s="27" t="n"/>
+      <c r="F175" s="27" t="n"/>
+      <c r="G175" s="27" t="n"/>
+      <c r="H175" s="27" t="n"/>
+      <c r="I175" s="27" t="n"/>
+      <c r="J175" s="57" t="n"/>
+    </row>
+    <row r="176" ht="6" customHeight="1" s="6">
+      <c r="A176" s="11" t="n"/>
+      <c r="B176" s="27" t="n"/>
+      <c r="C176" s="27" t="n"/>
+      <c r="D176" s="27" t="n"/>
+      <c r="E176" s="27" t="n"/>
+      <c r="F176" s="27" t="n"/>
+      <c r="G176" s="27" t="n"/>
+      <c r="H176" s="27" t="n"/>
+      <c r="I176" s="27" t="n"/>
+      <c r="J176" s="57" t="n"/>
+    </row>
+    <row r="177" ht="18" customHeight="1" s="6">
+      <c r="A177" s="9" t="inlineStr">
+        <is>
+          <t>7．主語は「彼ら」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B177" s="25" t="n"/>
+      <c r="C177" s="25" t="n"/>
+      <c r="D177" s="25" t="n"/>
+      <c r="E177" s="25" t="n"/>
+      <c r="F177" s="25" t="n"/>
+      <c r="G177" s="25" t="n"/>
+      <c r="H177" s="25" t="n"/>
+      <c r="I177" s="25" t="n"/>
+      <c r="J177" s="56" t="n"/>
+    </row>
+    <row r="178" ht="60" customHeight="1" s="6">
+      <c r="A178" s="55" t="inlineStr">
+        <is>
+          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
+※疑問文では ever、否定では never または not ... before を使います。
+※回数は four times / five times のように表します。</t>
+        </is>
+      </c>
+      <c r="B178" s="27" t="n"/>
+      <c r="C178" s="27" t="n"/>
+      <c r="D178" s="27" t="n"/>
+      <c r="E178" s="27" t="n"/>
+      <c r="F178" s="27" t="n"/>
+      <c r="G178" s="27" t="n"/>
+      <c r="H178" s="27" t="n"/>
+      <c r="I178" s="27" t="n"/>
+      <c r="J178" s="57" t="n"/>
+    </row>
+    <row r="179" ht="18" customHeight="1" s="6">
+      <c r="A179" s="9" t="inlineStr">
+        <is>
+          <t>【基本】訪れたことがある・ない</t>
+        </is>
+      </c>
+      <c r="B179" s="25" t="n"/>
+      <c r="C179" s="25" t="n"/>
+      <c r="D179" s="25" t="n"/>
+      <c r="E179" s="25" t="n"/>
+      <c r="F179" s="25" t="n"/>
+      <c r="G179" s="25" t="n"/>
+      <c r="H179" s="25" t="n"/>
+      <c r="I179" s="25" t="n"/>
+      <c r="J179" s="56" t="n"/>
+    </row>
+    <row r="180" ht="18" customHeight="1" s="6">
+      <c r="A180" s="11" t="inlineStr">
+        <is>
+          <t>彼らは京都を訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B180" s="27" t="n"/>
+      <c r="C180" s="27" t="n"/>
+      <c r="D180" s="27" t="n"/>
+      <c r="E180" s="27" t="n"/>
+      <c r="F180" s="27" t="n"/>
+      <c r="G180" s="27" t="n"/>
+      <c r="H180" s="27" t="n"/>
+      <c r="I180" s="27" t="n"/>
+      <c r="J180" s="57" t="n"/>
+    </row>
+    <row r="181" ht="22" customHeight="1" s="6">
+      <c r="A181" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：They have visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B181" s="27" t="n"/>
+      <c r="C181" s="27" t="n"/>
+      <c r="D181" s="27" t="n"/>
+      <c r="E181" s="27" t="n"/>
+      <c r="F181" s="27" t="n"/>
+      <c r="G181" s="27" t="n"/>
+      <c r="H181" s="27" t="n"/>
+      <c r="I181" s="27" t="n"/>
+      <c r="J181" s="57" t="n"/>
+    </row>
+    <row r="182" ht="18" customHeight="1" s="6">
+      <c r="A182" s="11" t="inlineStr">
+        <is>
+          <t>彼らはまだ一度も京都を訪れたことがありません。</t>
+        </is>
+      </c>
+      <c r="B182" s="27" t="n"/>
+      <c r="C182" s="27" t="n"/>
+      <c r="D182" s="27" t="n"/>
+      <c r="E182" s="27" t="n"/>
+      <c r="F182" s="27" t="n"/>
+      <c r="G182" s="27" t="n"/>
+      <c r="H182" s="27" t="n"/>
+      <c r="I182" s="27" t="n"/>
+      <c r="J182" s="57" t="n"/>
+    </row>
+    <row r="183" ht="22" customHeight="1" s="6">
+      <c r="A183" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：They have never visited Kyoto.</t>
+        </is>
+      </c>
+      <c r="B183" s="27" t="n"/>
+      <c r="C183" s="27" t="n"/>
+      <c r="D183" s="27" t="n"/>
+      <c r="E183" s="27" t="n"/>
+      <c r="F183" s="27" t="n"/>
+      <c r="G183" s="27" t="n"/>
+      <c r="H183" s="27" t="n"/>
+      <c r="I183" s="27" t="n"/>
+      <c r="J183" s="57" t="n"/>
+    </row>
+    <row r="184" ht="22" customHeight="1" s="6">
+      <c r="A184" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ）：They have not visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B184" s="27" t="n"/>
+      <c r="C184" s="27" t="n"/>
+      <c r="D184" s="27" t="n"/>
+      <c r="E184" s="27" t="n"/>
+      <c r="F184" s="27" t="n"/>
+      <c r="G184" s="27" t="n"/>
+      <c r="H184" s="27" t="n"/>
+      <c r="I184" s="27" t="n"/>
+      <c r="J184" s="57" t="n"/>
+    </row>
+    <row r="185" ht="22" customHeight="1" s="6">
+      <c r="A185" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：They haven't visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B185" s="27" t="n"/>
+      <c r="C185" s="27" t="n"/>
+      <c r="D185" s="27" t="n"/>
+      <c r="E185" s="27" t="n"/>
+      <c r="F185" s="27" t="n"/>
+      <c r="G185" s="27" t="n"/>
+      <c r="H185" s="27" t="n"/>
+      <c r="I185" s="27" t="n"/>
+      <c r="J185" s="57" t="n"/>
+    </row>
+    <row r="186" ht="18" customHeight="1" s="6">
+      <c r="A186" s="11" t="inlineStr">
+        <is>
+          <t>彼らは京都を訪れたことがありますか。</t>
+        </is>
+      </c>
+      <c r="B186" s="27" t="n"/>
+      <c r="C186" s="27" t="n"/>
+      <c r="D186" s="27" t="n"/>
+      <c r="E186" s="27" t="n"/>
+      <c r="F186" s="27" t="n"/>
+      <c r="G186" s="27" t="n"/>
+      <c r="H186" s="27" t="n"/>
+      <c r="I186" s="27" t="n"/>
+      <c r="J186" s="57" t="n"/>
+    </row>
+    <row r="187" ht="22" customHeight="1" s="6">
+      <c r="A187" s="11" t="inlineStr">
+        <is>
+          <t>正解（疑問文）：Have they ever visited Kyoto?</t>
+        </is>
+      </c>
+      <c r="B187" s="27" t="n"/>
+      <c r="C187" s="27" t="n"/>
+      <c r="D187" s="27" t="n"/>
+      <c r="E187" s="27" t="n"/>
+      <c r="F187" s="27" t="n"/>
+      <c r="G187" s="27" t="n"/>
+      <c r="H187" s="27" t="n"/>
+      <c r="I187" s="27" t="n"/>
+      <c r="J187" s="57" t="n"/>
+    </row>
+    <row r="188" ht="18" customHeight="1" s="6">
+      <c r="A188" s="11" t="inlineStr">
+        <is>
+          <t>はい、あります。</t>
+        </is>
+      </c>
+      <c r="B188" s="27" t="n"/>
+      <c r="C188" s="27" t="n"/>
+      <c r="D188" s="27" t="n"/>
+      <c r="E188" s="27" t="n"/>
+      <c r="F188" s="27" t="n"/>
+      <c r="G188" s="27" t="n"/>
+      <c r="H188" s="27" t="n"/>
+      <c r="I188" s="27" t="n"/>
+      <c r="J188" s="57" t="n"/>
+    </row>
+    <row r="189" ht="22" customHeight="1" s="6">
+      <c r="A189" s="11" t="inlineStr">
+        <is>
+          <t>正解（返答）：Yes, they have.</t>
+        </is>
+      </c>
+      <c r="B189" s="27" t="n"/>
+      <c r="C189" s="27" t="n"/>
+      <c r="D189" s="27" t="n"/>
+      <c r="E189" s="27" t="n"/>
+      <c r="F189" s="27" t="n"/>
+      <c r="G189" s="27" t="n"/>
+      <c r="H189" s="27" t="n"/>
+      <c r="I189" s="27" t="n"/>
+      <c r="J189" s="57" t="n"/>
+    </row>
+    <row r="190" ht="18" customHeight="1" s="6">
+      <c r="A190" s="11" t="inlineStr">
+        <is>
+          <t>いいえ、ありません。</t>
+        </is>
+      </c>
+      <c r="B190" s="27" t="n"/>
+      <c r="C190" s="27" t="n"/>
+      <c r="D190" s="27" t="n"/>
+      <c r="E190" s="27" t="n"/>
+      <c r="F190" s="27" t="n"/>
+      <c r="G190" s="27" t="n"/>
+      <c r="H190" s="27" t="n"/>
+      <c r="I190" s="27" t="n"/>
+      <c r="J190" s="57" t="n"/>
+    </row>
+    <row r="191" ht="22" customHeight="1" s="6">
+      <c r="A191" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：No, they have never visited Kyoto.</t>
+        </is>
+      </c>
+      <c r="B191" s="27" t="n"/>
+      <c r="C191" s="27" t="n"/>
+      <c r="D191" s="27" t="n"/>
+      <c r="E191" s="27" t="n"/>
+      <c r="F191" s="27" t="n"/>
+      <c r="G191" s="27" t="n"/>
+      <c r="H191" s="27" t="n"/>
+      <c r="I191" s="27" t="n"/>
+      <c r="J191" s="57" t="n"/>
+    </row>
+    <row r="192" ht="22" customHeight="1" s="6">
+      <c r="A192" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ）：No, they have not visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B192" s="27" t="n"/>
+      <c r="C192" s="27" t="n"/>
+      <c r="D192" s="27" t="n"/>
+      <c r="E192" s="27" t="n"/>
+      <c r="F192" s="27" t="n"/>
+      <c r="G192" s="27" t="n"/>
+      <c r="H192" s="27" t="n"/>
+      <c r="I192" s="27" t="n"/>
+      <c r="J192" s="57" t="n"/>
+    </row>
+    <row r="193" ht="22" customHeight="1" s="6">
+      <c r="A193" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：No, they haven't visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B193" s="27" t="n"/>
+      <c r="C193" s="27" t="n"/>
+      <c r="D193" s="27" t="n"/>
+      <c r="E193" s="27" t="n"/>
+      <c r="F193" s="27" t="n"/>
+      <c r="G193" s="27" t="n"/>
+      <c r="H193" s="27" t="n"/>
+      <c r="I193" s="27" t="n"/>
+      <c r="J193" s="57" t="n"/>
+    </row>
+    <row r="194" ht="18" customHeight="1" s="6">
+      <c r="A194" s="9" t="inlineStr">
+        <is>
+          <t>【回数】何回訪れたことがあるか</t>
+        </is>
+      </c>
+      <c r="B194" s="25" t="n"/>
+      <c r="C194" s="25" t="n"/>
+      <c r="D194" s="25" t="n"/>
+      <c r="E194" s="25" t="n"/>
+      <c r="F194" s="25" t="n"/>
+      <c r="G194" s="25" t="n"/>
+      <c r="H194" s="25" t="n"/>
+      <c r="I194" s="25" t="n"/>
+      <c r="J194" s="56" t="n"/>
+    </row>
+    <row r="195" ht="18" customHeight="1" s="6">
+      <c r="A195" s="11" t="inlineStr">
+        <is>
+          <t>彼らは京都を4回訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B195" s="27" t="n"/>
+      <c r="C195" s="27" t="n"/>
+      <c r="D195" s="27" t="n"/>
+      <c r="E195" s="27" t="n"/>
+      <c r="F195" s="27" t="n"/>
+      <c r="G195" s="27" t="n"/>
+      <c r="H195" s="27" t="n"/>
+      <c r="I195" s="27" t="n"/>
+      <c r="J195" s="57" t="n"/>
+    </row>
+    <row r="196" ht="22" customHeight="1" s="6">
+      <c r="A196" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：They have visited Kyoto four times.</t>
+        </is>
+      </c>
+      <c r="B196" s="27" t="n"/>
+      <c r="C196" s="27" t="n"/>
+      <c r="D196" s="27" t="n"/>
+      <c r="E196" s="27" t="n"/>
+      <c r="F196" s="27" t="n"/>
+      <c r="G196" s="27" t="n"/>
+      <c r="H196" s="27" t="n"/>
+      <c r="I196" s="27" t="n"/>
+      <c r="J196" s="57" t="n"/>
+    </row>
+    <row r="197" ht="18" customHeight="1" s="6">
+      <c r="A197" s="11" t="inlineStr">
+        <is>
+          <t>彼らは京都を何回訪れたことがありますか。</t>
+        </is>
+      </c>
+      <c r="B197" s="27" t="n"/>
+      <c r="C197" s="27" t="n"/>
+      <c r="D197" s="27" t="n"/>
+      <c r="E197" s="27" t="n"/>
+      <c r="F197" s="27" t="n"/>
+      <c r="G197" s="27" t="n"/>
+      <c r="H197" s="27" t="n"/>
+      <c r="I197" s="27" t="n"/>
+      <c r="J197" s="57" t="n"/>
+    </row>
+    <row r="198" ht="22" customHeight="1" s="6">
+      <c r="A198" s="11" t="inlineStr">
+        <is>
+          <t>正解（疑問文）：How many times have they visited Kyoto?</t>
+        </is>
+      </c>
+      <c r="B198" s="27" t="n"/>
+      <c r="C198" s="27" t="n"/>
+      <c r="D198" s="27" t="n"/>
+      <c r="E198" s="27" t="n"/>
+      <c r="F198" s="27" t="n"/>
+      <c r="G198" s="27" t="n"/>
+      <c r="H198" s="27" t="n"/>
+      <c r="I198" s="27" t="n"/>
+      <c r="J198" s="57" t="n"/>
+    </row>
+    <row r="199" ht="18" customHeight="1" s="6">
+      <c r="A199" s="11" t="inlineStr">
+        <is>
+          <t>5回訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B199" s="27" t="n"/>
+      <c r="C199" s="27" t="n"/>
+      <c r="D199" s="27" t="n"/>
+      <c r="E199" s="27" t="n"/>
+      <c r="F199" s="27" t="n"/>
+      <c r="G199" s="27" t="n"/>
+      <c r="H199" s="27" t="n"/>
+      <c r="I199" s="27" t="n"/>
+      <c r="J199" s="57" t="n"/>
+    </row>
+    <row r="200" ht="22" customHeight="1" s="6">
+      <c r="A200" s="11" t="inlineStr">
+        <is>
+          <t>正解（返答）：They have visited Kyoto five times.</t>
+        </is>
+      </c>
+      <c r="B200" s="27" t="n"/>
+      <c r="C200" s="27" t="n"/>
+      <c r="D200" s="27" t="n"/>
+      <c r="E200" s="27" t="n"/>
+      <c r="F200" s="27" t="n"/>
+      <c r="G200" s="27" t="n"/>
+      <c r="H200" s="27" t="n"/>
+      <c r="I200" s="27" t="n"/>
+      <c r="J200" s="57" t="n"/>
+    </row>
+    <row r="201" ht="18" customHeight="1" s="6">
+      <c r="A201" s="11" t="inlineStr">
+        <is>
+          <t>一度も訪れたことがありません。</t>
+        </is>
+      </c>
+      <c r="B201" s="27" t="n"/>
+      <c r="C201" s="27" t="n"/>
+      <c r="D201" s="27" t="n"/>
+      <c r="E201" s="27" t="n"/>
+      <c r="F201" s="27" t="n"/>
+      <c r="G201" s="27" t="n"/>
+      <c r="H201" s="27" t="n"/>
+      <c r="I201" s="27" t="n"/>
+      <c r="J201" s="57" t="n"/>
+    </row>
+    <row r="202" ht="22" customHeight="1" s="6">
+      <c r="A202" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：They have never visited Kyoto.</t>
+        </is>
+      </c>
+      <c r="B202" s="27" t="n"/>
+      <c r="C202" s="27" t="n"/>
+      <c r="D202" s="27" t="n"/>
+      <c r="E202" s="27" t="n"/>
+      <c r="F202" s="27" t="n"/>
+      <c r="G202" s="27" t="n"/>
+      <c r="H202" s="27" t="n"/>
+      <c r="I202" s="27" t="n"/>
+      <c r="J202" s="57" t="n"/>
+    </row>
+    <row r="203" ht="22" customHeight="1" s="6">
+      <c r="A203" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ）：They have not visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B203" s="27" t="n"/>
+      <c r="C203" s="27" t="n"/>
+      <c r="D203" s="27" t="n"/>
+      <c r="E203" s="27" t="n"/>
+      <c r="F203" s="27" t="n"/>
+      <c r="G203" s="27" t="n"/>
+      <c r="H203" s="27" t="n"/>
+      <c r="I203" s="27" t="n"/>
+      <c r="J203" s="57" t="n"/>
+    </row>
+    <row r="204" ht="22" customHeight="1" s="6">
+      <c r="A204" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：They haven't visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B204" s="27" t="n"/>
+      <c r="C204" s="27" t="n"/>
+      <c r="D204" s="27" t="n"/>
+      <c r="E204" s="27" t="n"/>
+      <c r="F204" s="27" t="n"/>
+      <c r="G204" s="27" t="n"/>
+      <c r="H204" s="27" t="n"/>
+      <c r="I204" s="27" t="n"/>
+      <c r="J204" s="57" t="n"/>
+    </row>
+    <row r="205" ht="6" customHeight="1" s="6">
+      <c r="A205" s="11" t="n"/>
+      <c r="B205" s="27" t="n"/>
+      <c r="C205" s="27" t="n"/>
+      <c r="D205" s="27" t="n"/>
+      <c r="E205" s="27" t="n"/>
+      <c r="F205" s="27" t="n"/>
+      <c r="G205" s="27" t="n"/>
+      <c r="H205" s="27" t="n"/>
+      <c r="I205" s="27" t="n"/>
+      <c r="J205" s="57" t="n"/>
+    </row>
+    <row r="206" ht="18" customHeight="1" s="6">
+      <c r="A206" s="9" t="inlineStr">
+        <is>
+          <t>8．主語は「リョウタロウ」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B206" s="25" t="n"/>
+      <c r="C206" s="25" t="n"/>
+      <c r="D206" s="25" t="n"/>
+      <c r="E206" s="25" t="n"/>
+      <c r="F206" s="25" t="n"/>
+      <c r="G206" s="25" t="n"/>
+      <c r="H206" s="25" t="n"/>
+      <c r="I206" s="25" t="n"/>
+      <c r="J206" s="56" t="n"/>
+    </row>
+    <row r="207" ht="60" customHeight="1" s="6">
+      <c r="A207" s="55" t="inlineStr">
+        <is>
+          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
+※疑問文では ever、否定では never または not ... before を使います。
+※回数は four times / five times のように表します。</t>
+        </is>
+      </c>
+      <c r="B207" s="27" t="n"/>
+      <c r="C207" s="27" t="n"/>
+      <c r="D207" s="27" t="n"/>
+      <c r="E207" s="27" t="n"/>
+      <c r="F207" s="27" t="n"/>
+      <c r="G207" s="27" t="n"/>
+      <c r="H207" s="27" t="n"/>
+      <c r="I207" s="27" t="n"/>
+      <c r="J207" s="57" t="n"/>
+    </row>
+    <row r="208" ht="18" customHeight="1" s="6">
+      <c r="A208" s="9" t="inlineStr">
+        <is>
+          <t>【基本】訪れたことがある・ない</t>
+        </is>
+      </c>
+      <c r="B208" s="25" t="n"/>
+      <c r="C208" s="25" t="n"/>
+      <c r="D208" s="25" t="n"/>
+      <c r="E208" s="25" t="n"/>
+      <c r="F208" s="25" t="n"/>
+      <c r="G208" s="25" t="n"/>
+      <c r="H208" s="25" t="n"/>
+      <c r="I208" s="25" t="n"/>
+      <c r="J208" s="56" t="n"/>
+    </row>
+    <row r="209" ht="18" customHeight="1" s="6">
+      <c r="A209" s="11" t="inlineStr">
+        <is>
+          <t>リョウタロウは京都を訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B209" s="27" t="n"/>
+      <c r="C209" s="27" t="n"/>
+      <c r="D209" s="27" t="n"/>
+      <c r="E209" s="27" t="n"/>
+      <c r="F209" s="27" t="n"/>
+      <c r="G209" s="27" t="n"/>
+      <c r="H209" s="27" t="n"/>
+      <c r="I209" s="27" t="n"/>
+      <c r="J209" s="57" t="n"/>
+    </row>
+    <row r="210" ht="22" customHeight="1" s="6">
+      <c r="A210" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：Ryoutarou has visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B210" s="27" t="n"/>
+      <c r="C210" s="27" t="n"/>
+      <c r="D210" s="27" t="n"/>
+      <c r="E210" s="27" t="n"/>
+      <c r="F210" s="27" t="n"/>
+      <c r="G210" s="27" t="n"/>
+      <c r="H210" s="27" t="n"/>
+      <c r="I210" s="27" t="n"/>
+      <c r="J210" s="57" t="n"/>
+    </row>
+    <row r="211" ht="18" customHeight="1" s="6">
+      <c r="A211" s="11" t="inlineStr">
+        <is>
+          <t>リョウタロウはまだ一度も京都を訪れたことがありません。</t>
+        </is>
+      </c>
+      <c r="B211" s="27" t="n"/>
+      <c r="C211" s="27" t="n"/>
+      <c r="D211" s="27" t="n"/>
+      <c r="E211" s="27" t="n"/>
+      <c r="F211" s="27" t="n"/>
+      <c r="G211" s="27" t="n"/>
+      <c r="H211" s="27" t="n"/>
+      <c r="I211" s="27" t="n"/>
+      <c r="J211" s="57" t="n"/>
+    </row>
+    <row r="212" ht="22" customHeight="1" s="6">
+      <c r="A212" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：Ryoutarou has never visited Kyoto.</t>
+        </is>
+      </c>
+      <c r="B212" s="27" t="n"/>
+      <c r="C212" s="27" t="n"/>
+      <c r="D212" s="27" t="n"/>
+      <c r="E212" s="27" t="n"/>
+      <c r="F212" s="27" t="n"/>
+      <c r="G212" s="27" t="n"/>
+      <c r="H212" s="27" t="n"/>
+      <c r="I212" s="27" t="n"/>
+      <c r="J212" s="57" t="n"/>
+    </row>
+    <row r="213" ht="22" customHeight="1" s="6">
+      <c r="A213" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ）：Ryoutarou has not visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B213" s="27" t="n"/>
+      <c r="C213" s="27" t="n"/>
+      <c r="D213" s="27" t="n"/>
+      <c r="E213" s="27" t="n"/>
+      <c r="F213" s="27" t="n"/>
+      <c r="G213" s="27" t="n"/>
+      <c r="H213" s="27" t="n"/>
+      <c r="I213" s="27" t="n"/>
+      <c r="J213" s="57" t="n"/>
+    </row>
+    <row r="214" ht="22" customHeight="1" s="6">
+      <c r="A214" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：Ryoutarou hasn't visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B214" s="27" t="n"/>
+      <c r="C214" s="27" t="n"/>
+      <c r="D214" s="27" t="n"/>
+      <c r="E214" s="27" t="n"/>
+      <c r="F214" s="27" t="n"/>
+      <c r="G214" s="27" t="n"/>
+      <c r="H214" s="27" t="n"/>
+      <c r="I214" s="27" t="n"/>
+      <c r="J214" s="57" t="n"/>
+    </row>
+    <row r="215" ht="18" customHeight="1" s="6">
+      <c r="A215" s="11" t="inlineStr">
+        <is>
+          <t>リョウタロウは京都を訪れたことがありますか。</t>
+        </is>
+      </c>
+      <c r="B215" s="27" t="n"/>
+      <c r="C215" s="27" t="n"/>
+      <c r="D215" s="27" t="n"/>
+      <c r="E215" s="27" t="n"/>
+      <c r="F215" s="27" t="n"/>
+      <c r="G215" s="27" t="n"/>
+      <c r="H215" s="27" t="n"/>
+      <c r="I215" s="27" t="n"/>
+      <c r="J215" s="57" t="n"/>
+    </row>
+    <row r="216" ht="22" customHeight="1" s="6">
+      <c r="A216" s="11" t="inlineStr">
+        <is>
+          <t>正解（疑問文）：Has Ryoutarou ever visited Kyoto?</t>
+        </is>
+      </c>
+      <c r="B216" s="27" t="n"/>
+      <c r="C216" s="27" t="n"/>
+      <c r="D216" s="27" t="n"/>
+      <c r="E216" s="27" t="n"/>
+      <c r="F216" s="27" t="n"/>
+      <c r="G216" s="27" t="n"/>
+      <c r="H216" s="27" t="n"/>
+      <c r="I216" s="27" t="n"/>
+      <c r="J216" s="57" t="n"/>
+    </row>
+    <row r="217" ht="18" customHeight="1" s="6">
+      <c r="A217" s="11" t="inlineStr">
+        <is>
+          <t>はい、あります。</t>
+        </is>
+      </c>
+      <c r="B217" s="27" t="n"/>
+      <c r="C217" s="27" t="n"/>
+      <c r="D217" s="27" t="n"/>
+      <c r="E217" s="27" t="n"/>
+      <c r="F217" s="27" t="n"/>
+      <c r="G217" s="27" t="n"/>
+      <c r="H217" s="27" t="n"/>
+      <c r="I217" s="27" t="n"/>
+      <c r="J217" s="57" t="n"/>
+    </row>
+    <row r="218" ht="22" customHeight="1" s="6">
+      <c r="A218" s="11" t="inlineStr">
+        <is>
+          <t>正解（返答）：Yes, he has.</t>
+        </is>
+      </c>
+      <c r="B218" s="27" t="n"/>
+      <c r="C218" s="27" t="n"/>
+      <c r="D218" s="27" t="n"/>
+      <c r="E218" s="27" t="n"/>
+      <c r="F218" s="27" t="n"/>
+      <c r="G218" s="27" t="n"/>
+      <c r="H218" s="27" t="n"/>
+      <c r="I218" s="27" t="n"/>
+      <c r="J218" s="57" t="n"/>
+    </row>
+    <row r="219" ht="18" customHeight="1" s="6">
+      <c r="A219" s="11" t="inlineStr">
+        <is>
+          <t>いいえ、ありません。</t>
+        </is>
+      </c>
+      <c r="B219" s="27" t="n"/>
+      <c r="C219" s="27" t="n"/>
+      <c r="D219" s="27" t="n"/>
+      <c r="E219" s="27" t="n"/>
+      <c r="F219" s="27" t="n"/>
+      <c r="G219" s="27" t="n"/>
+      <c r="H219" s="27" t="n"/>
+      <c r="I219" s="27" t="n"/>
+      <c r="J219" s="57" t="n"/>
+    </row>
+    <row r="220" ht="22" customHeight="1" s="6">
+      <c r="A220" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：No, he has never visited Kyoto.</t>
+        </is>
+      </c>
+      <c r="B220" s="27" t="n"/>
+      <c r="C220" s="27" t="n"/>
+      <c r="D220" s="27" t="n"/>
+      <c r="E220" s="27" t="n"/>
+      <c r="F220" s="27" t="n"/>
+      <c r="G220" s="27" t="n"/>
+      <c r="H220" s="27" t="n"/>
+      <c r="I220" s="27" t="n"/>
+      <c r="J220" s="57" t="n"/>
+    </row>
+    <row r="221" ht="22" customHeight="1" s="6">
+      <c r="A221" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ）：No, he has not visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B221" s="27" t="n"/>
+      <c r="C221" s="27" t="n"/>
+      <c r="D221" s="27" t="n"/>
+      <c r="E221" s="27" t="n"/>
+      <c r="F221" s="27" t="n"/>
+      <c r="G221" s="27" t="n"/>
+      <c r="H221" s="27" t="n"/>
+      <c r="I221" s="27" t="n"/>
+      <c r="J221" s="57" t="n"/>
+    </row>
+    <row r="222" ht="22" customHeight="1" s="6">
+      <c r="A222" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：No, he hasn't visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B222" s="27" t="n"/>
+      <c r="C222" s="27" t="n"/>
+      <c r="D222" s="27" t="n"/>
+      <c r="E222" s="27" t="n"/>
+      <c r="F222" s="27" t="n"/>
+      <c r="G222" s="27" t="n"/>
+      <c r="H222" s="27" t="n"/>
+      <c r="I222" s="27" t="n"/>
+      <c r="J222" s="57" t="n"/>
+    </row>
+    <row r="223" ht="18" customHeight="1" s="6">
+      <c r="A223" s="9" t="inlineStr">
+        <is>
+          <t>【回数】何回訪れたことがあるか</t>
+        </is>
+      </c>
+      <c r="B223" s="25" t="n"/>
+      <c r="C223" s="25" t="n"/>
+      <c r="D223" s="25" t="n"/>
+      <c r="E223" s="25" t="n"/>
+      <c r="F223" s="25" t="n"/>
+      <c r="G223" s="25" t="n"/>
+      <c r="H223" s="25" t="n"/>
+      <c r="I223" s="25" t="n"/>
+      <c r="J223" s="56" t="n"/>
+    </row>
+    <row r="224" ht="18" customHeight="1" s="6">
+      <c r="A224" s="11" t="inlineStr">
+        <is>
+          <t>リョウタロウは京都を4回訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B224" s="27" t="n"/>
+      <c r="C224" s="27" t="n"/>
+      <c r="D224" s="27" t="n"/>
+      <c r="E224" s="27" t="n"/>
+      <c r="F224" s="27" t="n"/>
+      <c r="G224" s="27" t="n"/>
+      <c r="H224" s="27" t="n"/>
+      <c r="I224" s="27" t="n"/>
+      <c r="J224" s="57" t="n"/>
+    </row>
+    <row r="225" ht="22" customHeight="1" s="6">
+      <c r="A225" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：Ryoutarou has visited Kyoto four times.</t>
+        </is>
+      </c>
+      <c r="B225" s="27" t="n"/>
+      <c r="C225" s="27" t="n"/>
+      <c r="D225" s="27" t="n"/>
+      <c r="E225" s="27" t="n"/>
+      <c r="F225" s="27" t="n"/>
+      <c r="G225" s="27" t="n"/>
+      <c r="H225" s="27" t="n"/>
+      <c r="I225" s="27" t="n"/>
+      <c r="J225" s="57" t="n"/>
+    </row>
+    <row r="226" ht="18" customHeight="1" s="6">
+      <c r="A226" s="11" t="inlineStr">
+        <is>
+          <t>リョウタロウは京都を何回訪れたことがありますか。</t>
+        </is>
+      </c>
+      <c r="B226" s="27" t="n"/>
+      <c r="C226" s="27" t="n"/>
+      <c r="D226" s="27" t="n"/>
+      <c r="E226" s="27" t="n"/>
+      <c r="F226" s="27" t="n"/>
+      <c r="G226" s="27" t="n"/>
+      <c r="H226" s="27" t="n"/>
+      <c r="I226" s="27" t="n"/>
+      <c r="J226" s="57" t="n"/>
+    </row>
+    <row r="227" ht="22" customHeight="1" s="6">
+      <c r="A227" s="11" t="inlineStr">
+        <is>
+          <t>正解（疑問文）：How many times has Ryoutarou visited Kyoto?</t>
+        </is>
+      </c>
+      <c r="B227" s="27" t="n"/>
+      <c r="C227" s="27" t="n"/>
+      <c r="D227" s="27" t="n"/>
+      <c r="E227" s="27" t="n"/>
+      <c r="F227" s="27" t="n"/>
+      <c r="G227" s="27" t="n"/>
+      <c r="H227" s="27" t="n"/>
+      <c r="I227" s="27" t="n"/>
+      <c r="J227" s="57" t="n"/>
+    </row>
+    <row r="228" ht="18" customHeight="1" s="6">
+      <c r="A228" s="11" t="inlineStr">
+        <is>
+          <t>5回訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B228" s="27" t="n"/>
+      <c r="C228" s="27" t="n"/>
+      <c r="D228" s="27" t="n"/>
+      <c r="E228" s="27" t="n"/>
+      <c r="F228" s="27" t="n"/>
+      <c r="G228" s="27" t="n"/>
+      <c r="H228" s="27" t="n"/>
+      <c r="I228" s="27" t="n"/>
+      <c r="J228" s="57" t="n"/>
+    </row>
+    <row r="229" ht="22" customHeight="1" s="6">
+      <c r="A229" s="11" t="inlineStr">
+        <is>
+          <t>正解（返答）：He has visited Kyoto five times.</t>
+        </is>
+      </c>
+      <c r="B229" s="27" t="n"/>
+      <c r="C229" s="27" t="n"/>
+      <c r="D229" s="27" t="n"/>
+      <c r="E229" s="27" t="n"/>
+      <c r="F229" s="27" t="n"/>
+      <c r="G229" s="27" t="n"/>
+      <c r="H229" s="27" t="n"/>
+      <c r="I229" s="27" t="n"/>
+      <c r="J229" s="57" t="n"/>
+    </row>
+    <row r="230" ht="18" customHeight="1" s="6">
+      <c r="A230" s="11" t="inlineStr">
+        <is>
+          <t>一度も訪れたことがありません。</t>
+        </is>
+      </c>
+      <c r="B230" s="27" t="n"/>
+      <c r="C230" s="27" t="n"/>
+      <c r="D230" s="27" t="n"/>
+      <c r="E230" s="27" t="n"/>
+      <c r="F230" s="27" t="n"/>
+      <c r="G230" s="27" t="n"/>
+      <c r="H230" s="27" t="n"/>
+      <c r="I230" s="27" t="n"/>
+      <c r="J230" s="57" t="n"/>
+    </row>
+    <row r="231" ht="22" customHeight="1" s="6">
+      <c r="A231" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：He has never visited Kyoto.</t>
+        </is>
+      </c>
+      <c r="B231" s="27" t="n"/>
+      <c r="C231" s="27" t="n"/>
+      <c r="D231" s="27" t="n"/>
+      <c r="E231" s="27" t="n"/>
+      <c r="F231" s="27" t="n"/>
+      <c r="G231" s="27" t="n"/>
+      <c r="H231" s="27" t="n"/>
+      <c r="I231" s="27" t="n"/>
+      <c r="J231" s="57" t="n"/>
+    </row>
+    <row r="232" ht="22" customHeight="1" s="6">
+      <c r="A232" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ）：He has not visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B232" s="27" t="n"/>
+      <c r="C232" s="27" t="n"/>
+      <c r="D232" s="27" t="n"/>
+      <c r="E232" s="27" t="n"/>
+      <c r="F232" s="27" t="n"/>
+      <c r="G232" s="27" t="n"/>
+      <c r="H232" s="27" t="n"/>
+      <c r="I232" s="27" t="n"/>
+      <c r="J232" s="57" t="n"/>
+    </row>
+    <row r="233" ht="22" customHeight="1" s="6">
+      <c r="A233" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：He hasn't visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B233" s="27" t="n"/>
+      <c r="C233" s="27" t="n"/>
+      <c r="D233" s="27" t="n"/>
+      <c r="E233" s="27" t="n"/>
+      <c r="F233" s="27" t="n"/>
+      <c r="G233" s="27" t="n"/>
+      <c r="H233" s="27" t="n"/>
+      <c r="I233" s="27" t="n"/>
+      <c r="J233" s="57" t="n"/>
+    </row>
+    <row r="234" ht="6" customHeight="1" s="6">
+      <c r="A234" s="11" t="n"/>
+      <c r="B234" s="27" t="n"/>
+      <c r="C234" s="27" t="n"/>
+      <c r="D234" s="27" t="n"/>
+      <c r="E234" s="27" t="n"/>
+      <c r="F234" s="27" t="n"/>
+      <c r="G234" s="27" t="n"/>
+      <c r="H234" s="27" t="n"/>
+      <c r="I234" s="27" t="n"/>
+      <c r="J234" s="57" t="n"/>
+    </row>
+    <row r="235" ht="18" customHeight="1" s="6">
+      <c r="A235" s="9" t="inlineStr">
+        <is>
+          <t>9．主語は「チサコ」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B235" s="25" t="n"/>
+      <c r="C235" s="25" t="n"/>
+      <c r="D235" s="25" t="n"/>
+      <c r="E235" s="25" t="n"/>
+      <c r="F235" s="25" t="n"/>
+      <c r="G235" s="25" t="n"/>
+      <c r="H235" s="25" t="n"/>
+      <c r="I235" s="25" t="n"/>
+      <c r="J235" s="56" t="n"/>
+    </row>
+    <row r="236" ht="60" customHeight="1" s="6">
+      <c r="A236" s="55" t="inlineStr">
+        <is>
+          <t>※経験用法は have / has + 過去分詞で「〜したことがある」を表します。
+※疑問文では ever、否定では never または not ... before を使います。
+※回数は four times / five times のように表します。</t>
+        </is>
+      </c>
+      <c r="B236" s="27" t="n"/>
+      <c r="C236" s="27" t="n"/>
+      <c r="D236" s="27" t="n"/>
+      <c r="E236" s="27" t="n"/>
+      <c r="F236" s="27" t="n"/>
+      <c r="G236" s="27" t="n"/>
+      <c r="H236" s="27" t="n"/>
+      <c r="I236" s="27" t="n"/>
+      <c r="J236" s="57" t="n"/>
+    </row>
+    <row r="237" ht="18" customHeight="1" s="6">
+      <c r="A237" s="9" t="inlineStr">
+        <is>
+          <t>【基本】訪れたことがある・ない</t>
+        </is>
+      </c>
+      <c r="B237" s="25" t="n"/>
+      <c r="C237" s="25" t="n"/>
+      <c r="D237" s="25" t="n"/>
+      <c r="E237" s="25" t="n"/>
+      <c r="F237" s="25" t="n"/>
+      <c r="G237" s="25" t="n"/>
+      <c r="H237" s="25" t="n"/>
+      <c r="I237" s="25" t="n"/>
+      <c r="J237" s="56" t="n"/>
+    </row>
+    <row r="238" ht="18" customHeight="1" s="6">
+      <c r="A238" s="11" t="inlineStr">
+        <is>
+          <t>チサコは京都を訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B238" s="27" t="n"/>
+      <c r="C238" s="27" t="n"/>
+      <c r="D238" s="27" t="n"/>
+      <c r="E238" s="27" t="n"/>
+      <c r="F238" s="27" t="n"/>
+      <c r="G238" s="27" t="n"/>
+      <c r="H238" s="27" t="n"/>
+      <c r="I238" s="27" t="n"/>
+      <c r="J238" s="57" t="n"/>
+    </row>
+    <row r="239" ht="22" customHeight="1" s="6">
+      <c r="A239" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：Chisako has visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B239" s="27" t="n"/>
+      <c r="C239" s="27" t="n"/>
+      <c r="D239" s="27" t="n"/>
+      <c r="E239" s="27" t="n"/>
+      <c r="F239" s="27" t="n"/>
+      <c r="G239" s="27" t="n"/>
+      <c r="H239" s="27" t="n"/>
+      <c r="I239" s="27" t="n"/>
+      <c r="J239" s="57" t="n"/>
+    </row>
+    <row r="240" ht="18" customHeight="1" s="6">
+      <c r="A240" s="11" t="inlineStr">
+        <is>
+          <t>チサコはまだ一度も京都を訪れたことがありません。</t>
+        </is>
+      </c>
+      <c r="B240" s="27" t="n"/>
+      <c r="C240" s="27" t="n"/>
+      <c r="D240" s="27" t="n"/>
+      <c r="E240" s="27" t="n"/>
+      <c r="F240" s="27" t="n"/>
+      <c r="G240" s="27" t="n"/>
+      <c r="H240" s="27" t="n"/>
+      <c r="I240" s="27" t="n"/>
+      <c r="J240" s="57" t="n"/>
+    </row>
+    <row r="241" ht="22" customHeight="1" s="6">
+      <c r="A241" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：Chisako has never visited Kyoto.</t>
+        </is>
+      </c>
+      <c r="B241" s="27" t="n"/>
+      <c r="C241" s="27" t="n"/>
+      <c r="D241" s="27" t="n"/>
+      <c r="E241" s="27" t="n"/>
+      <c r="F241" s="27" t="n"/>
+      <c r="G241" s="27" t="n"/>
+      <c r="H241" s="27" t="n"/>
+      <c r="I241" s="27" t="n"/>
+      <c r="J241" s="57" t="n"/>
+    </row>
+    <row r="242" ht="22" customHeight="1" s="6">
+      <c r="A242" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ）：Chisako has not visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B242" s="27" t="n"/>
+      <c r="C242" s="27" t="n"/>
+      <c r="D242" s="27" t="n"/>
+      <c r="E242" s="27" t="n"/>
+      <c r="F242" s="27" t="n"/>
+      <c r="G242" s="27" t="n"/>
+      <c r="H242" s="27" t="n"/>
+      <c r="I242" s="27" t="n"/>
+      <c r="J242" s="57" t="n"/>
+    </row>
+    <row r="243" ht="22" customHeight="1" s="6">
+      <c r="A243" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：Chisako hasn't visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B243" s="27" t="n"/>
+      <c r="C243" s="27" t="n"/>
+      <c r="D243" s="27" t="n"/>
+      <c r="E243" s="27" t="n"/>
+      <c r="F243" s="27" t="n"/>
+      <c r="G243" s="27" t="n"/>
+      <c r="H243" s="27" t="n"/>
+      <c r="I243" s="27" t="n"/>
+      <c r="J243" s="57" t="n"/>
+    </row>
+    <row r="244" ht="18" customHeight="1" s="6">
+      <c r="A244" s="11" t="inlineStr">
+        <is>
+          <t>チサコは京都を訪れたことがありますか。</t>
+        </is>
+      </c>
+      <c r="B244" s="27" t="n"/>
+      <c r="C244" s="27" t="n"/>
+      <c r="D244" s="27" t="n"/>
+      <c r="E244" s="27" t="n"/>
+      <c r="F244" s="27" t="n"/>
+      <c r="G244" s="27" t="n"/>
+      <c r="H244" s="27" t="n"/>
+      <c r="I244" s="27" t="n"/>
+      <c r="J244" s="57" t="n"/>
+    </row>
+    <row r="245" ht="22" customHeight="1" s="6">
+      <c r="A245" s="11" t="inlineStr">
+        <is>
+          <t>正解（疑問文）：Has Chisako ever visited Kyoto?</t>
+        </is>
+      </c>
+      <c r="B245" s="27" t="n"/>
+      <c r="C245" s="27" t="n"/>
+      <c r="D245" s="27" t="n"/>
+      <c r="E245" s="27" t="n"/>
+      <c r="F245" s="27" t="n"/>
+      <c r="G245" s="27" t="n"/>
+      <c r="H245" s="27" t="n"/>
+      <c r="I245" s="27" t="n"/>
+      <c r="J245" s="57" t="n"/>
+    </row>
+    <row r="246" ht="18" customHeight="1" s="6">
+      <c r="A246" s="11" t="inlineStr">
+        <is>
+          <t>はい、あります。</t>
+        </is>
+      </c>
+      <c r="B246" s="27" t="n"/>
+      <c r="C246" s="27" t="n"/>
+      <c r="D246" s="27" t="n"/>
+      <c r="E246" s="27" t="n"/>
+      <c r="F246" s="27" t="n"/>
+      <c r="G246" s="27" t="n"/>
+      <c r="H246" s="27" t="n"/>
+      <c r="I246" s="27" t="n"/>
+      <c r="J246" s="57" t="n"/>
+    </row>
+    <row r="247" ht="22" customHeight="1" s="6">
+      <c r="A247" s="11" t="inlineStr">
+        <is>
+          <t>正解（返答）：Yes, she has.</t>
+        </is>
+      </c>
+      <c r="B247" s="27" t="n"/>
+      <c r="C247" s="27" t="n"/>
+      <c r="D247" s="27" t="n"/>
+      <c r="E247" s="27" t="n"/>
+      <c r="F247" s="27" t="n"/>
+      <c r="G247" s="27" t="n"/>
+      <c r="H247" s="27" t="n"/>
+      <c r="I247" s="27" t="n"/>
+      <c r="J247" s="57" t="n"/>
+    </row>
+    <row r="248" ht="18" customHeight="1" s="6">
+      <c r="A248" s="11" t="inlineStr">
+        <is>
+          <t>いいえ、ありません。</t>
+        </is>
+      </c>
+      <c r="B248" s="27" t="n"/>
+      <c r="C248" s="27" t="n"/>
+      <c r="D248" s="27" t="n"/>
+      <c r="E248" s="27" t="n"/>
+      <c r="F248" s="27" t="n"/>
+      <c r="G248" s="27" t="n"/>
+      <c r="H248" s="27" t="n"/>
+      <c r="I248" s="27" t="n"/>
+      <c r="J248" s="57" t="n"/>
+    </row>
+    <row r="249" ht="22" customHeight="1" s="6">
+      <c r="A249" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：No, she has never visited Kyoto.</t>
+        </is>
+      </c>
+      <c r="B249" s="27" t="n"/>
+      <c r="C249" s="27" t="n"/>
+      <c r="D249" s="27" t="n"/>
+      <c r="E249" s="27" t="n"/>
+      <c r="F249" s="27" t="n"/>
+      <c r="G249" s="27" t="n"/>
+      <c r="H249" s="27" t="n"/>
+      <c r="I249" s="27" t="n"/>
+      <c r="J249" s="57" t="n"/>
+    </row>
+    <row r="250" ht="22" customHeight="1" s="6">
+      <c r="A250" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ）：No, she has not visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B250" s="27" t="n"/>
+      <c r="C250" s="27" t="n"/>
+      <c r="D250" s="27" t="n"/>
+      <c r="E250" s="27" t="n"/>
+      <c r="F250" s="27" t="n"/>
+      <c r="G250" s="27" t="n"/>
+      <c r="H250" s="27" t="n"/>
+      <c r="I250" s="27" t="n"/>
+      <c r="J250" s="57" t="n"/>
+    </row>
+    <row r="251" ht="22" customHeight="1" s="6">
+      <c r="A251" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：No, she hasn't visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B251" s="27" t="n"/>
+      <c r="C251" s="27" t="n"/>
+      <c r="D251" s="27" t="n"/>
+      <c r="E251" s="27" t="n"/>
+      <c r="F251" s="27" t="n"/>
+      <c r="G251" s="27" t="n"/>
+      <c r="H251" s="27" t="n"/>
+      <c r="I251" s="27" t="n"/>
+      <c r="J251" s="57" t="n"/>
+    </row>
+    <row r="252" ht="18" customHeight="1" s="6">
+      <c r="A252" s="9" t="inlineStr">
+        <is>
+          <t>【回数】何回訪れたことがあるか</t>
+        </is>
+      </c>
+      <c r="B252" s="25" t="n"/>
+      <c r="C252" s="25" t="n"/>
+      <c r="D252" s="25" t="n"/>
+      <c r="E252" s="25" t="n"/>
+      <c r="F252" s="25" t="n"/>
+      <c r="G252" s="25" t="n"/>
+      <c r="H252" s="25" t="n"/>
+      <c r="I252" s="25" t="n"/>
+      <c r="J252" s="56" t="n"/>
+    </row>
+    <row r="253" ht="18" customHeight="1" s="6">
+      <c r="A253" s="11" t="inlineStr">
+        <is>
+          <t>チサコは京都を4回訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B253" s="27" t="n"/>
+      <c r="C253" s="27" t="n"/>
+      <c r="D253" s="27" t="n"/>
+      <c r="E253" s="27" t="n"/>
+      <c r="F253" s="27" t="n"/>
+      <c r="G253" s="27" t="n"/>
+      <c r="H253" s="27" t="n"/>
+      <c r="I253" s="27" t="n"/>
+      <c r="J253" s="57" t="n"/>
+    </row>
+    <row r="254" ht="22" customHeight="1" s="6">
+      <c r="A254" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：Chisako has visited Kyoto four times.</t>
+        </is>
+      </c>
+      <c r="B254" s="27" t="n"/>
+      <c r="C254" s="27" t="n"/>
+      <c r="D254" s="27" t="n"/>
+      <c r="E254" s="27" t="n"/>
+      <c r="F254" s="27" t="n"/>
+      <c r="G254" s="27" t="n"/>
+      <c r="H254" s="27" t="n"/>
+      <c r="I254" s="27" t="n"/>
+      <c r="J254" s="57" t="n"/>
+    </row>
+    <row r="255" ht="18" customHeight="1" s="6">
+      <c r="A255" s="11" t="inlineStr">
+        <is>
+          <t>チサコは京都を何回訪れたことがありますか。</t>
+        </is>
+      </c>
+      <c r="B255" s="27" t="n"/>
+      <c r="C255" s="27" t="n"/>
+      <c r="D255" s="27" t="n"/>
+      <c r="E255" s="27" t="n"/>
+      <c r="F255" s="27" t="n"/>
+      <c r="G255" s="27" t="n"/>
+      <c r="H255" s="27" t="n"/>
+      <c r="I255" s="27" t="n"/>
+      <c r="J255" s="57" t="n"/>
+    </row>
+    <row r="256" ht="22" customHeight="1" s="6">
+      <c r="A256" s="11" t="inlineStr">
+        <is>
+          <t>正解（疑問文）：How many times has Chisako visited Kyoto?</t>
+        </is>
+      </c>
+      <c r="B256" s="27" t="n"/>
+      <c r="C256" s="27" t="n"/>
+      <c r="D256" s="27" t="n"/>
+      <c r="E256" s="27" t="n"/>
+      <c r="F256" s="27" t="n"/>
+      <c r="G256" s="27" t="n"/>
+      <c r="H256" s="27" t="n"/>
+      <c r="I256" s="27" t="n"/>
+      <c r="J256" s="57" t="n"/>
+    </row>
+    <row r="257" ht="18" customHeight="1" s="6">
+      <c r="A257" s="11" t="inlineStr">
+        <is>
+          <t>5回訪れたことがあります。</t>
+        </is>
+      </c>
+      <c r="B257" s="27" t="n"/>
+      <c r="C257" s="27" t="n"/>
+      <c r="D257" s="27" t="n"/>
+      <c r="E257" s="27" t="n"/>
+      <c r="F257" s="27" t="n"/>
+      <c r="G257" s="27" t="n"/>
+      <c r="H257" s="27" t="n"/>
+      <c r="I257" s="27" t="n"/>
+      <c r="J257" s="57" t="n"/>
+    </row>
+    <row r="258" ht="22" customHeight="1" s="6">
+      <c r="A258" s="11" t="inlineStr">
+        <is>
+          <t>正解（返答）：She has visited Kyoto five times.</t>
+        </is>
+      </c>
+      <c r="B258" s="27" t="n"/>
+      <c r="C258" s="27" t="n"/>
+      <c r="D258" s="27" t="n"/>
+      <c r="E258" s="27" t="n"/>
+      <c r="F258" s="27" t="n"/>
+      <c r="G258" s="27" t="n"/>
+      <c r="H258" s="27" t="n"/>
+      <c r="I258" s="27" t="n"/>
+      <c r="J258" s="57" t="n"/>
+    </row>
+    <row r="259" ht="18" customHeight="1" s="6">
+      <c r="A259" s="11" t="inlineStr">
+        <is>
+          <t>一度も訪れたことがありません。</t>
+        </is>
+      </c>
+      <c r="B259" s="27" t="n"/>
+      <c r="C259" s="27" t="n"/>
+      <c r="D259" s="27" t="n"/>
+      <c r="E259" s="27" t="n"/>
+      <c r="F259" s="27" t="n"/>
+      <c r="G259" s="27" t="n"/>
+      <c r="H259" s="27" t="n"/>
+      <c r="I259" s="27" t="n"/>
+      <c r="J259" s="57" t="n"/>
+    </row>
+    <row r="260" ht="22" customHeight="1" s="6">
+      <c r="A260" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：She has never visited Kyoto.</t>
+        </is>
+      </c>
+      <c r="B260" s="27" t="n"/>
+      <c r="C260" s="27" t="n"/>
+      <c r="D260" s="27" t="n"/>
+      <c r="E260" s="27" t="n"/>
+      <c r="F260" s="27" t="n"/>
+      <c r="G260" s="27" t="n"/>
+      <c r="H260" s="27" t="n"/>
+      <c r="I260" s="27" t="n"/>
+      <c r="J260" s="57" t="n"/>
+    </row>
+    <row r="261" ht="22" customHeight="1" s="6">
+      <c r="A261" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ）：She has not visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B261" s="27" t="n"/>
+      <c r="C261" s="27" t="n"/>
+      <c r="D261" s="27" t="n"/>
+      <c r="E261" s="27" t="n"/>
+      <c r="F261" s="27" t="n"/>
+      <c r="G261" s="27" t="n"/>
+      <c r="H261" s="27" t="n"/>
+      <c r="I261" s="27" t="n"/>
+      <c r="J261" s="57" t="n"/>
+    </row>
+    <row r="262" ht="22" customHeight="1" s="6">
+      <c r="A262" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：She hasn't visited Kyoto before.</t>
+        </is>
+      </c>
+      <c r="B262" s="27" t="n"/>
+      <c r="C262" s="27" t="n"/>
+      <c r="D262" s="27" t="n"/>
+      <c r="E262" s="27" t="n"/>
+      <c r="F262" s="27" t="n"/>
+      <c r="G262" s="27" t="n"/>
+      <c r="H262" s="27" t="n"/>
+      <c r="I262" s="27" t="n"/>
+      <c r="J262" s="57" t="n"/>
+    </row>
+    <row r="263" ht="6" customHeight="1" s="6">
+      <c r="A263" s="11" t="n"/>
+      <c r="B263" s="27" t="n"/>
+      <c r="C263" s="27" t="n"/>
+      <c r="D263" s="27" t="n"/>
+      <c r="E263" s="27" t="n"/>
+      <c r="F263" s="27" t="n"/>
+      <c r="G263" s="27" t="n"/>
+      <c r="H263" s="27" t="n"/>
+      <c r="I263" s="27" t="n"/>
+      <c r="J263" s="57" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="155">
+  <mergeCells count="263">
     <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A194:J194"/>
+    <mergeCell ref="A234:J234"/>
+    <mergeCell ref="A181:J181"/>
     <mergeCell ref="A91:J91"/>
+    <mergeCell ref="A184:J184"/>
     <mergeCell ref="A43:J43"/>
+    <mergeCell ref="A156:J156"/>
+    <mergeCell ref="A171:J171"/>
+    <mergeCell ref="A165:J165"/>
     <mergeCell ref="A52:J52"/>
     <mergeCell ref="A63:J63"/>
+    <mergeCell ref="A155:J155"/>
     <mergeCell ref="A115:J115"/>
-    <mergeCell ref="A155:J155"/>
     <mergeCell ref="A93:J93"/>
+    <mergeCell ref="A220:J220"/>
+    <mergeCell ref="A173:J173"/>
+    <mergeCell ref="A229:J229"/>
     <mergeCell ref="A130:J130"/>
     <mergeCell ref="A77:J77"/>
+    <mergeCell ref="A83:J83"/>
     <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A83:J83"/>
     <mergeCell ref="A148:J148"/>
+    <mergeCell ref="A261:J261"/>
+    <mergeCell ref="A157:J157"/>
+    <mergeCell ref="A222:J222"/>
+    <mergeCell ref="A138:J138"/>
     <mergeCell ref="A49:J49"/>
-    <mergeCell ref="A138:J138"/>
     <mergeCell ref="A132:J132"/>
     <mergeCell ref="A36:J36"/>
     <mergeCell ref="A119:J119"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A69:J69"/>
+    <mergeCell ref="A196:J196"/>
+    <mergeCell ref="A174:J174"/>
+    <mergeCell ref="A256:J256"/>
+    <mergeCell ref="A205:J205"/>
+    <mergeCell ref="A183:J183"/>
     <mergeCell ref="A66:J66"/>
     <mergeCell ref="A118:J118"/>
     <mergeCell ref="A75:J75"/>
     <mergeCell ref="A133:J133"/>
+    <mergeCell ref="A246:J246"/>
+    <mergeCell ref="A198:J198"/>
+    <mergeCell ref="A233:J233"/>
+    <mergeCell ref="A238:J238"/>
     <mergeCell ref="A120:J120"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A55:J55"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A239:J239"/>
     <mergeCell ref="A95:J95"/>
+    <mergeCell ref="A248:J248"/>
     <mergeCell ref="A104:J104"/>
+    <mergeCell ref="A175:J175"/>
     <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A263:J263"/>
     <mergeCell ref="A32:J32"/>
     <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A159:J159"/>
     <mergeCell ref="A97:J97"/>
+    <mergeCell ref="A219:J219"/>
+    <mergeCell ref="A224:J224"/>
     <mergeCell ref="A106:J106"/>
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A200:J200"/>
     <mergeCell ref="A81:J81"/>
+    <mergeCell ref="A209:J209"/>
+    <mergeCell ref="A96:J96"/>
     <mergeCell ref="A38:J38"/>
-    <mergeCell ref="A96:J96"/>
     <mergeCell ref="A121:J121"/>
     <mergeCell ref="A147:J147"/>
+    <mergeCell ref="A161:J161"/>
     <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A170:J170"/>
     <mergeCell ref="A44:J44"/>
     <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A202:J202"/>
     <mergeCell ref="A58:J58"/>
+    <mergeCell ref="A258:J258"/>
     <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A211:J211"/>
     <mergeCell ref="A67:J67"/>
     <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A186:J186"/>
+    <mergeCell ref="A257:J257"/>
     <mergeCell ref="A73:J73"/>
     <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A201:J201"/>
+    <mergeCell ref="A226:J226"/>
     <mergeCell ref="A82:J82"/>
+    <mergeCell ref="A260:J260"/>
     <mergeCell ref="A60:J60"/>
+    <mergeCell ref="A241:J241"/>
     <mergeCell ref="A123:J123"/>
+    <mergeCell ref="A250:J250"/>
+    <mergeCell ref="A197:J197"/>
+    <mergeCell ref="A228:J228"/>
     <mergeCell ref="A110:J110"/>
     <mergeCell ref="A146:J146"/>
     <mergeCell ref="A124:J124"/>
+    <mergeCell ref="A237:J237"/>
     <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A172:J172"/>
     <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A187:J187"/>
+    <mergeCell ref="A212:J212"/>
+    <mergeCell ref="A221:J221"/>
     <mergeCell ref="A25:J25"/>
+    <mergeCell ref="A243:J243"/>
+    <mergeCell ref="A252:J252"/>
     <mergeCell ref="A108:J108"/>
     <mergeCell ref="A84:J84"/>
+    <mergeCell ref="A236:J236"/>
     <mergeCell ref="A149:J149"/>
+    <mergeCell ref="A214:J214"/>
     <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A189:J189"/>
+    <mergeCell ref="A158:J158"/>
+    <mergeCell ref="A223:J223"/>
     <mergeCell ref="A50:J50"/>
+    <mergeCell ref="A204:J204"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A86:J86"/>
     <mergeCell ref="A42:J42"/>
+    <mergeCell ref="A213:J213"/>
     <mergeCell ref="A151:J151"/>
     <mergeCell ref="A47:J47"/>
+    <mergeCell ref="A160:J160"/>
     <mergeCell ref="A141:J141"/>
+    <mergeCell ref="A254:J254"/>
     <mergeCell ref="A135:J135"/>
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="A150:J150"/>
+    <mergeCell ref="A206:J206"/>
+    <mergeCell ref="A144:J144"/>
     <mergeCell ref="A62:J62"/>
-    <mergeCell ref="A144:J144"/>
     <mergeCell ref="A122:J122"/>
+    <mergeCell ref="A215:J215"/>
+    <mergeCell ref="A262:J262"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A125:J125"/>
+    <mergeCell ref="A190:J190"/>
     <mergeCell ref="A72:J72"/>
     <mergeCell ref="A134:J134"/>
+    <mergeCell ref="A199:J199"/>
     <mergeCell ref="A28:J28"/>
     <mergeCell ref="A112:J112"/>
     <mergeCell ref="A152:J152"/>
     <mergeCell ref="A127:J127"/>
+    <mergeCell ref="A167:J167"/>
+    <mergeCell ref="A249:J249"/>
+    <mergeCell ref="A176:J176"/>
     <mergeCell ref="A30:J30"/>
     <mergeCell ref="A114:J114"/>
     <mergeCell ref="A59:J59"/>
+    <mergeCell ref="A182:J182"/>
     <mergeCell ref="A64:J64"/>
     <mergeCell ref="A98:J98"/>
+    <mergeCell ref="A191:J191"/>
+    <mergeCell ref="A169:J169"/>
+    <mergeCell ref="A225:J225"/>
     <mergeCell ref="A51:J51"/>
     <mergeCell ref="A107:J107"/>
+    <mergeCell ref="A178:J178"/>
     <mergeCell ref="A79:J79"/>
     <mergeCell ref="A61:J61"/>
     <mergeCell ref="A88:J88"/>
     <mergeCell ref="A70:J70"/>
     <mergeCell ref="A153:J153"/>
+    <mergeCell ref="A162:J162"/>
+    <mergeCell ref="A227:J227"/>
     <mergeCell ref="A54:J54"/>
     <mergeCell ref="A137:J137"/>
+    <mergeCell ref="A177:J177"/>
     <mergeCell ref="A90:J90"/>
     <mergeCell ref="A41:J41"/>
+    <mergeCell ref="A217:J217"/>
     <mergeCell ref="A99:J99"/>
+    <mergeCell ref="A164:J164"/>
     <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A145:J145"/>
     <mergeCell ref="A56:J56"/>
     <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A145:J145"/>
     <mergeCell ref="A139:J139"/>
     <mergeCell ref="A154:J154"/>
+    <mergeCell ref="A163:J163"/>
     <mergeCell ref="A101:J101"/>
+    <mergeCell ref="A242:J242"/>
+    <mergeCell ref="A195:J195"/>
+    <mergeCell ref="A251:J251"/>
     <mergeCell ref="A76:J76"/>
     <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A203:J203"/>
     <mergeCell ref="A116:J116"/>
     <mergeCell ref="A85:J85"/>
     <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A188:J188"/>
+    <mergeCell ref="A244:J244"/>
+    <mergeCell ref="A259:J259"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A100:J100"/>
+    <mergeCell ref="A253:J253"/>
     <mergeCell ref="A131:J131"/>
     <mergeCell ref="A126:J126"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A100:J100"/>
-    <mergeCell ref="A140:J140"/>
     <mergeCell ref="A53:J53"/>
     <mergeCell ref="A35:J35"/>
     <mergeCell ref="A109:J109"/>
+    <mergeCell ref="A140:J140"/>
+    <mergeCell ref="A180:J180"/>
+    <mergeCell ref="A231:J231"/>
+    <mergeCell ref="A240:J240"/>
     <mergeCell ref="A129:J129"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="A68:J68"/>
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A102:J102"/>
     <mergeCell ref="A117:J117"/>
+    <mergeCell ref="A230:J230"/>
     <mergeCell ref="A111:J111"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="A143:J143"/>
+    <mergeCell ref="A245:J245"/>
     <mergeCell ref="A92:J92"/>
     <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A166:J166"/>
     <mergeCell ref="A48:J48"/>
+    <mergeCell ref="A232:J232"/>
     <mergeCell ref="A142:J142"/>
+    <mergeCell ref="A207:J207"/>
     <mergeCell ref="A11:J11"/>
     <mergeCell ref="A103:J103"/>
     <mergeCell ref="A94:J94"/>
     <mergeCell ref="A45:J45"/>
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A216:J216"/>
+    <mergeCell ref="A168:J168"/>
     <mergeCell ref="A78:J78"/>
     <mergeCell ref="A87:J87"/>
     <mergeCell ref="A65:J65"/>
+    <mergeCell ref="A218:J218"/>
     <mergeCell ref="A128:J128"/>
+    <mergeCell ref="A193:J193"/>
+    <mergeCell ref="A255:J255"/>
     <mergeCell ref="A80:J80"/>
     <mergeCell ref="A46:J46"/>
     <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A208:J208"/>
     <mergeCell ref="A89:J89"/>
     <mergeCell ref="A136:J136"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="A105:J105"/>
+    <mergeCell ref="A192:J192"/>
     <mergeCell ref="A57:J57"/>
     <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A210:J210"/>
     <mergeCell ref="A113:J113"/>
+    <mergeCell ref="A179:J179"/>
+    <mergeCell ref="A235:J235"/>
+    <mergeCell ref="A247:J247"/>
     <mergeCell ref="A71:J71"/>
+    <mergeCell ref="A185:J185"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1" gridLines="1"/>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1" verticalDpi="0"/>
   <rowBreaks count="8" manualBreakCount="8">
-    <brk id="19" min="0" max="16383" man="1"/>
-    <brk id="36" min="0" max="16383" man="1"/>
-    <brk id="53" min="0" max="16383" man="1"/>
-    <brk id="70" min="0" max="16383" man="1"/>
-    <brk id="87" min="0" max="16383" man="1"/>
-    <brk id="104" min="0" max="16383" man="1"/>
-    <brk id="121" min="0" max="16383" man="1"/>
-    <brk id="138" min="0" max="16383" man="1"/>
+    <brk id="31" min="0" max="16383" man="1"/>
+    <brk id="60" min="0" max="16383" man="1"/>
+    <brk id="89" min="0" max="16383" man="1"/>
+    <brk id="118" min="0" max="16383" man="1"/>
+    <brk id="147" min="0" max="16383" man="1"/>
+    <brk id="176" min="0" max="16383" man="1"/>
+    <brk id="205" min="0" max="16383" man="1"/>
+    <brk id="234" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/Studymaterials/中学生英作文現在完了形_経験用法編.xlsx
+++ b/Studymaterials/中学生英作文現在完了形_経験用法編.xlsx
@@ -5833,7 +5833,7 @@
     <row r="18" ht="22" customHeight="1" s="6">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：No, you have not visited Kyoto before.</t>
+          <t>正解（言いかえ）：No, you have not (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B18" s="27" t="n"/>
@@ -5849,7 +5849,7 @@
     <row r="19" ht="22" customHeight="1" s="6">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, you haven't visited Kyoto before.</t>
+          <t>正解（短縮形）：No, you haven't (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B19" s="27" t="n"/>
@@ -6009,7 +6009,7 @@
     <row r="29" ht="22" customHeight="1" s="6">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：You have not visited Kyoto before.</t>
+          <t>正解（言いかえ）：You have not (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B29" s="27" t="n"/>
@@ -6025,7 +6025,7 @@
     <row r="30" ht="22" customHeight="1" s="6">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：You haven't visited Kyoto before.</t>
+          <t>正解（短縮形）：You haven't (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B30" s="27" t="n"/>
@@ -6295,7 +6295,7 @@
     <row r="47" ht="22" customHeight="1" s="6">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：No, I have not visited Kyoto before.</t>
+          <t>正解（言いかえ）：No, I have not (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B47" s="27" t="n"/>
@@ -6311,7 +6311,7 @@
     <row r="48" ht="22" customHeight="1" s="6">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, I haven't visited Kyoto before.</t>
+          <t>正解（短縮形）：No, I haven't (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B48" s="27" t="n"/>
@@ -6471,7 +6471,7 @@
     <row r="58" ht="22" customHeight="1" s="6">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：I have not visited Kyoto before.</t>
+          <t>正解（言いかえ）：I have not (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B58" s="27" t="n"/>
@@ -6487,7 +6487,7 @@
     <row r="59" ht="22" customHeight="1" s="6">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：I haven't visited Kyoto before.</t>
+          <t>正解（短縮形）：I haven't (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B59" s="27" t="n"/>
@@ -6757,7 +6757,7 @@
     <row r="76" ht="22" customHeight="1" s="6">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：No, he has not visited Kyoto before.</t>
+          <t>正解（言いかえ）：No, he has not (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B76" s="27" t="n"/>
@@ -6773,7 +6773,7 @@
     <row r="77" ht="22" customHeight="1" s="6">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, he hasn't visited Kyoto before.</t>
+          <t>正解（短縮形）：No, he hasn't (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B77" s="27" t="n"/>
@@ -6933,7 +6933,7 @@
     <row r="87" ht="22" customHeight="1" s="6">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：He has not visited Kyoto before.</t>
+          <t>正解（言いかえ）：He has not (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B87" s="27" t="n"/>
@@ -6949,7 +6949,7 @@
     <row r="88" ht="22" customHeight="1" s="6">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：He hasn't visited Kyoto before.</t>
+          <t>正解（短縮形）：He hasn't (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B88" s="27" t="n"/>
@@ -7219,7 +7219,7 @@
     <row r="105" ht="22" customHeight="1" s="6">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：No, she has not visited Kyoto before.</t>
+          <t>正解（言いかえ）：No, she has not (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B105" s="27" t="n"/>
@@ -7235,7 +7235,7 @@
     <row r="106" ht="22" customHeight="1" s="6">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, she hasn't visited Kyoto before.</t>
+          <t>正解（短縮形）：No, she hasn't (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B106" s="27" t="n"/>
@@ -7395,7 +7395,7 @@
     <row r="116" ht="22" customHeight="1" s="6">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：She has not visited Kyoto before.</t>
+          <t>正解（言いかえ）：She has not (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B116" s="27" t="n"/>
@@ -7411,7 +7411,7 @@
     <row r="117" ht="22" customHeight="1" s="6">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：She hasn't visited Kyoto before.</t>
+          <t>正解（短縮形）：She hasn't (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B117" s="27" t="n"/>
@@ -7682,7 +7682,7 @@
     <row r="134" ht="22" customHeight="1" s="6">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：No, you have not visited Kyoto before.</t>
+          <t>正解（言いかえ）：No, you have not (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B134" s="27" t="n"/>
@@ -7698,7 +7698,7 @@
     <row r="135" ht="22" customHeight="1" s="6">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, you haven't visited Kyoto before.</t>
+          <t>正解（短縮形）：No, you haven't (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B135" s="27" t="n"/>
@@ -7858,7 +7858,7 @@
     <row r="145" ht="22" customHeight="1" s="6">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：You have not visited Kyoto before.</t>
+          <t>正解（言いかえ）：You have not (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B145" s="27" t="n"/>
@@ -7874,7 +7874,7 @@
     <row r="146" ht="22" customHeight="1" s="6">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：You haven't visited Kyoto before.</t>
+          <t>正解（短縮形）：You haven't (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B146" s="27" t="n"/>
@@ -8128,7 +8128,7 @@
     <row r="162" ht="22" customHeight="1" s="6">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：No, We have never visited Kyoto.</t>
+          <t>正解（基本形）：No, we have never visited Kyoto.</t>
         </is>
       </c>
       <c r="B162" s="27" t="n"/>
@@ -8144,7 +8144,7 @@
     <row r="163" ht="22" customHeight="1" s="6">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：No, We have not visited Kyoto before.</t>
+          <t>正解（言いかえ）：No, we have not (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B163" s="27" t="n"/>
@@ -8160,7 +8160,7 @@
     <row r="164" ht="22" customHeight="1" s="6">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, We haven't visited Kyoto before.</t>
+          <t>正解（短縮形）：No, we haven't (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B164" s="27" t="n"/>
@@ -8320,7 +8320,7 @@
     <row r="174" ht="22" customHeight="1" s="6">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：We have not visited Kyoto before.</t>
+          <t>正解（言いかえ）：We have not (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B174" s="27" t="n"/>
@@ -8336,7 +8336,7 @@
     <row r="175" ht="22" customHeight="1" s="6">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：We haven't visited Kyoto before.</t>
+          <t>正解（短縮形）：We haven't (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B175" s="27" t="n"/>
@@ -8606,7 +8606,7 @@
     <row r="192" ht="22" customHeight="1" s="6">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：No, they have not visited Kyoto before.</t>
+          <t>正解（言いかえ）：No, they have not (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B192" s="27" t="n"/>
@@ -8622,7 +8622,7 @@
     <row r="193" ht="22" customHeight="1" s="6">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, they haven't visited Kyoto before.</t>
+          <t>正解（短縮形）：No, they haven't (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B193" s="27" t="n"/>
@@ -8782,7 +8782,7 @@
     <row r="203" ht="22" customHeight="1" s="6">
       <c r="A203" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：They have not visited Kyoto before.</t>
+          <t>正解（言いかえ）：They have not (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B203" s="27" t="n"/>
@@ -8798,7 +8798,7 @@
     <row r="204" ht="22" customHeight="1" s="6">
       <c r="A204" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：They haven't visited Kyoto before.</t>
+          <t>正解（短縮形）：They haven't (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B204" s="27" t="n"/>
@@ -9068,7 +9068,7 @@
     <row r="221" ht="22" customHeight="1" s="6">
       <c r="A221" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：No, he has not visited Kyoto before.</t>
+          <t>正解（言いかえ）：No, he has not (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B221" s="27" t="n"/>
@@ -9084,7 +9084,7 @@
     <row r="222" ht="22" customHeight="1" s="6">
       <c r="A222" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, he hasn't visited Kyoto before.</t>
+          <t>正解（短縮形）：No, he hasn't (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B222" s="27" t="n"/>
@@ -9244,7 +9244,7 @@
     <row r="232" ht="22" customHeight="1" s="6">
       <c r="A232" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：He has not visited Kyoto before.</t>
+          <t>正解（言いかえ）：He has not (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B232" s="27" t="n"/>
@@ -9260,7 +9260,7 @@
     <row r="233" ht="22" customHeight="1" s="6">
       <c r="A233" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：He hasn't visited Kyoto before.</t>
+          <t>正解（短縮形）：He hasn't (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B233" s="27" t="n"/>
@@ -9530,7 +9530,7 @@
     <row r="250" ht="22" customHeight="1" s="6">
       <c r="A250" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：No, she has not visited Kyoto before.</t>
+          <t>正解（言いかえ）：No, she has not (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B250" s="27" t="n"/>
@@ -9546,7 +9546,7 @@
     <row r="251" ht="22" customHeight="1" s="6">
       <c r="A251" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, she hasn't visited Kyoto before.</t>
+          <t>正解（短縮形）：No, she hasn't (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B251" s="27" t="n"/>
@@ -9706,7 +9706,7 @@
     <row r="261" ht="22" customHeight="1" s="6">
       <c r="A261" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：She has not visited Kyoto before.</t>
+          <t>正解（言いかえ）：She has not (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B261" s="27" t="n"/>
@@ -9722,7 +9722,7 @@
     <row r="262" ht="22" customHeight="1" s="6">
       <c r="A262" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：She hasn't visited Kyoto before.</t>
+          <t>正解（短縮形）：She hasn't (visited Kyoto before).</t>
         </is>
       </c>
       <c r="B262" s="27" t="n"/>
